--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -149,12 +149,11 @@
           </rPr>
           <t xml:space="preserve">
 {0}百分比
-{1} 固定值 
-{2} 距离 
-{3}持续时间 
-{4}最大攻击数量 
-{5}行
-{6}列
+{1} 固定值  
+{2}持续时间 
+{3}最大攻击数量 
+{4}行
+{5}列
 </t>
         </r>
       </text>
@@ -301,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH3" authorId="0">
+    <comment ref="AG3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -328,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="151">
   <si>
     <t>_ID</t>
   </si>
@@ -525,7 +524,7 @@
     <t>基础心法</t>
   </si>
   <si>
-    <t>被动增加人物100点物攻和1%的物攻倍率，无需上阵</t>
+    <t>被动增加{0}%的物攻倍率和{1}点物攻，无需上阵</t>
   </si>
   <si>
     <t>Self</t>
@@ -549,7 +548,7 @@
     <t>半月弯刀</t>
   </si>
   <si>
-    <t>施展{3}*{4}范围的剑阵，持续{2}s，对其内的敌人造成{0}%物攻+{1}点伤害，按攻速结算</t>
+    <t>施展{4}*{5}范围的剑阵，持续{2}s，对其内的敌人造成{0}%物攻+{1}点伤害，按攻速结算</t>
   </si>
   <si>
     <t>Enemy</t>
@@ -567,7 +566,7 @@
     <t>野蛮撞击</t>
   </si>
   <si>
-    <t>对目标敌人造成{1}%物攻伤害，并且晕眩2秒</t>
+    <t>对目标敌人造成{0}%物攻+{1}点物攻伤害，并且晕眩{2}秒</t>
   </si>
   <si>
     <t>Chase</t>
@@ -582,7 +581,7 @@
     <t>武力盾</t>
   </si>
   <si>
-    <t>提高人物{1}防御和{2}生命，持续{3}秒</t>
+    <t>提高人物{0}防御和{1}生命，持续{2}秒</t>
   </si>
   <si>
     <t>Square</t>
@@ -597,7 +596,7 @@
     <t>武力精通</t>
   </si>
   <si>
-    <t>战士技能增加{1}%技能系数增幅，无需上阵</t>
+    <t>战士技能增加{0}%技能系数增幅，无需上阵</t>
   </si>
   <si>
     <t>FullBox</t>
@@ -609,16 +608,16 @@
     <t>烈火</t>
   </si>
   <si>
-    <t>对单个敌人造成{1}%物攻+{0}点伤害，降低敌人一半的防御和减伤</t>
+    <t>对单个敌人造成{0}%物攻+{1}点伤害，降低敌人一半的防御和减伤</t>
   </si>
   <si>
     <t>"103,4,0,25","101,0,0,10"</t>
   </si>
   <si>
-    <t>冥想法</t>
-  </si>
-  <si>
-    <t>被动增加人物100点魔攻和1%的魔攻倍率，无需上阵</t>
+    <t>冥想心法</t>
+  </si>
+  <si>
+    <t>被动增加{0}%的魔攻倍率和{1}点魔攻，无需上阵</t>
   </si>
   <si>
     <t>Circle</t>
@@ -630,25 +629,25 @@
     <t>雷电术</t>
   </si>
   <si>
-    <t>对{4}个敌人造成{0}%魔法+{1}点伤害</t>
-  </si>
-  <si>
-    <t>烈焰墙</t>
+    <t>对{3}个敌人造成{0}%魔法+{1}点伤害</t>
+  </si>
+  <si>
+    <t>火海术</t>
   </si>
   <si>
     <t>火墙</t>
   </si>
   <si>
-    <t>施展{3}*{4}范围的烈焰，持续{2}s，对其内的敌人造成{0}%魔法+{1}点伤害，按攻速结算</t>
-  </si>
-  <si>
-    <t>烈焰环</t>
+    <t>施展{4}*{5}范围的烈焰，持续{2}s，对其内的敌人造成{0}%魔法+{1}点伤害，按攻速结算</t>
+  </si>
+  <si>
+    <t>烈焰术</t>
   </si>
   <si>
     <t>抗拒火环</t>
   </si>
   <si>
-    <t>对{5}*{6}范围内的敌人造成{0}%魔法+{1}点伤害</t>
+    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点伤害</t>
   </si>
   <si>
     <t>"12,60,3,10"</t>
@@ -660,7 +659,7 @@
     <t>魔法盾</t>
   </si>
   <si>
-    <t>提高人物{1}魔攻和{2}生命，持续{3}秒</t>
+    <t>提高人物{0}魔攻和{1}生命，持续{2}秒</t>
   </si>
   <si>
     <t>冰心诀</t>
@@ -669,7 +668,7 @@
     <t>法术精通</t>
   </si>
   <si>
-    <t>法师技能增加{1}%技能系数增幅，无需上阵</t>
+    <t>法师技能增加{0}%技能系数增幅，无需上阵</t>
   </si>
   <si>
     <t>冰封术</t>
@@ -678,16 +677,16 @@
     <t>冰咆哮</t>
   </si>
   <si>
-    <t>对{3}*{4}范围内的敌人造成{1}%魔法伤害，冰封所有敌人2秒</t>
+    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点伤害，冰封所有敌人2秒</t>
   </si>
   <si>
     <t>"305,1,1,0"</t>
   </si>
   <si>
-    <t>祈福术</t>
-  </si>
-  <si>
-    <t>被动增加人物100点道攻和1%的道攻倍率，无需上阵</t>
+    <t>祈福心法</t>
+  </si>
+  <si>
+    <t>被动增加{0}%的道攻倍率和{1}点道攻，无需上阵</t>
   </si>
   <si>
     <t>灭魔符</t>
@@ -696,7 +695,7 @@
     <t>火符术</t>
   </si>
   <si>
-    <t>对{0}个敌人造成{1}%道术伤害，无视70%防御</t>
+    <t>对{3}个敌人造成{0}%道术+{1}点伤害</t>
   </si>
   <si>
     <t>毒咒术</t>
@@ -705,7 +704,7 @@
     <t>施毒术</t>
   </si>
   <si>
-    <t>对{4}个敌人造成{0}%道术+{1}点的持续{3}秒伤害，按攻速结算</t>
+    <t>对{3}个敌人造成{0}%道术+{1}点的持续{2}秒伤害，按攻速结算</t>
   </si>
   <si>
     <t>"104,5,0,35"</t>
@@ -726,7 +725,7 @@
     <t>道力盾</t>
   </si>
   <si>
-    <t>提高人物{1}减伤和{2}生命，持续{3}秒</t>
+    <t>提高人物{0}减伤和{1}生命，持续{2}秒</t>
   </si>
   <si>
     <t>圣心诀</t>
@@ -735,7 +734,7 @@
     <t>道力精通</t>
   </si>
   <si>
-    <t>被动道士技能增加{1}%技能系数增幅，无需上阵</t>
+    <t>被动道士技能增加{0}%技能系数增幅，无需上阵</t>
   </si>
   <si>
     <t>唤神咒</t>
@@ -744,7 +743,7 @@
     <t>召唤神兽</t>
   </si>
   <si>
-    <t>召唤{4}只神兽战斗，攻击为{0}%道攻+{1}，其他全额继承</t>
+    <t>召唤{3}只神兽战斗，攻击为{0}%道攻+{1}，其他全额继承</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -778,12 +777,6 @@
   </si>
   <si>
     <t>"18,3,0,100"</t>
-  </si>
-  <si>
-    <t>飓风破</t>
-  </si>
-  <si>
-    <t>对{3}*{4}范围内的敌人造成驱魔符伤害*火符弹射次数*{1}%，额外附带70%无视伤害</t>
   </si>
   <si>
     <t>普攻</t>
@@ -1767,7 +1760,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:AI79"/>
+  <dimension ref="C2:AH79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
@@ -1792,19 +1785,19 @@
     <col min="23" max="23" width="7.375" style="2" customWidth="1"/>
     <col min="24" max="24" width="7.50833333333333" style="2" customWidth="1"/>
     <col min="25" max="25" width="8.25" style="2" customWidth="1"/>
-    <col min="27" max="29" width="7.625" style="2" customWidth="1"/>
-    <col min="30" max="30" width="9.625" style="2" customWidth="1"/>
-    <col min="31" max="32" width="7.875" style="2" customWidth="1"/>
-    <col min="33" max="33" width="9.75" style="2" customWidth="1"/>
-    <col min="34" max="34" width="21.75" style="2" customWidth="1"/>
-    <col min="35" max="35" width="11.75" style="2" customWidth="1"/>
-    <col min="36" max="16384" width="9" style="2"/>
+    <col min="26" max="28" width="7.625" style="2" customWidth="1"/>
+    <col min="29" max="29" width="9.625" style="2" customWidth="1"/>
+    <col min="30" max="31" width="7.875" style="2" customWidth="1"/>
+    <col min="32" max="32" width="9.75" style="2" customWidth="1"/>
+    <col min="33" max="33" width="21.75" style="2" customWidth="1"/>
+    <col min="34" max="34" width="11.75" style="2" customWidth="1"/>
+    <col min="35" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" ht="33" customHeight="1" spans="3:35">
+    <row r="2" ht="33" customHeight="1" spans="3:34">
       <c r="L2" s="3"/>
     </row>
-    <row r="3" customHeight="1" spans="3:35">
+    <row r="3" customHeight="1" spans="3:34">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1874,35 +1867,35 @@
       <c r="Y3" s="4" t="s">
         <v>21</v>
       </c>
+      <c r="Z3" s="4" t="s">
+        <v>22</v>
+      </c>
       <c r="AA3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AG3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="AI3" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" customHeight="1" spans="3:35">
+    <row r="4" customHeight="1" spans="3:34">
       <c r="C4" s="4" t="s">
         <v>31</v>
       </c>
@@ -1972,35 +1965,35 @@
       <c r="Y4" s="4" t="s">
         <v>51</v>
       </c>
+      <c r="Z4" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="AA4" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AH4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="AI4" s="4" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" customHeight="1" spans="3:35">
+    <row r="5" customHeight="1" spans="3:34">
       <c r="C5" s="4" t="s">
         <v>61</v>
       </c>
@@ -2070,6 +2063,9 @@
       <c r="Y5" s="4" t="s">
         <v>62</v>
       </c>
+      <c r="Z5" s="4" t="s">
+        <v>61</v>
+      </c>
       <c r="AA5" s="4" t="s">
         <v>61</v>
       </c>
@@ -2089,16 +2085,13 @@
         <v>61</v>
       </c>
       <c r="AG5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="AH5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI5" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:35">
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2166,8 +2159,11 @@
       <c r="Y6" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
       <c r="AA6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" s="1">
         <v>0</v>
@@ -2184,14 +2180,11 @@
       <c r="AF6" s="1">
         <v>0</v>
       </c>
-      <c r="AG6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="1">
+      <c r="AH6" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2261,8 +2254,11 @@
       <c r="Y7" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="Z7" s="1">
+        <v>2</v>
+      </c>
       <c r="AA7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB7" s="1">
         <v>0</v>
@@ -2279,14 +2275,11 @@
       <c r="AF7" s="1">
         <v>0</v>
       </c>
-      <c r="AG7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="1">
+      <c r="AH7" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2348,7 +2341,7 @@
         <v>800</v>
       </c>
       <c r="W8" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X8" s="1" t="s">
         <v>74</v>
@@ -2356,11 +2349,14 @@
       <c r="Y8" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
       <c r="AA8" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AC8" s="1">
         <v>0</v>
@@ -2374,17 +2370,14 @@
       <c r="AF8" s="1">
         <v>0</v>
       </c>
-      <c r="AG8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH8" s="1" t="s">
+      <c r="AG8" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="AI8" s="1">
+      <c r="AH8" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2454,8 +2447,11 @@
       <c r="Y9" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="Z9" s="1">
+        <v>1</v>
+      </c>
       <c r="AA9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" s="1">
         <v>0</v>
@@ -2472,17 +2468,14 @@
       <c r="AF9" s="1">
         <v>0</v>
       </c>
-      <c r="AG9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH9" s="1" t="s">
+      <c r="AG9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="AI9" s="1">
+      <c r="AH9" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2552,6 +2545,9 @@
       <c r="Y10" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z10" s="1">
+        <v>0</v>
+      </c>
       <c r="AA10" s="1">
         <v>0</v>
       </c>
@@ -2570,17 +2566,14 @@
       <c r="AF10" s="1">
         <v>0</v>
       </c>
-      <c r="AG10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="5" t="s">
+      <c r="AG10" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AI10" s="1">
+      <c r="AH10" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2650,6 +2643,9 @@
       <c r="Y11" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
       <c r="AA11" s="1">
         <v>0</v>
       </c>
@@ -2668,14 +2664,11 @@
       <c r="AF11" s="1">
         <v>0</v>
       </c>
-      <c r="AG11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="1">
+      <c r="AH11" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2745,8 +2738,11 @@
       <c r="Y12" s="1" t="s">
         <v>67</v>
       </c>
+      <c r="Z12" s="1">
+        <v>1</v>
+      </c>
       <c r="AA12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" s="1">
         <v>0</v>
@@ -2763,29 +2759,26 @@
       <c r="AF12" s="1">
         <v>0</v>
       </c>
-      <c r="AG12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="6" t="s">
+      <c r="AG12" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="AI12" s="1">
+      <c r="AH12" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G13" s="2"/>
-      <c r="AH13" s="6"/>
+      <c r="AG13" s="6"/>
     </row>
     <row r="14" customFormat="1" customHeight="1"/>
     <row r="15" customFormat="1" customHeight="1"/>
     <row r="16" customFormat="1" customHeight="1"/>
     <row r="17" customFormat="1" customHeight="1"/>
     <row r="18" customFormat="1" customHeight="1"/>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G19" s="2"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C20" s="1">
         <v>2001</v>
       </c>
@@ -2853,8 +2846,11 @@
       <c r="Y20" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="Z20" s="1">
+        <v>0</v>
+      </c>
       <c r="AA20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" s="1">
         <v>0</v>
@@ -2871,14 +2867,11 @@
       <c r="AF20" s="1">
         <v>0</v>
       </c>
-      <c r="AG20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="1">
+      <c r="AH20" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C21" s="1">
         <v>2002</v>
       </c>
@@ -2948,8 +2941,11 @@
       <c r="Y21" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="Z21" s="1">
+        <v>1</v>
+      </c>
       <c r="AA21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="1">
         <v>0</v>
@@ -2966,14 +2962,11 @@
       <c r="AF21" s="1">
         <v>0</v>
       </c>
-      <c r="AG21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="1">
+      <c r="AH21" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C22" s="1">
         <v>2003</v>
       </c>
@@ -3043,14 +3036,17 @@
       <c r="Y22" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z22" s="1">
+        <v>0</v>
+      </c>
       <c r="AA22" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB22" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC22" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD22" s="1">
         <v>0</v>
@@ -3061,14 +3057,11 @@
       <c r="AF22" s="1">
         <v>0</v>
       </c>
-      <c r="AG22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI22" s="1">
+      <c r="AH22" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C23" s="1">
         <v>2004</v>
       </c>
@@ -3138,14 +3131,17 @@
       <c r="Y23" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z23" s="1">
+        <v>0</v>
+      </c>
       <c r="AA23" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB23" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AC23" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD23" s="1">
         <v>0</v>
@@ -3156,17 +3152,14 @@
       <c r="AF23" s="1">
         <v>0</v>
       </c>
-      <c r="AG23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH23" s="1" t="s">
+      <c r="AG23" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AI23" s="1">
+      <c r="AH23" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C24" s="1">
         <v>2005</v>
       </c>
@@ -3236,6 +3229,9 @@
       <c r="Y24" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z24" s="1">
+        <v>0</v>
+      </c>
       <c r="AA24" s="1">
         <v>0</v>
       </c>
@@ -3254,17 +3250,14 @@
       <c r="AF24" s="1">
         <v>0</v>
       </c>
-      <c r="AG24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH24" s="5" t="s">
+      <c r="AG24" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AI24" s="1">
+      <c r="AH24" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C25" s="1">
         <v>2006</v>
       </c>
@@ -3334,6 +3327,9 @@
       <c r="Y25" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="Z25" s="1">
+        <v>0</v>
+      </c>
       <c r="AA25" s="1">
         <v>0</v>
       </c>
@@ -3352,14 +3348,11 @@
       <c r="AF25" s="1">
         <v>0</v>
       </c>
-      <c r="AG25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI25" s="1">
+      <c r="AH25" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C26" s="1">
         <v>2007</v>
       </c>
@@ -3429,14 +3422,17 @@
       <c r="Y26" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z26" s="1">
+        <v>0</v>
+      </c>
       <c r="AA26" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AB26" s="1">
         <v>3</v>
       </c>
       <c r="AC26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD26" s="1">
         <v>0</v>
@@ -3447,27 +3443,24 @@
       <c r="AF26" s="1">
         <v>0</v>
       </c>
-      <c r="AG26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH26" s="6" t="s">
+      <c r="AG26" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="AI26" s="1">
+      <c r="AH26" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G27" s="2"/>
-      <c r="AH27" s="6"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:35">
+      <c r="AG27" s="6"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G28" s="2"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G30" s="2"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -3475,7 +3468,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G31" s="2"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -3483,13 +3476,13 @@
       <c r="K31" s="1"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="L32" s="2"/>
     </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G33" s="2"/>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C34" s="1">
         <v>3001</v>
       </c>
@@ -3557,6 +3550,9 @@
       <c r="Y34" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
       <c r="AA34" s="1">
         <v>0</v>
       </c>
@@ -3575,14 +3571,11 @@
       <c r="AF34" s="1">
         <v>0</v>
       </c>
-      <c r="AG34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI34" s="1">
+      <c r="AH34" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C35" s="1">
         <v>3002</v>
       </c>
@@ -3652,8 +3645,11 @@
       <c r="Y35" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="Z35" s="1">
+        <v>1</v>
+      </c>
       <c r="AA35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="1">
         <v>0</v>
@@ -3670,14 +3666,11 @@
       <c r="AF35" s="1">
         <v>0</v>
       </c>
-      <c r="AG35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI35" s="1">
+      <c r="AH35" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C36" s="1">
         <v>3003</v>
       </c>
@@ -3747,8 +3740,11 @@
       <c r="Y36" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="Z36" s="1">
+        <v>5</v>
+      </c>
       <c r="AA36" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB36" s="1">
         <v>0</v>
@@ -3765,17 +3761,14 @@
       <c r="AF36" s="1">
         <v>0</v>
       </c>
-      <c r="AG36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH36" s="1" t="s">
+      <c r="AG36" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="AI36" s="1">
+      <c r="AH36" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C37" s="1">
         <v>3004</v>
       </c>
@@ -3845,8 +3838,11 @@
       <c r="Y37" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="Z37" s="1">
+        <v>3</v>
+      </c>
       <c r="AA37" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" s="1">
         <v>0</v>
@@ -3863,14 +3859,11 @@
       <c r="AF37" s="1">
         <v>0</v>
       </c>
-      <c r="AG37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI37" s="1">
+      <c r="AH37" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C38" s="1">
         <v>3005</v>
       </c>
@@ -3940,6 +3933,9 @@
       <c r="Y38" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z38" s="1">
+        <v>0</v>
+      </c>
       <c r="AA38" s="1">
         <v>0</v>
       </c>
@@ -3958,17 +3954,14 @@
       <c r="AF38" s="1">
         <v>0</v>
       </c>
-      <c r="AG38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH38" s="5" t="s">
+      <c r="AG38" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="AI38" s="1">
+      <c r="AH38" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C39" s="1">
         <v>3006</v>
       </c>
@@ -4038,6 +4031,9 @@
       <c r="Y39" s="1" t="s">
         <v>90</v>
       </c>
+      <c r="Z39" s="1">
+        <v>0</v>
+      </c>
       <c r="AA39" s="1">
         <v>0</v>
       </c>
@@ -4056,14 +4052,11 @@
       <c r="AF39" s="1">
         <v>0</v>
       </c>
-      <c r="AG39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI39" s="1">
+      <c r="AH39" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C40" s="1">
         <v>3007</v>
       </c>
@@ -4133,8 +4126,11 @@
       <c r="Y40" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z40" s="1">
+        <v>2</v>
+      </c>
       <c r="AA40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB40" s="1">
         <v>0</v>
@@ -4151,23 +4147,20 @@
       <c r="AF40" s="1">
         <v>0</v>
       </c>
-      <c r="AG40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI40" s="1">
+      <c r="AH40" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G41" s="2"/>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G42" s="2"/>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G43" s="2"/>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C44" s="1">
         <v>4001</v>
       </c>
@@ -4237,6 +4230,9 @@
       <c r="Y44" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z44" s="1">
+        <v>0</v>
+      </c>
       <c r="AA44" s="1">
         <v>0</v>
       </c>
@@ -4255,17 +4251,14 @@
       <c r="AF44" s="1">
         <v>0</v>
       </c>
-      <c r="AG44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="1" t="s">
+      <c r="AG44" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="AI44" s="1">
+      <c r="AH44" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C45" s="1">
         <v>4002</v>
       </c>
@@ -4335,6 +4328,9 @@
       <c r="Y45" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z45" s="1">
+        <v>0</v>
+      </c>
       <c r="AA45" s="1">
         <v>0</v>
       </c>
@@ -4353,15 +4349,12 @@
       <c r="AF45" s="1">
         <v>0</v>
       </c>
-      <c r="AG45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH45" s="5"/>
-      <c r="AI45" s="1">
+      <c r="AG45" s="5"/>
+      <c r="AH45" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C46" s="1">
         <v>4003</v>
       </c>
@@ -4431,6 +4424,9 @@
       <c r="Y46" s="1" t="s">
         <v>85</v>
       </c>
+      <c r="Z46" s="1">
+        <v>0</v>
+      </c>
       <c r="AA46" s="1">
         <v>0</v>
       </c>
@@ -4449,116 +4445,21 @@
       <c r="AF46" s="1">
         <v>0</v>
       </c>
-      <c r="AG46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH46" s="1" t="s">
+      <c r="AG46" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="AI46" s="1">
+      <c r="AH46" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:35">
-      <c r="C47" s="1">
-        <v>4004</v>
-      </c>
-      <c r="D47" s="1">
-        <v>4004</v>
-      </c>
-      <c r="E47" s="1">
-        <v>7</v>
-      </c>
-      <c r="F47" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H47" s="1">
-        <v>1</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="J47" s="1">
-        <v>3002</v>
-      </c>
-      <c r="K47" s="1">
-        <v>10</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="M47" s="1">
-        <v>0</v>
-      </c>
-      <c r="N47" s="1">
-        <v>0</v>
-      </c>
-      <c r="O47" s="1">
-        <v>0</v>
-      </c>
-      <c r="P47" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q47" s="1">
-        <v>3</v>
-      </c>
-      <c r="R47" s="1">
-        <v>1</v>
-      </c>
-      <c r="S47" s="1">
-        <v>500</v>
-      </c>
-      <c r="T47" s="1">
-        <v>0</v>
-      </c>
-      <c r="U47" s="1">
-        <v>0</v>
-      </c>
-      <c r="V47" s="1">
-        <v>0</v>
-      </c>
-      <c r="W47" s="1">
-        <v>6</v>
-      </c>
-      <c r="X47" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y47" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA47" s="1">
-        <v>5</v>
-      </c>
-      <c r="AB47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG47" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI47" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="G47" s="2"/>
+    </row>
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C49" s="1">
         <v>9001</v>
       </c>
@@ -4569,10 +4470,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H49" s="1">
         <v>9</v>
@@ -4622,8 +4523,11 @@
       <c r="Y49" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="Z49" s="1">
+        <v>1</v>
+      </c>
       <c r="AA49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB49" s="1">
         <v>0</v>
@@ -4640,18 +4544,15 @@
       <c r="AF49" s="1">
         <v>0</v>
       </c>
-      <c r="AG49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AI49" s="1">
+      <c r="AH49" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1"/>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G51" s="2"/>
     </row>
-    <row r="52" customHeight="1" spans="3:35">
+    <row r="52" customHeight="1" spans="3:34">
       <c r="E52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
@@ -4664,6 +4565,7 @@
       <c r="V52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1"/>
+      <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
@@ -4671,9 +4573,8 @@
       <c r="AF52" s="1"/>
       <c r="AG52" s="1"/>
       <c r="AH52" s="1"/>
-      <c r="AI52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="3:35">
+    </row>
+    <row r="53" customHeight="1" spans="3:34">
       <c r="E53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
@@ -4689,6 +4590,7 @@
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
       <c r="AC53" s="1"/>
@@ -4697,9 +4599,8 @@
       <c r="AF53" s="1"/>
       <c r="AG53" s="1"/>
       <c r="AH53" s="1"/>
-      <c r="AI53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="3:35">
+    </row>
+    <row r="54" customHeight="1" spans="3:34">
       <c r="E54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
@@ -4707,12 +4608,12 @@
       <c r="P54" s="1"/>
       <c r="U54" s="1"/>
       <c r="V54" s="1"/>
+      <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
       <c r="AC54" s="1"/>
-      <c r="AD54" s="1"/>
-      <c r="AI54" s="1"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:35">
+      <c r="AH54" s="1"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="1"/>
@@ -4725,72 +4626,72 @@
       <c r="R55" s="2"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1"/>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G58" s="2"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G59" s="2"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1"/>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G61" s="2"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
-      <c r="AH61" s="5"/>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:35">
+      <c r="AG61" s="5"/>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G62" s="2"/>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:35">
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="G63" s="2"/>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1"/>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G65" s="2"/>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G66" s="2"/>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G67" s="2"/>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G68" s="2"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
-      <c r="AH68" s="5"/>
+      <c r="AG68" s="5"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1"/>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G70" s="2"/>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G71" s="2"/>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1"/>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G73" s="2"/>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G74" s="2"/>
     </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G75" s="2"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
-      <c r="AH75" s="5"/>
+      <c r="AG75" s="5"/>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1"/>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G77" s="2"/>
     </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="L78" s="2"/>
@@ -4799,7 +4700,7 @@
       <c r="U78" s="2"/>
       <c r="V78" s="2"/>
     </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:34">
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:33">
       <c r="G79" s="2"/>
     </row>
   </sheetData>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -158,7 +158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0">
+    <comment ref="O3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -183,7 +183,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0">
+    <comment ref="P3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -205,7 +205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -227,7 +227,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0">
+    <comment ref="V3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -250,7 +250,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X3" authorId="0">
+    <comment ref="W3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -274,7 +274,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Y3" authorId="0">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -300,7 +300,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AG3" authorId="0">
+    <comment ref="AF3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="150">
   <si>
     <t>_ID</t>
   </si>
@@ -359,9 +359,6 @@
     <t>技能描述</t>
   </si>
   <si>
-    <t>Rate</t>
-  </si>
-  <si>
     <t>冷却时间</t>
   </si>
   <si>
@@ -524,7 +521,7 @@
     <t>基础心法</t>
   </si>
   <si>
-    <t>被动增加{0}%的物攻倍率和{1}点物攻，无需上阵</t>
+    <t>被动增加{0}%的物攻加成和{1}点物攻，无需上阵</t>
   </si>
   <si>
     <t>Self</t>
@@ -539,7 +536,7 @@
     <t>刺杀</t>
   </si>
   <si>
-    <t>对直线攻击距离内的敌人造成{0}%物攻+{1}点伤害</t>
+    <t>对直线攻击距离内的敌人造成{0}%物攻+{1}点技能伤害</t>
   </si>
   <si>
     <t>四方剑阵</t>
@@ -566,7 +563,7 @@
     <t>野蛮撞击</t>
   </si>
   <si>
-    <t>对目标敌人造成{0}%物攻+{1}点物攻伤害，并且晕眩{2}秒</t>
+    <t>对目标敌人造成{0}%物攻+{1}点技能伤害，并且晕眩{2}秒</t>
   </si>
   <si>
     <t>Chase</t>
@@ -617,7 +614,7 @@
     <t>冥想心法</t>
   </si>
   <si>
-    <t>被动增加{0}%的魔攻倍率和{1}点魔攻，无需上阵</t>
+    <t>被动增加{0}%的魔攻加成和{1}点魔攻，无需上阵</t>
   </si>
   <si>
     <t>Circle</t>
@@ -629,7 +626,7 @@
     <t>雷电术</t>
   </si>
   <si>
-    <t>对{3}个敌人造成{0}%魔法+{1}点伤害</t>
+    <t>对{3}个敌人造成{0}%魔法+{1}点技能伤害</t>
   </si>
   <si>
     <t>火海术</t>
@@ -647,7 +644,7 @@
     <t>抗拒火环</t>
   </si>
   <si>
-    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点伤害</t>
+    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点技能伤害</t>
   </si>
   <si>
     <t>"12,60,3,10"</t>
@@ -686,7 +683,7 @@
     <t>祈福心法</t>
   </si>
   <si>
-    <t>被动增加{0}%的道攻倍率和{1}点道攻，无需上阵</t>
+    <t>被动增加{0}%的道攻加成和{1}点道攻，无需上阵</t>
   </si>
   <si>
     <t>灭魔符</t>
@@ -695,7 +692,7 @@
     <t>火符术</t>
   </si>
   <si>
-    <t>对{3}个敌人造成{0}%道术+{1}点伤害</t>
+    <t>对{3}个敌人造成{0}%道术+{1}点技能伤害</t>
   </si>
   <si>
     <t>毒咒术</t>
@@ -704,7 +701,7 @@
     <t>施毒术</t>
   </si>
   <si>
-    <t>对{3}个敌人造成{0}%道术+{1}点的持续{2}秒伤害，按攻速结算</t>
+    <t>对{3}个敌人造成{0}%道术+{1}点技能伤害的持续{2}秒，按攻速结算</t>
   </si>
   <si>
     <t>"104,5,0,35"</t>
@@ -716,7 +713,7 @@
     <t>召唤骷髅</t>
   </si>
   <si>
-    <t>恢复自己和队友的{0}%道术生命+{1}点生命</t>
+    <t>恢复自己和队友的{0}%道术+{1}点生命</t>
   </si>
   <si>
     <t>护魂盾</t>
@@ -743,7 +740,7 @@
     <t>召唤神兽</t>
   </si>
   <si>
-    <t>召唤{3}只神兽战斗，攻击为{0}%道攻+{1}，其他全额继承</t>
+    <t>召唤{3}只神兽战斗，攻击为{0}%*道攻+{1}，其他全额继承</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -1760,7 +1757,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:AH79"/>
+  <dimension ref="C2:AG79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
@@ -1773,31 +1770,30 @@
     <col min="10" max="10" width="9.33333333333333" style="2" customWidth="1"/>
     <col min="11" max="11" width="5.25" style="2" customWidth="1"/>
     <col min="12" max="12" width="61.75" style="2" customWidth="1"/>
-    <col min="13" max="13" width="10.5083333333333" style="2" customWidth="1"/>
-    <col min="14" max="14" width="5.875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="6.50833333333333" style="2" customWidth="1"/>
-    <col min="16" max="16" width="8.375" style="2" customWidth="1"/>
-    <col min="17" max="17" width="7.16666666666667" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="19" max="20" width="7.875" style="2" customWidth="1"/>
-    <col min="21" max="21" width="8.66666666666667" style="2" customWidth="1"/>
-    <col min="22" max="22" width="9.5" style="2" customWidth="1"/>
-    <col min="23" max="23" width="7.375" style="2" customWidth="1"/>
-    <col min="24" max="24" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="25" max="25" width="8.25" style="2" customWidth="1"/>
-    <col min="26" max="28" width="7.625" style="2" customWidth="1"/>
-    <col min="29" max="29" width="9.625" style="2" customWidth="1"/>
-    <col min="30" max="31" width="7.875" style="2" customWidth="1"/>
-    <col min="32" max="32" width="9.75" style="2" customWidth="1"/>
-    <col min="33" max="33" width="21.75" style="2" customWidth="1"/>
-    <col min="34" max="34" width="11.75" style="2" customWidth="1"/>
-    <col min="35" max="16384" width="9" style="2"/>
+    <col min="13" max="13" width="5.875" style="2" customWidth="1"/>
+    <col min="14" max="14" width="6.50833333333333" style="2" customWidth="1"/>
+    <col min="15" max="15" width="8.375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="7.16666666666667" style="2" customWidth="1"/>
+    <col min="17" max="17" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="18" max="19" width="7.875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.66666666666667" style="2" customWidth="1"/>
+    <col min="21" max="21" width="9.5" style="2" customWidth="1"/>
+    <col min="22" max="22" width="7.375" style="2" customWidth="1"/>
+    <col min="23" max="23" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="24" max="24" width="8.25" style="2" customWidth="1"/>
+    <col min="25" max="27" width="7.625" style="2" customWidth="1"/>
+    <col min="28" max="28" width="9.625" style="2" customWidth="1"/>
+    <col min="29" max="30" width="7.875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="9.75" style="2" customWidth="1"/>
+    <col min="32" max="32" width="21.75" style="2" customWidth="1"/>
+    <col min="33" max="33" width="11.75" style="2" customWidth="1"/>
+    <col min="34" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" ht="33" customHeight="1" spans="3:34">
+    <row r="2" ht="33" customHeight="1" spans="3:33">
       <c r="L2" s="3"/>
     </row>
-    <row r="3" customHeight="1" spans="3:34">
+    <row r="3" customHeight="1" spans="3:33">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1853,7 +1849,7 @@
         <v>17</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V3" s="4" t="s">
         <v>18</v>
@@ -1891,43 +1887,40 @@
       <c r="AG3" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AH3" s="4" t="s">
+    </row>
+    <row r="4" customHeight="1" spans="3:33">
+      <c r="C4" s="4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:34">
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>31</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>39</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>40</v>
@@ -1989,109 +1982,103 @@
       <c r="AG4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AH4" s="4" t="s">
+    </row>
+    <row r="5" customHeight="1" spans="3:33">
+      <c r="C5" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:34">
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="H5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="M5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W5" s="4" t="s">
         <v>61</v>
       </c>
       <c r="X5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF5" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="Y5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AA5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AB5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AE5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="AF5" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="AG5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH5" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:34">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2102,7 +2089,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
@@ -2118,46 +2105,46 @@
         <v>10</v>
       </c>
       <c r="L6" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>10</v>
+      </c>
+      <c r="R6" s="1">
+        <v>1</v>
+      </c>
+      <c r="S6" s="1">
+        <v>100</v>
+      </c>
+      <c r="T6" s="1">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1">
+        <v>100</v>
+      </c>
+      <c r="V6" s="1">
+        <v>0</v>
+      </c>
+      <c r="W6" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>1</v>
-      </c>
-      <c r="R6" s="1">
-        <v>10</v>
-      </c>
-      <c r="S6" s="1">
-        <v>1</v>
-      </c>
-      <c r="T6" s="1">
-        <v>100</v>
-      </c>
-      <c r="U6" s="1">
-        <v>1</v>
-      </c>
-      <c r="V6" s="1">
-        <v>100</v>
-      </c>
-      <c r="W6" s="1">
-        <v>0</v>
       </c>
       <c r="X6" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y6" s="1" t="s">
-        <v>67</v>
+      <c r="Y6" s="1">
+        <v>0</v>
       </c>
       <c r="Z6" s="1">
         <v>0</v>
@@ -2177,14 +2164,11 @@
       <c r="AE6" s="1">
         <v>0</v>
       </c>
-      <c r="AF6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH6" s="1">
+      <c r="AG6" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2195,67 +2179,67 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="H7" s="1">
+        <v>1</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>10</v>
+      </c>
+      <c r="L7" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="H7" s="1">
-        <v>1</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>10</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="M7" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N7" s="1">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="1">
         <v>1</v>
       </c>
       <c r="Q7" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R7" s="1">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="S7" s="1">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="T7" s="1">
+        <v>10</v>
+      </c>
+      <c r="U7" s="1">
         <v>1000</v>
       </c>
-      <c r="U7" s="1">
-        <v>10</v>
-      </c>
       <c r="V7" s="1">
-        <v>1000</v>
-      </c>
-      <c r="W7" s="1">
         <v>2</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="X7" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y7" s="1" t="s">
-        <v>67</v>
+      <c r="Y7" s="1">
+        <v>2</v>
       </c>
       <c r="Z7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="1">
         <v>0</v>
@@ -2272,14 +2256,11 @@
       <c r="AE7" s="1">
         <v>0</v>
       </c>
-      <c r="AF7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH7" s="1">
+      <c r="AG7" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2290,73 +2271,73 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="H8" s="1">
+        <v>1</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>10</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="1">
-        <v>1</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>10</v>
-      </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="1">
+        <v>10</v>
+      </c>
+      <c r="N8" s="1">
+        <v>5</v>
+      </c>
+      <c r="O8" s="1">
+        <v>2</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>10</v>
+      </c>
+      <c r="R8" s="1">
+        <v>80</v>
+      </c>
+      <c r="S8" s="1">
+        <v>800</v>
+      </c>
+      <c r="T8" s="1">
+        <v>5</v>
+      </c>
+      <c r="U8" s="1">
+        <v>800</v>
+      </c>
+      <c r="V8" s="1">
+        <v>3</v>
+      </c>
+      <c r="W8" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
-        <v>10</v>
-      </c>
-      <c r="O8" s="1">
-        <v>5</v>
-      </c>
-      <c r="P8" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>1</v>
-      </c>
-      <c r="R8" s="1">
-        <v>10</v>
-      </c>
-      <c r="S8" s="1">
-        <v>80</v>
-      </c>
-      <c r="T8" s="1">
-        <v>800</v>
-      </c>
-      <c r="U8" s="1">
-        <v>5</v>
-      </c>
-      <c r="V8" s="1">
-        <v>800</v>
-      </c>
-      <c r="W8" s="1">
-        <v>3</v>
       </c>
       <c r="X8" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="Y8" s="1" t="s">
-        <v>75</v>
+      <c r="Y8" s="1">
+        <v>0</v>
       </c>
       <c r="Z8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA8" s="1">
         <v>3</v>
       </c>
       <c r="AB8" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC8" s="1">
         <v>0</v>
@@ -2367,17 +2348,14 @@
       <c r="AE8" s="1">
         <v>0</v>
       </c>
-      <c r="AF8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="AH8" s="1">
+      <c r="AF8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG8" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2388,10 +2366,10 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="H9" s="1">
         <v>7</v>
@@ -2406,76 +2384,73 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M9" s="1">
+        <v>8</v>
+      </c>
+      <c r="N9" s="1">
+        <v>2</v>
+      </c>
+      <c r="O9" s="1">
+        <v>1</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>10</v>
+      </c>
+      <c r="R9" s="1">
+        <v>150</v>
+      </c>
+      <c r="S9" s="1">
+        <v>2000</v>
+      </c>
+      <c r="T9" s="1">
+        <v>20</v>
+      </c>
+      <c r="U9" s="1">
+        <v>2000</v>
+      </c>
+      <c r="V9" s="1">
+        <v>4</v>
+      </c>
+      <c r="W9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>8</v>
-      </c>
-      <c r="O9" s="1">
-        <v>2</v>
-      </c>
-      <c r="P9" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>1</v>
-      </c>
-      <c r="R9" s="1">
-        <v>10</v>
-      </c>
-      <c r="S9" s="1">
-        <v>150</v>
-      </c>
-      <c r="T9" s="1">
-        <v>2000</v>
-      </c>
-      <c r="U9" s="1">
-        <v>20</v>
-      </c>
-      <c r="V9" s="1">
-        <v>2000</v>
-      </c>
-      <c r="W9" s="1">
-        <v>4</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y9" s="1" t="s">
+      <c r="Y9" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="Z9" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AH9" s="1">
+      <c r="AG9" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2486,10 +2461,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="H10" s="1">
         <v>5</v>
@@ -2504,76 +2479,73 @@
         <v>50</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M10" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N10" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="O10" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="P10" s="1">
         <v>1</v>
       </c>
       <c r="Q10" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R10" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="S10" s="1">
         <v>50</v>
       </c>
       <c r="T10" s="1">
+        <v>10</v>
+      </c>
+      <c r="U10" s="1">
         <v>50</v>
       </c>
-      <c r="U10" s="1">
-        <v>10</v>
-      </c>
       <c r="V10" s="1">
-        <v>50</v>
-      </c>
-      <c r="W10" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="Z10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH10" s="1">
+      <c r="AG10" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2584,10 +2556,10 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="H11" s="1">
         <v>6</v>
@@ -2602,46 +2574,46 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>10</v>
+      </c>
+      <c r="R11" s="1">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1">
+        <v>1</v>
+      </c>
+      <c r="U11" s="1">
+        <v>0</v>
+      </c>
+      <c r="V11" s="1">
+        <v>0</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X11" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>1</v>
-      </c>
-      <c r="R11" s="1">
-        <v>10</v>
-      </c>
-      <c r="S11" s="1">
-        <v>1</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
-      <c r="U11" s="1">
-        <v>1</v>
-      </c>
-      <c r="V11" s="1">
-        <v>0</v>
-      </c>
-      <c r="W11" s="1">
-        <v>0</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>90</v>
+      <c r="Y11" s="1">
+        <v>0</v>
       </c>
       <c r="Z11" s="1">
         <v>0</v>
@@ -2661,14 +2633,11 @@
       <c r="AE11" s="1">
         <v>0</v>
       </c>
-      <c r="AF11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="1">
+      <c r="AG11" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2679,67 +2648,67 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="1">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>10</v>
+      </c>
+      <c r="L12" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>10</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="M12" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N12" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12" s="1">
         <v>1</v>
       </c>
       <c r="Q12" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R12" s="1">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="S12" s="1">
-        <v>300</v>
+        <v>10000</v>
       </c>
       <c r="T12" s="1">
+        <v>50</v>
+      </c>
+      <c r="U12" s="1">
         <v>10000</v>
       </c>
-      <c r="U12" s="1">
-        <v>50</v>
-      </c>
       <c r="V12" s="1">
-        <v>10000</v>
-      </c>
-      <c r="W12" s="1">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="X12" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="Y12" s="1" t="s">
-        <v>67</v>
+      <c r="Y12" s="1">
+        <v>1</v>
       </c>
       <c r="Z12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12" s="1">
         <v>0</v>
@@ -2756,29 +2725,26 @@
       <c r="AE12" s="1">
         <v>0</v>
       </c>
-      <c r="AF12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="AH12" s="1">
+      <c r="AF12" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="AG12" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G13" s="2"/>
-      <c r="AG13" s="6"/>
+      <c r="AF13" s="6"/>
     </row>
     <row r="14" customFormat="1" customHeight="1"/>
     <row r="15" customFormat="1" customHeight="1"/>
     <row r="16" customFormat="1" customHeight="1"/>
     <row r="17" customFormat="1" customHeight="1"/>
     <row r="18" customFormat="1" customHeight="1"/>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G19" s="2"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C20" s="1">
         <v>2001</v>
       </c>
@@ -2789,7 +2755,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2805,73 +2771,70 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+      <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q20" s="1">
+        <v>10</v>
+      </c>
+      <c r="R20" s="1">
+        <v>1</v>
+      </c>
+      <c r="S20" s="1">
+        <v>100</v>
+      </c>
+      <c r="T20" s="1">
+        <v>1</v>
+      </c>
+      <c r="U20" s="1">
+        <v>100</v>
+      </c>
+      <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X20" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>2</v>
-      </c>
-      <c r="R20" s="1">
-        <v>10</v>
-      </c>
-      <c r="S20" s="1">
-        <v>1</v>
-      </c>
-      <c r="T20" s="1">
+      <c r="Y20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="1">
         <v>100</v>
       </c>
-      <c r="U20" s="1">
-        <v>1</v>
-      </c>
-      <c r="V20" s="1">
-        <v>100</v>
-      </c>
-      <c r="W20" s="1">
-        <v>0</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:34">
+    </row>
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C21" s="1">
         <v>2002</v>
       </c>
@@ -2882,91 +2845,88 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
+      <c r="I21" s="1">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>10</v>
+      </c>
+      <c r="L21" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="1">
-        <v>1</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>10</v>
-      </c>
-      <c r="L21" s="1" t="s">
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+      <c r="O21" s="1">
+        <v>1</v>
+      </c>
+      <c r="P21" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q21" s="1">
+        <v>10</v>
+      </c>
+      <c r="R21" s="1">
+        <v>120</v>
+      </c>
+      <c r="S21" s="1">
+        <v>1000</v>
+      </c>
+      <c r="T21" s="1">
+        <v>12</v>
+      </c>
+      <c r="U21" s="1">
+        <v>1000</v>
+      </c>
+      <c r="V21" s="1">
+        <v>3</v>
+      </c>
+      <c r="W21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X21" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="1">
         <v>100</v>
       </c>
-      <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>2</v>
-      </c>
-      <c r="R21" s="1">
-        <v>10</v>
-      </c>
-      <c r="S21" s="1">
-        <v>120</v>
-      </c>
-      <c r="T21" s="1">
-        <v>1000</v>
-      </c>
-      <c r="U21" s="1">
-        <v>12</v>
-      </c>
-      <c r="V21" s="1">
-        <v>1000</v>
-      </c>
-      <c r="W21" s="1">
-        <v>3</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z21" s="1">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:34">
+    </row>
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C22" s="1">
         <v>2003</v>
       </c>
@@ -2977,10 +2937,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="H22" s="1">
         <v>3</v>
@@ -2995,55 +2955,55 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="M22" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N22" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="O22" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P22" s="1">
         <v>2</v>
       </c>
       <c r="Q22" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R22" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="S22" s="1">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="T22" s="1">
+        <v>5</v>
+      </c>
+      <c r="U22" s="1">
         <v>800</v>
       </c>
-      <c r="U22" s="1">
-        <v>5</v>
-      </c>
       <c r="V22" s="1">
-        <v>800</v>
-      </c>
-      <c r="W22" s="1">
         <v>3</v>
       </c>
+      <c r="W22" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="X22" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y22" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>0</v>
       </c>
       <c r="Z22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA22" s="1">
         <v>3</v>
       </c>
       <c r="AB22" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC22" s="1">
         <v>0</v>
@@ -3054,14 +3014,11 @@
       <c r="AE22" s="1">
         <v>0</v>
       </c>
-      <c r="AF22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH22" s="1">
+      <c r="AG22" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C23" s="1">
         <v>2004</v>
       </c>
@@ -3072,26 +3029,26 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
+      <c r="I23" s="1">
+        <v>0</v>
+      </c>
+      <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
+        <v>10</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="H23" s="1">
-        <v>1</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
-        <v>10</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="M23" s="1">
         <v>0</v>
       </c>
@@ -3099,46 +3056,46 @@
         <v>0</v>
       </c>
       <c r="O23" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P23" s="1">
         <v>2</v>
       </c>
       <c r="Q23" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R23" s="1">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="S23" s="1">
-        <v>120</v>
+        <v>2000</v>
       </c>
       <c r="T23" s="1">
+        <v>10</v>
+      </c>
+      <c r="U23" s="1">
         <v>2000</v>
       </c>
-      <c r="U23" s="1">
-        <v>10</v>
-      </c>
       <c r="V23" s="1">
-        <v>2000</v>
-      </c>
-      <c r="W23" s="1">
         <v>4</v>
       </c>
+      <c r="W23" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="X23" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>0</v>
       </c>
       <c r="Z23" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA23" s="1">
         <v>3</v>
       </c>
       <c r="AB23" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC23" s="1">
         <v>0</v>
@@ -3149,17 +3106,14 @@
       <c r="AE23" s="1">
         <v>0</v>
       </c>
-      <c r="AF23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG23" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="AH23" s="1">
+      <c r="AF23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG23" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C24" s="1">
         <v>2005</v>
       </c>
@@ -3170,10 +3124,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="H24" s="1">
         <v>5</v>
@@ -3188,76 +3142,73 @@
         <v>50</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M24" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N24" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="O24" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="P24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q24" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R24" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="S24" s="1">
         <v>50</v>
       </c>
       <c r="T24" s="1">
+        <v>10</v>
+      </c>
+      <c r="U24" s="1">
         <v>50</v>
       </c>
-      <c r="U24" s="1">
-        <v>10</v>
-      </c>
       <c r="V24" s="1">
-        <v>50</v>
-      </c>
-      <c r="W24" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="Z24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG24" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH24" s="1">
+      <c r="AG24" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C25" s="1">
         <v>2006</v>
       </c>
@@ -3268,10 +3219,10 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="H25" s="1">
         <v>6</v>
@@ -3286,7 +3237,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
@@ -3298,34 +3249,34 @@
         <v>0</v>
       </c>
       <c r="P25" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q25" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R25" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
       </c>
-      <c r="W25" s="1">
-        <v>0</v>
+      <c r="W25" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y25" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="Y25" s="1">
+        <v>0</v>
       </c>
       <c r="Z25" s="1">
         <v>0</v>
@@ -3345,14 +3296,11 @@
       <c r="AE25" s="1">
         <v>0</v>
       </c>
-      <c r="AF25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH25" s="1">
+      <c r="AG25" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C26" s="1">
         <v>2007</v>
       </c>
@@ -3363,73 +3311,73 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
+      <c r="I26" s="1">
+        <v>0</v>
+      </c>
+      <c r="J26" s="1">
+        <v>0</v>
+      </c>
+      <c r="K26" s="1">
+        <v>10</v>
+      </c>
+      <c r="L26" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0</v>
-      </c>
-      <c r="K26" s="1">
-        <v>10</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="M26" s="1">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="N26" s="1">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O26" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P26" s="1">
         <v>2</v>
       </c>
       <c r="Q26" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="R26" s="1">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="S26" s="1">
-        <v>150</v>
+        <v>5000</v>
       </c>
       <c r="T26" s="1">
+        <v>30</v>
+      </c>
+      <c r="U26" s="1">
         <v>5000</v>
       </c>
-      <c r="U26" s="1">
-        <v>30</v>
-      </c>
       <c r="V26" s="1">
-        <v>5000</v>
-      </c>
-      <c r="W26" s="1">
         <v>5</v>
       </c>
+      <c r="W26" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="X26" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="Y26" s="1">
+        <v>0</v>
       </c>
       <c r="Z26" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA26" s="1">
         <v>3</v>
       </c>
       <c r="AB26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC26" s="1">
         <v>0</v>
@@ -3440,27 +3388,24 @@
       <c r="AE26" s="1">
         <v>0</v>
       </c>
-      <c r="AF26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG26" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="AH26" s="1">
+      <c r="AF26" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="AG26" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G27" s="2"/>
-      <c r="AG27" s="6"/>
-    </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="AF27" s="6"/>
+    </row>
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G28" s="2"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G30" s="2"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -3468,7 +3413,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G31" s="2"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -3476,13 +3421,13 @@
       <c r="K31" s="1"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="L32" s="2"/>
     </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G33" s="2"/>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C34" s="1">
         <v>3001</v>
       </c>
@@ -3493,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
@@ -3509,73 +3454,70 @@
         <v>20</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M34" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N34" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
       </c>
       <c r="P34" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q34" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R34" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S34" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="T34" s="1">
+        <v>1</v>
+      </c>
+      <c r="U34" s="1">
         <v>100</v>
       </c>
-      <c r="U34" s="1">
-        <v>1</v>
-      </c>
       <c r="V34" s="1">
+        <v>0</v>
+      </c>
+      <c r="W34" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="1">
         <v>100</v>
       </c>
-      <c r="W34" s="1">
-        <v>0</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y34" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH34" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:34">
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C35" s="1">
         <v>3002</v>
       </c>
@@ -3586,26 +3528,26 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="H35" s="1">
+        <v>1</v>
+      </c>
+      <c r="I35" s="1">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>10</v>
+      </c>
+      <c r="L35" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="H35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1">
-        <v>10</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>122</v>
-      </c>
       <c r="M35" s="1">
         <v>0</v>
       </c>
@@ -3613,40 +3555,40 @@
         <v>0</v>
       </c>
       <c r="O35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P35" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q35" s="1">
+        <v>10</v>
+      </c>
+      <c r="R35" s="1">
+        <v>120</v>
+      </c>
+      <c r="S35" s="1">
+        <v>1000</v>
+      </c>
+      <c r="T35" s="1">
+        <v>10</v>
+      </c>
+      <c r="U35" s="1">
+        <v>1000</v>
+      </c>
+      <c r="V35" s="1">
         <v>3</v>
       </c>
-      <c r="R35" s="1">
-        <v>10</v>
-      </c>
-      <c r="S35" s="1">
-        <v>120</v>
-      </c>
-      <c r="T35" s="1">
-        <v>1000</v>
-      </c>
-      <c r="U35" s="1">
-        <v>10</v>
-      </c>
-      <c r="V35" s="1">
-        <v>1000</v>
-      </c>
-      <c r="W35" s="1">
-        <v>3</v>
+      <c r="W35" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y35" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="Y35" s="1">
+        <v>1</v>
       </c>
       <c r="Z35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="1">
         <v>0</v>
@@ -3663,14 +3605,11 @@
       <c r="AE35" s="1">
         <v>0</v>
       </c>
-      <c r="AF35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH35" s="1">
+      <c r="AG35" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C36" s="1">
         <v>3003</v>
       </c>
@@ -3681,94 +3620,91 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="H36" s="1">
+        <v>1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>0</v>
+      </c>
+      <c r="J36" s="1">
+        <v>0</v>
+      </c>
+      <c r="K36" s="1">
+        <v>10</v>
+      </c>
+      <c r="L36" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="H36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1">
-        <v>0</v>
-      </c>
-      <c r="K36" s="1">
-        <v>10</v>
-      </c>
-      <c r="L36" s="1" t="s">
+      <c r="M36" s="1">
+        <v>10</v>
+      </c>
+      <c r="N36" s="1">
+        <v>5</v>
+      </c>
+      <c r="O36" s="1">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>10</v>
+      </c>
+      <c r="R36" s="1">
+        <v>80</v>
+      </c>
+      <c r="S36" s="1">
+        <v>800</v>
+      </c>
+      <c r="T36" s="1">
+        <v>5</v>
+      </c>
+      <c r="U36" s="1">
+        <v>800</v>
+      </c>
+      <c r="V36" s="1">
+        <v>4</v>
+      </c>
+      <c r="W36" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y36" s="1">
+        <v>3</v>
+      </c>
+      <c r="Z36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="M36" s="1">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1">
-        <v>10</v>
-      </c>
-      <c r="O36" s="1">
-        <v>5</v>
-      </c>
-      <c r="P36" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q36" s="1">
-        <v>3</v>
-      </c>
-      <c r="R36" s="1">
-        <v>10</v>
-      </c>
-      <c r="S36" s="1">
-        <v>80</v>
-      </c>
-      <c r="T36" s="1">
-        <v>800</v>
-      </c>
-      <c r="U36" s="1">
-        <v>5</v>
-      </c>
-      <c r="V36" s="1">
-        <v>800</v>
-      </c>
-      <c r="W36" s="1">
-        <v>4</v>
-      </c>
-      <c r="X36" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y36" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="Z36" s="1">
-        <v>5</v>
-      </c>
-      <c r="AA36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG36" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="AH36" s="1">
+      <c r="AG36" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C37" s="1">
         <v>3004</v>
       </c>
@@ -3779,10 +3715,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="H37" s="1">
         <v>2</v>
@@ -3797,49 +3733,49 @@
         <v>100</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M37" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N37" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O37" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q37" s="1">
+        <v>10</v>
+      </c>
+      <c r="R37" s="1">
+        <v>1000</v>
+      </c>
+      <c r="S37" s="1">
+        <v>100000</v>
+      </c>
+      <c r="T37" s="1">
+        <v>1000</v>
+      </c>
+      <c r="U37" s="1">
+        <v>100000</v>
+      </c>
+      <c r="V37" s="1">
+        <v>5</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X37" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y37" s="1">
         <v>3</v>
       </c>
-      <c r="R37" s="1">
-        <v>10</v>
-      </c>
-      <c r="S37" s="1">
-        <v>1000</v>
-      </c>
-      <c r="T37" s="1">
-        <v>100000</v>
-      </c>
-      <c r="U37" s="1">
-        <v>1000</v>
-      </c>
-      <c r="V37" s="1">
-        <v>100000</v>
-      </c>
-      <c r="W37" s="1">
-        <v>5</v>
-      </c>
-      <c r="X37" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y37" s="1" t="s">
-        <v>90</v>
-      </c>
       <c r="Z37" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="1">
         <v>0</v>
@@ -3856,14 +3792,11 @@
       <c r="AE37" s="1">
         <v>0</v>
       </c>
-      <c r="AF37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="1">
+      <c r="AG37" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C38" s="1">
         <v>3005</v>
       </c>
@@ -3874,10 +3807,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="H38" s="1">
         <v>5</v>
@@ -3892,76 +3825,73 @@
         <v>50</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M38" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N38" s="1">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="O38" s="1">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="P38" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q38" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R38" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="S38" s="1">
         <v>50</v>
       </c>
       <c r="T38" s="1">
+        <v>10</v>
+      </c>
+      <c r="U38" s="1">
         <v>50</v>
       </c>
-      <c r="U38" s="1">
-        <v>10</v>
-      </c>
       <c r="V38" s="1">
-        <v>50</v>
-      </c>
-      <c r="W38" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W38" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y38" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="Z38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG38" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="AH38" s="1">
+      <c r="AG38" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C39" s="1">
         <v>3006</v>
       </c>
@@ -3972,10 +3902,10 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="H39" s="1">
         <v>6</v>
@@ -3990,7 +3920,7 @@
         <v>10</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
@@ -4002,34 +3932,34 @@
         <v>0</v>
       </c>
       <c r="P39" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q39" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R39" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
       </c>
-      <c r="W39" s="1">
-        <v>0</v>
+      <c r="W39" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y39" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>0</v>
       </c>
       <c r="Z39" s="1">
         <v>0</v>
@@ -4049,14 +3979,11 @@
       <c r="AE39" s="1">
         <v>0</v>
       </c>
-      <c r="AF39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH39" s="1">
+      <c r="AG39" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C40" s="1">
         <v>3007</v>
       </c>
@@ -4067,10 +3994,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>137</v>
       </c>
       <c r="H40" s="1">
         <v>2</v>
@@ -4085,49 +4012,49 @@
         <v>100</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M40" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="N40" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q40" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="R40" s="1">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="S40" s="1">
-        <v>200</v>
+        <v>8000</v>
       </c>
       <c r="T40" s="1">
+        <v>40</v>
+      </c>
+      <c r="U40" s="1">
         <v>8000</v>
       </c>
-      <c r="U40" s="1">
-        <v>40</v>
-      </c>
       <c r="V40" s="1">
-        <v>8000</v>
-      </c>
-      <c r="W40" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="W40" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y40" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="Y40" s="1">
+        <v>2</v>
       </c>
       <c r="Z40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA40" s="1">
         <v>0</v>
@@ -4144,23 +4071,20 @@
       <c r="AE40" s="1">
         <v>0</v>
       </c>
-      <c r="AF40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="1">
+      <c r="AG40" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G41" s="2"/>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G42" s="2"/>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G43" s="2"/>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C44" s="1">
         <v>4001</v>
       </c>
@@ -4171,10 +4095,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="H44" s="1">
         <v>4001</v>
@@ -4189,76 +4113,73 @@
         <v>-100</v>
       </c>
       <c r="L44" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="M44" s="1">
+        <v>30</v>
+      </c>
+      <c r="N44" s="1">
+        <v>2</v>
+      </c>
+      <c r="O44" s="1">
+        <v>0</v>
+      </c>
+      <c r="P44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>0</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1">
-        <v>30</v>
-      </c>
-      <c r="O44" s="1">
-        <v>2</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1">
-        <v>0</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
-      </c>
-      <c r="W44" s="1">
-        <v>0</v>
-      </c>
-      <c r="X44" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y44" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG44" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AH44" s="1">
+      <c r="AG44" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C45" s="1">
         <v>4002</v>
       </c>
@@ -4269,10 +4190,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="H45" s="1">
         <v>4002</v>
@@ -4287,13 +4208,13 @@
         <v>200</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="M45" s="1">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="N45" s="1">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -4305,28 +4226,28 @@
         <v>0</v>
       </c>
       <c r="R45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T45" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U45" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V45" s="1">
         <v>0</v>
       </c>
-      <c r="W45" s="1">
-        <v>0</v>
+      <c r="W45" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y45" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
+      </c>
+      <c r="Y45" s="1">
+        <v>0</v>
       </c>
       <c r="Z45" s="1">
         <v>0</v>
@@ -4346,15 +4267,12 @@
       <c r="AE45" s="1">
         <v>0</v>
       </c>
-      <c r="AF45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="5"/>
-      <c r="AH45" s="1">
+      <c r="AF45" s="5"/>
+      <c r="AG45" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C46" s="1">
         <v>4003</v>
       </c>
@@ -4365,10 +4283,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="H46" s="1">
         <v>4003</v>
@@ -4383,83 +4301,80 @@
         <v>-1</v>
       </c>
       <c r="L46" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="M46" s="1">
+        <v>60</v>
+      </c>
+      <c r="N46" s="1">
+        <v>0</v>
+      </c>
+      <c r="O46" s="1">
+        <v>0</v>
+      </c>
+      <c r="P46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>100</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
+        <v>0</v>
+      </c>
+      <c r="U46" s="1">
+        <v>0</v>
+      </c>
+      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="X46" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="Y46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="M46" s="1">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1">
-        <v>60</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>100</v>
-      </c>
-      <c r="T46" s="1">
-        <v>0</v>
-      </c>
-      <c r="U46" s="1">
-        <v>0</v>
-      </c>
-      <c r="V46" s="1">
-        <v>0</v>
-      </c>
-      <c r="W46" s="1">
-        <v>0</v>
-      </c>
-      <c r="X46" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y46" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG46" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AH46" s="1">
+      <c r="AG46" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G47" s="2"/>
     </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C49" s="1">
         <v>9001</v>
       </c>
@@ -4470,10 +4385,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H49" s="1">
         <v>9</v>
@@ -4494,37 +4409,37 @@
         <v>0</v>
       </c>
       <c r="O49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49" s="1">
         <v>0</v>
       </c>
       <c r="R49" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="T49" s="1">
         <v>0</v>
       </c>
-      <c r="U49" s="1">
-        <v>0</v>
-      </c>
-      <c r="W49" s="1">
-        <v>1</v>
+      <c r="V49" s="1">
+        <v>1</v>
+      </c>
+      <c r="W49" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="X49" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y49" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
+      </c>
+      <c r="Y49" s="1">
+        <v>1</v>
       </c>
       <c r="Z49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA49" s="1">
         <v>0</v>
@@ -4541,30 +4456,27 @@
       <c r="AE49" s="1">
         <v>0</v>
       </c>
-      <c r="AF49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AH49" s="1">
+      <c r="AG49" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1"/>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G51" s="2"/>
     </row>
-    <row r="52" customHeight="1" spans="3:34">
+    <row r="52" customHeight="1" spans="3:33">
       <c r="E52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-      <c r="M52" s="1"/>
+      <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
-      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
       <c r="T52" s="1"/>
       <c r="U52" s="1"/>
-      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
       <c r="X52" s="1"/>
-      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
@@ -4572,13 +4484,12 @@
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
       <c r="AG52" s="1"/>
-      <c r="AH52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="3:34">
+    </row>
+    <row r="53" customHeight="1" spans="3:33">
       <c r="E53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="M53" s="1"/>
+      <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
@@ -4598,22 +4509,20 @@
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
       <c r="AG53" s="1"/>
-      <c r="AH53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="3:34">
+    </row>
+    <row r="54" customHeight="1" spans="3:33">
       <c r="E54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="P54" s="1"/>
+      <c r="O54" s="1"/>
+      <c r="T54" s="1"/>
       <c r="U54" s="1"/>
-      <c r="V54" s="1"/>
+      <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
-      <c r="AC54" s="1"/>
-      <c r="AH54" s="1"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="AG54" s="1"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="1"/>
@@ -4622,90 +4531,88 @@
       <c r="K55" s="1"/>
       <c r="L55" s="2"/>
       <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="R55" s="2"/>
+      <c r="Q55" s="2"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1"/>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G58" s="2"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G59" s="2"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1"/>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G61" s="2"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
-      <c r="AG61" s="5"/>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="AF61" s="5"/>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G62" s="2"/>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G63" s="2"/>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1"/>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G65" s="2"/>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G66" s="2"/>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G67" s="2"/>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G68" s="2"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
-      <c r="AG68" s="5"/>
+      <c r="AF68" s="5"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1"/>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G70" s="2"/>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G71" s="2"/>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1"/>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G73" s="2"/>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G74" s="2"/>
     </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G75" s="2"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
-      <c r="AG75" s="5"/>
+      <c r="AF75" s="5"/>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1"/>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G77" s="2"/>
     </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:33">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="R78" s="2"/>
+      <c r="Q78" s="2"/>
+      <c r="T78" s="2"/>
       <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:33">
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G79" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="141">
   <si>
     <t>_ID</t>
   </si>
@@ -554,9 +554,6 @@
     <t>Arc</t>
   </si>
   <si>
-    <t>"14,60,3,10"</t>
-  </si>
-  <si>
     <t>重击剑术</t>
   </si>
   <si>
@@ -569,9 +566,6 @@
     <t>Chase</t>
   </si>
   <si>
-    <t>"306,2,0,0"</t>
-  </si>
-  <si>
     <t>武神盾</t>
   </si>
   <si>
@@ -584,9 +578,6 @@
     <t>Square</t>
   </si>
   <si>
-    <t>"14,0,0,10","4,0,0,0","5,0,0,0"</t>
-  </si>
-  <si>
     <t>无求易决</t>
   </si>
   <si>
@@ -608,9 +599,6 @@
     <t>对单个敌人造成{0}%物攻+{1}点伤害，降低敌人一半的防御和减伤</t>
   </si>
   <si>
-    <t>"103,4,0,25","101,0,0,10"</t>
-  </si>
-  <si>
     <t>冥想心法</t>
   </si>
   <si>
@@ -647,9 +635,6 @@
     <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点技能伤害</t>
   </si>
   <si>
-    <t>"12,60,3,10"</t>
-  </si>
-  <si>
     <t>念力盾</t>
   </si>
   <si>
@@ -677,9 +662,6 @@
     <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点伤害，冰封所有敌人2秒</t>
   </si>
   <si>
-    <t>"305,1,1,0"</t>
-  </si>
-  <si>
     <t>祈福心法</t>
   </si>
   <si>
@@ -704,9 +686,6 @@
     <t>对{3}个敌人造成{0}%道术+{1}点技能伤害的持续{2}秒，按攻速结算</t>
   </si>
   <si>
-    <t>"104,5,0,35"</t>
-  </si>
-  <si>
     <t>疗伤术</t>
   </si>
   <si>
@@ -752,9 +731,6 @@
     <t>麻痹敌人{2}S，CD30S</t>
   </si>
   <si>
-    <t>"307,2,0,0"</t>
-  </si>
-  <si>
     <t>神盾指环</t>
   </si>
   <si>
@@ -771,9 +747,6 @@
   </si>
   <si>
     <t>复活自己并且免疫2S所有伤害，CD60S</t>
-  </si>
-  <si>
-    <t>"18,3,0,100"</t>
   </si>
   <si>
     <t>普攻</t>
@@ -966,7 +939,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -976,12 +949,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1302,7 +1269,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1326,16 +1293,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1344,89 +1311,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1437,7 +1404,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2348,9 +2314,7 @@
       <c r="AE8" s="1">
         <v>0</v>
       </c>
-      <c r="AF8" s="1" t="s">
-        <v>75</v>
-      </c>
+      <c r="AF8" s="1"/>
       <c r="AG8" s="1">
         <v>100</v>
       </c>
@@ -2366,10 +2330,10 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="H9" s="1">
         <v>7</v>
@@ -2384,7 +2348,7 @@
         <v>10</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M9" s="1">
         <v>8</v>
@@ -2420,7 +2384,7 @@
         <v>73</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Y9" s="1">
         <v>1</v>
@@ -2443,9 +2407,7 @@
       <c r="AE9" s="1">
         <v>0</v>
       </c>
-      <c r="AF9" s="1" t="s">
-        <v>80</v>
-      </c>
+      <c r="AF9" s="1"/>
       <c r="AG9" s="1">
         <v>100</v>
       </c>
@@ -2461,10 +2423,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H10" s="1">
         <v>5</v>
@@ -2479,7 +2441,7 @@
         <v>50</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="M10" s="1">
         <v>60</v>
@@ -2515,7 +2477,7 @@
         <v>65</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y10" s="1">
         <v>0</v>
@@ -2538,9 +2500,7 @@
       <c r="AE10" s="1">
         <v>0</v>
       </c>
-      <c r="AF10" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="AF10" s="1"/>
       <c r="AG10" s="1">
         <v>100</v>
       </c>
@@ -2556,10 +2516,10 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H11" s="1">
         <v>6</v>
@@ -2574,7 +2534,7 @@
         <v>10</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M11" s="1">
         <v>0</v>
@@ -2610,7 +2570,7 @@
         <v>65</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
@@ -2648,10 +2608,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="H12" s="1">
         <v>1</v>
@@ -2666,7 +2626,7 @@
         <v>10</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1">
         <v>10</v>
@@ -2725,22 +2685,29 @@
       <c r="AE12" s="1">
         <v>0</v>
       </c>
-      <c r="AF12" s="6" t="s">
-        <v>93</v>
-      </c>
+      <c r="AF12" s="1"/>
       <c r="AG12" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G13" s="2"/>
-      <c r="AF13" s="6"/>
-    </row>
-    <row r="14" customFormat="1" customHeight="1"/>
-    <row r="15" customFormat="1" customHeight="1"/>
-    <row r="16" customFormat="1" customHeight="1"/>
-    <row r="17" customFormat="1" customHeight="1"/>
-    <row r="18" customFormat="1" customHeight="1"/>
+    </row>
+    <row r="14" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF14" s="1"/>
+    </row>
+    <row r="15" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF15" s="1"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF16" s="1"/>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF17" s="1"/>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF18" s="1"/>
+    </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G19" s="2"/>
     </row>
@@ -2755,7 +2722,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2771,7 +2738,7 @@
         <v>10</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M20" s="1">
         <v>0</v>
@@ -2807,7 +2774,7 @@
         <v>65</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y20" s="1">
         <v>0</v>
@@ -2845,10 +2812,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H21" s="1">
         <v>1</v>
@@ -2863,7 +2830,7 @@
         <v>10</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="M21" s="1">
         <v>0</v>
@@ -2899,7 +2866,7 @@
         <v>73</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y21" s="1">
         <v>1</v>
@@ -2937,10 +2904,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H22" s="1">
         <v>3</v>
@@ -2955,7 +2922,7 @@
         <v>10</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="M22" s="1">
         <v>10</v>
@@ -2991,7 +2958,7 @@
         <v>73</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y22" s="1">
         <v>0</v>
@@ -3029,10 +2996,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="H23" s="1">
         <v>1</v>
@@ -3047,7 +3014,7 @@
         <v>10</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="M23" s="1">
         <v>0</v>
@@ -3083,7 +3050,7 @@
         <v>73</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y23" s="1">
         <v>0</v>
@@ -3106,9 +3073,7 @@
       <c r="AE23" s="1">
         <v>0</v>
       </c>
-      <c r="AF23" s="1" t="s">
-        <v>106</v>
-      </c>
+      <c r="AF23" s="1"/>
       <c r="AG23" s="1">
         <v>100</v>
       </c>
@@ -3124,10 +3089,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H24" s="1">
         <v>5</v>
@@ -3142,7 +3107,7 @@
         <v>50</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="M24" s="1">
         <v>60</v>
@@ -3178,7 +3143,7 @@
         <v>65</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -3201,9 +3166,7 @@
       <c r="AE24" s="1">
         <v>0</v>
       </c>
-      <c r="AF24" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="AF24" s="1"/>
       <c r="AG24" s="1">
         <v>100</v>
       </c>
@@ -3219,10 +3182,10 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="H25" s="1">
         <v>6</v>
@@ -3237,7 +3200,7 @@
         <v>10</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="M25" s="1">
         <v>0</v>
@@ -3273,7 +3236,7 @@
         <v>65</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Y25" s="1">
         <v>0</v>
@@ -3311,10 +3274,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H26" s="1">
         <v>1</v>
@@ -3329,7 +3292,7 @@
         <v>10</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="M26" s="1">
         <v>15</v>
@@ -3365,7 +3328,7 @@
         <v>73</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y26" s="1">
         <v>0</v>
@@ -3388,16 +3351,13 @@
       <c r="AE26" s="1">
         <v>0</v>
       </c>
-      <c r="AF26" s="6" t="s">
-        <v>116</v>
-      </c>
+      <c r="AF26" s="1"/>
       <c r="AG26" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G27" s="2"/>
-      <c r="AF27" s="6"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G28" s="2"/>
@@ -3438,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
@@ -3454,7 +3414,7 @@
         <v>20</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="M34" s="1">
         <v>4</v>
@@ -3490,7 +3450,7 @@
         <v>65</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y34" s="1">
         <v>0</v>
@@ -3528,10 +3488,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="H35" s="1">
         <v>1</v>
@@ -3546,7 +3506,7 @@
         <v>10</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="M35" s="1">
         <v>0</v>
@@ -3582,7 +3542,7 @@
         <v>73</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y35" s="1">
         <v>1</v>
@@ -3620,10 +3580,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="H36" s="1">
         <v>1</v>
@@ -3638,7 +3598,7 @@
         <v>10</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="M36" s="1">
         <v>10</v>
@@ -3674,7 +3634,7 @@
         <v>73</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y36" s="1">
         <v>3</v>
@@ -3697,9 +3657,7 @@
       <c r="AE36" s="1">
         <v>0</v>
       </c>
-      <c r="AF36" s="1" t="s">
-        <v>125</v>
-      </c>
+      <c r="AF36" s="1"/>
       <c r="AG36" s="1">
         <v>100</v>
       </c>
@@ -3715,10 +3673,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="H37" s="1">
         <v>2</v>
@@ -3733,7 +3691,7 @@
         <v>100</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="M37" s="1">
         <v>10</v>
@@ -3769,7 +3727,7 @@
         <v>65</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Y37" s="1">
         <v>3</v>
@@ -3807,10 +3765,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="H38" s="1">
         <v>5</v>
@@ -3825,7 +3783,7 @@
         <v>50</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="M38" s="1">
         <v>60</v>
@@ -3861,7 +3819,7 @@
         <v>65</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y38" s="1">
         <v>0</v>
@@ -3884,9 +3842,7 @@
       <c r="AE38" s="1">
         <v>0</v>
       </c>
-      <c r="AF38" s="5" t="s">
-        <v>85</v>
-      </c>
+      <c r="AF38" s="5"/>
       <c r="AG38" s="1">
         <v>100</v>
       </c>
@@ -3902,10 +3858,10 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="H39" s="1">
         <v>6</v>
@@ -3920,7 +3876,7 @@
         <v>10</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="M39" s="1">
         <v>0</v>
@@ -3956,7 +3912,7 @@
         <v>65</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="Y39" s="1">
         <v>0</v>
@@ -3994,10 +3950,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="H40" s="1">
         <v>2</v>
@@ -4012,7 +3968,7 @@
         <v>100</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="M40" s="1">
         <v>30</v>
@@ -4048,7 +4004,7 @@
         <v>73</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y40" s="1">
         <v>2</v>
@@ -4095,10 +4051,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="H44" s="1">
         <v>4001</v>
@@ -4113,7 +4069,7 @@
         <v>-100</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="M44" s="1">
         <v>30</v>
@@ -4149,7 +4105,7 @@
         <v>65</v>
       </c>
       <c r="X44" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y44" s="1">
         <v>0</v>
@@ -4172,9 +4128,7 @@
       <c r="AE44" s="1">
         <v>0</v>
       </c>
-      <c r="AF44" s="1" t="s">
-        <v>141</v>
-      </c>
+      <c r="AF44" s="1"/>
       <c r="AG44" s="1">
         <v>99999</v>
       </c>
@@ -4190,10 +4144,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="H45" s="1">
         <v>4002</v>
@@ -4208,7 +4162,7 @@
         <v>200</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="M45" s="1">
         <v>60</v>
@@ -4244,7 +4198,7 @@
         <v>65</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y45" s="1">
         <v>0</v>
@@ -4283,10 +4237,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="H46" s="1">
         <v>4003</v>
@@ -4301,7 +4255,7 @@
         <v>-1</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="M46" s="1">
         <v>60</v>
@@ -4337,7 +4291,7 @@
         <v>65</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Y46" s="1">
         <v>0</v>
@@ -4360,9 +4314,7 @@
       <c r="AE46" s="1">
         <v>0</v>
       </c>
-      <c r="AF46" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="AF46" s="1"/>
       <c r="AG46" s="1">
         <v>99999</v>
       </c>
@@ -4385,10 +4337,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="H49" s="1">
         <v>9</v>
@@ -4433,7 +4385,7 @@
         <v>65</v>
       </c>
       <c r="X49" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="Y49" s="1">
         <v>1</v>
@@ -4612,7 +4564,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="M3:M5 C3:L5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -3417,7 +3417,7 @@
         <v>112</v>
       </c>
       <c r="M34" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N34" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -572,7 +572,7 @@
     <t>武力盾</t>
   </si>
   <si>
-    <t>提高人物{0}防御和{1}生命，持续{2}秒</t>
+    <t>提高人物{0}防御，并且生成一个{1}%生命的护盾，持续{2}秒</t>
   </si>
   <si>
     <t>Square</t>
@@ -641,7 +641,7 @@
     <t>魔法盾</t>
   </si>
   <si>
-    <t>提高人物{0}魔攻和{1}生命，持续{2}秒</t>
+    <t>提高人物{0}魔攻，并且生成一个{1}%生命的护盾，持续{2}秒</t>
   </si>
   <si>
     <t>冰心诀</t>
@@ -701,7 +701,7 @@
     <t>道力盾</t>
   </si>
   <si>
-    <t>提高人物{0}减伤和{1}生命，持续{2}秒</t>
+    <t>提高人物{0}生命，并且生成一个{1}%生命的护盾，持续{2}秒</t>
   </si>
   <si>
     <t>圣心诀</t>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -176,36 +176,11 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0 被动
-1 单体（施毒术属于单体）
-2 范围
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="P3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
 1</t>
         </r>
       </text>
     </comment>
-    <comment ref="R3" authorId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -227,7 +202,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
+    <comment ref="U3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -247,6 +222,31 @@
           <t xml:space="preserve">
 0 以自己为圆心
 1 距离1格</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0 被动
+1 单体（施毒术属于单体）
+2 范围
+</t>
         </r>
       </text>
     </comment>
@@ -365,27 +365,27 @@
     <t>持续时间</t>
   </si>
   <si>
+    <t>职业</t>
+  </si>
+  <si>
+    <t>最大等级</t>
+  </si>
+  <si>
+    <t>伤害比例</t>
+  </si>
+  <si>
+    <t>固定伤害</t>
+  </si>
+  <si>
+    <t>等级成长</t>
+  </si>
+  <si>
+    <t>攻击距离</t>
+  </si>
+  <si>
     <t>施法类型</t>
   </si>
   <si>
-    <t>职业</t>
-  </si>
-  <si>
-    <t>最大等级</t>
-  </si>
-  <si>
-    <t>伤害比例</t>
-  </si>
-  <si>
-    <t>固定伤害</t>
-  </si>
-  <si>
-    <t>等级成长</t>
-  </si>
-  <si>
-    <t>攻击距离</t>
-  </si>
-  <si>
     <t>中心目标</t>
   </si>
   <si>
@@ -452,30 +452,30 @@
     <t>Duration</t>
   </si>
   <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>MaxLevel</t>
+  </si>
+  <si>
+    <t>Percent</t>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>LevelPercent</t>
+  </si>
+  <si>
+    <t>LevelDamage</t>
+  </si>
+  <si>
+    <t>Dis</t>
+  </si>
+  <si>
     <t>CastType</t>
   </si>
   <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>MaxLevel</t>
-  </si>
-  <si>
-    <t>Percent</t>
-  </si>
-  <si>
-    <t>Damage</t>
-  </si>
-  <si>
-    <t>LevelPercent</t>
-  </si>
-  <si>
-    <t>LevelDamage</t>
-  </si>
-  <si>
-    <t>Dis</t>
-  </si>
-  <si>
     <t>Center</t>
   </si>
   <si>
@@ -689,7 +689,7 @@
     <t>疗伤术</t>
   </si>
   <si>
-    <t>召唤骷髅</t>
+    <t>治疗术</t>
   </si>
   <si>
     <t>恢复自己和队友的{0}%道术+{1}点生命</t>
@@ -719,7 +719,7 @@
     <t>召唤神兽</t>
   </si>
   <si>
-    <t>召唤{3}只神兽战斗，攻击为{0}%*道攻+{1}，其他全额继承</t>
+    <t>召唤{3}只神将战斗，攻击为{0}%*道攻+{1}，其他全额继承</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -1735,16 +1735,16 @@
     <col min="9" max="9" width="9.375" style="2" customWidth="1"/>
     <col min="10" max="10" width="9.33333333333333" style="2" customWidth="1"/>
     <col min="11" max="11" width="5.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="61.75" style="2" customWidth="1"/>
+    <col min="12" max="12" width="57.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="5.875" style="2" customWidth="1"/>
     <col min="14" max="14" width="6.50833333333333" style="2" customWidth="1"/>
-    <col min="15" max="15" width="8.375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7.16666666666667" style="2" customWidth="1"/>
-    <col min="17" max="17" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="18" max="19" width="7.875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="8.66666666666667" style="2" customWidth="1"/>
-    <col min="21" max="21" width="9.5" style="2" customWidth="1"/>
-    <col min="22" max="22" width="7.375" style="2" customWidth="1"/>
+    <col min="15" max="15" width="7.16666666666667" style="2" customWidth="1"/>
+    <col min="16" max="16" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="17" max="18" width="7.875" style="2" customWidth="1"/>
+    <col min="19" max="19" width="8.66666666666667" style="2" customWidth="1"/>
+    <col min="20" max="20" width="9.5" style="2" customWidth="1"/>
+    <col min="21" max="21" width="7.375" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.375" style="2" customWidth="1"/>
     <col min="23" max="23" width="7.50833333333333" style="2" customWidth="1"/>
     <col min="24" max="24" width="8.25" style="2" customWidth="1"/>
     <col min="25" max="27" width="7.625" style="2" customWidth="1"/>
@@ -1812,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="U3" s="4" t="s">
         <v>17</v>
@@ -2080,25 +2080,25 @@
         <v>0</v>
       </c>
       <c r="O6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q6" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R6" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S6" s="1">
+        <v>1</v>
+      </c>
+      <c r="T6" s="1">
         <v>100</v>
       </c>
-      <c r="T6" s="1">
-        <v>1</v>
-      </c>
       <c r="U6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V6" s="1">
         <v>0</v>
@@ -2175,25 +2175,25 @@
         <v>1</v>
       </c>
       <c r="P7" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="1">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="R7" s="1">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="S7" s="1">
+        <v>10</v>
+      </c>
+      <c r="T7" s="1">
         <v>1000</v>
       </c>
-      <c r="T7" s="1">
-        <v>10</v>
-      </c>
       <c r="U7" s="1">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="V7" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W7" s="1" t="s">
         <v>65</v>
@@ -2264,28 +2264,28 @@
         <v>5</v>
       </c>
       <c r="O8" s="1">
+        <v>1</v>
+      </c>
+      <c r="P8" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>80</v>
+      </c>
+      <c r="R8" s="1">
+        <v>800</v>
+      </c>
+      <c r="S8" s="1">
+        <v>5</v>
+      </c>
+      <c r="T8" s="1">
+        <v>800</v>
+      </c>
+      <c r="U8" s="1">
+        <v>3</v>
+      </c>
+      <c r="V8" s="1">
         <v>2</v>
-      </c>
-      <c r="P8" s="1">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>10</v>
-      </c>
-      <c r="R8" s="1">
-        <v>80</v>
-      </c>
-      <c r="S8" s="1">
-        <v>800</v>
-      </c>
-      <c r="T8" s="1">
-        <v>5</v>
-      </c>
-      <c r="U8" s="1">
-        <v>800</v>
-      </c>
-      <c r="V8" s="1">
-        <v>3</v>
       </c>
       <c r="W8" s="1" t="s">
         <v>73</v>
@@ -2360,25 +2360,25 @@
         <v>1</v>
       </c>
       <c r="P9" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q9" s="1">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="R9" s="1">
-        <v>150</v>
+        <v>2000</v>
       </c>
       <c r="S9" s="1">
+        <v>20</v>
+      </c>
+      <c r="T9" s="1">
         <v>2000</v>
       </c>
-      <c r="T9" s="1">
-        <v>20</v>
-      </c>
       <c r="U9" s="1">
-        <v>2000</v>
+        <v>4</v>
       </c>
       <c r="V9" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W9" s="1" t="s">
         <v>73</v>
@@ -2453,25 +2453,25 @@
         <v>1</v>
       </c>
       <c r="P10" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q10" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="R10" s="1">
         <v>50</v>
       </c>
       <c r="S10" s="1">
+        <v>10</v>
+      </c>
+      <c r="T10" s="1">
         <v>50</v>
       </c>
-      <c r="T10" s="1">
-        <v>10</v>
-      </c>
       <c r="U10" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" s="1" t="s">
         <v>65</v>
@@ -2543,22 +2543,22 @@
         <v>0</v>
       </c>
       <c r="O11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q11" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U11" s="1">
         <v>0</v>
@@ -2638,22 +2638,22 @@
         <v>1</v>
       </c>
       <c r="P12" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="Q12" s="1">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="R12" s="1">
-        <v>300</v>
+        <v>10000</v>
       </c>
       <c r="S12" s="1">
+        <v>50</v>
+      </c>
+      <c r="T12" s="1">
         <v>10000</v>
       </c>
-      <c r="T12" s="1">
-        <v>50</v>
-      </c>
       <c r="U12" s="1">
-        <v>10000</v>
+        <v>1</v>
       </c>
       <c r="V12" s="1">
         <v>1</v>
@@ -2747,25 +2747,25 @@
         <v>0</v>
       </c>
       <c r="O20" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P20" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q20" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R20" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S20" s="1">
+        <v>1</v>
+      </c>
+      <c r="T20" s="1">
         <v>100</v>
       </c>
-      <c r="T20" s="1">
-        <v>1</v>
-      </c>
       <c r="U20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V20" s="1">
         <v>0</v>
@@ -2839,28 +2839,28 @@
         <v>0</v>
       </c>
       <c r="O21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P21" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q21" s="1">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="R21" s="1">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="S21" s="1">
+        <v>12</v>
+      </c>
+      <c r="T21" s="1">
         <v>1000</v>
       </c>
-      <c r="T21" s="1">
-        <v>12</v>
-      </c>
       <c r="U21" s="1">
-        <v>1000</v>
+        <v>3</v>
       </c>
       <c r="V21" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W21" s="1" t="s">
         <v>73</v>
@@ -2934,25 +2934,25 @@
         <v>2</v>
       </c>
       <c r="P22" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>80</v>
+      </c>
+      <c r="R22" s="1">
+        <v>800</v>
+      </c>
+      <c r="S22" s="1">
+        <v>5</v>
+      </c>
+      <c r="T22" s="1">
+        <v>800</v>
+      </c>
+      <c r="U22" s="1">
+        <v>3</v>
+      </c>
+      <c r="V22" s="1">
         <v>2</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>10</v>
-      </c>
-      <c r="R22" s="1">
-        <v>80</v>
-      </c>
-      <c r="S22" s="1">
-        <v>800</v>
-      </c>
-      <c r="T22" s="1">
-        <v>5</v>
-      </c>
-      <c r="U22" s="1">
-        <v>800</v>
-      </c>
-      <c r="V22" s="1">
-        <v>3</v>
       </c>
       <c r="W22" s="1" t="s">
         <v>73</v>
@@ -3026,25 +3026,25 @@
         <v>2</v>
       </c>
       <c r="P23" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>120</v>
+      </c>
+      <c r="R23" s="1">
+        <v>2000</v>
+      </c>
+      <c r="S23" s="1">
+        <v>10</v>
+      </c>
+      <c r="T23" s="1">
+        <v>2000</v>
+      </c>
+      <c r="U23" s="1">
+        <v>4</v>
+      </c>
+      <c r="V23" s="1">
         <v>2</v>
-      </c>
-      <c r="Q23" s="1">
-        <v>10</v>
-      </c>
-      <c r="R23" s="1">
-        <v>120</v>
-      </c>
-      <c r="S23" s="1">
-        <v>2000</v>
-      </c>
-      <c r="T23" s="1">
-        <v>10</v>
-      </c>
-      <c r="U23" s="1">
-        <v>2000</v>
-      </c>
-      <c r="V23" s="1">
-        <v>4</v>
       </c>
       <c r="W23" s="1" t="s">
         <v>73</v>
@@ -3116,28 +3116,28 @@
         <v>30</v>
       </c>
       <c r="O24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P24" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q24" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="R24" s="1">
         <v>50</v>
       </c>
       <c r="S24" s="1">
+        <v>10</v>
+      </c>
+      <c r="T24" s="1">
         <v>50</v>
       </c>
-      <c r="T24" s="1">
-        <v>10</v>
-      </c>
       <c r="U24" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>65</v>
@@ -3209,22 +3209,22 @@
         <v>0</v>
       </c>
       <c r="O25" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P25" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="Q25" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U25" s="1">
         <v>0</v>
@@ -3304,25 +3304,25 @@
         <v>2</v>
       </c>
       <c r="P26" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>150</v>
+      </c>
+      <c r="R26" s="1">
+        <v>5000</v>
+      </c>
+      <c r="S26" s="1">
+        <v>30</v>
+      </c>
+      <c r="T26" s="1">
+        <v>5000</v>
+      </c>
+      <c r="U26" s="1">
+        <v>5</v>
+      </c>
+      <c r="V26" s="1">
         <v>2</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>10</v>
-      </c>
-      <c r="R26" s="1">
-        <v>150</v>
-      </c>
-      <c r="S26" s="1">
-        <v>5000</v>
-      </c>
-      <c r="T26" s="1">
-        <v>30</v>
-      </c>
-      <c r="U26" s="1">
-        <v>5000</v>
-      </c>
-      <c r="V26" s="1">
-        <v>5</v>
       </c>
       <c r="W26" s="1" t="s">
         <v>73</v>
@@ -3423,25 +3423,25 @@
         <v>0</v>
       </c>
       <c r="O34" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P34" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q34" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R34" s="1">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="S34" s="1">
+        <v>1</v>
+      </c>
+      <c r="T34" s="1">
         <v>100</v>
       </c>
-      <c r="T34" s="1">
-        <v>1</v>
-      </c>
       <c r="U34" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V34" s="1">
         <v>0</v>
@@ -3515,28 +3515,28 @@
         <v>0</v>
       </c>
       <c r="O35" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P35" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>120</v>
+      </c>
+      <c r="R35" s="1">
+        <v>1000</v>
+      </c>
+      <c r="S35" s="1">
+        <v>10</v>
+      </c>
+      <c r="T35" s="1">
+        <v>1000</v>
+      </c>
+      <c r="U35" s="1">
         <v>3</v>
       </c>
-      <c r="Q35" s="1">
-        <v>10</v>
-      </c>
-      <c r="R35" s="1">
-        <v>120</v>
-      </c>
-      <c r="S35" s="1">
-        <v>1000</v>
-      </c>
-      <c r="T35" s="1">
-        <v>10</v>
-      </c>
-      <c r="U35" s="1">
-        <v>1000</v>
-      </c>
       <c r="V35" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W35" s="1" t="s">
         <v>73</v>
@@ -3607,28 +3607,28 @@
         <v>5</v>
       </c>
       <c r="O36" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P36" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q36" s="1">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="R36" s="1">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="S36" s="1">
+        <v>5</v>
+      </c>
+      <c r="T36" s="1">
         <v>800</v>
       </c>
-      <c r="T36" s="1">
-        <v>5</v>
-      </c>
       <c r="U36" s="1">
-        <v>800</v>
+        <v>4</v>
       </c>
       <c r="V36" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W36" s="1" t="s">
         <v>73</v>
@@ -3679,7 +3679,7 @@
         <v>120</v>
       </c>
       <c r="H37" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I37" s="1">
         <v>6</v>
@@ -3700,28 +3700,28 @@
         <v>0</v>
       </c>
       <c r="O37" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P37" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q37" s="1">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="R37" s="1">
+        <v>100000</v>
+      </c>
+      <c r="S37" s="1">
         <v>1000</v>
       </c>
-      <c r="S37" s="1">
+      <c r="T37" s="1">
         <v>100000</v>
       </c>
-      <c r="T37" s="1">
-        <v>1000</v>
-      </c>
       <c r="U37" s="1">
-        <v>100000</v>
+        <v>5</v>
       </c>
       <c r="V37" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="W37" s="1" t="s">
         <v>65</v>
@@ -3792,28 +3792,28 @@
         <v>30</v>
       </c>
       <c r="O38" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P38" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q38" s="1">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="R38" s="1">
         <v>50</v>
       </c>
       <c r="S38" s="1">
+        <v>10</v>
+      </c>
+      <c r="T38" s="1">
         <v>50</v>
       </c>
-      <c r="T38" s="1">
-        <v>10</v>
-      </c>
       <c r="U38" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="V38" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W38" s="1" t="s">
         <v>65</v>
@@ -3885,22 +3885,22 @@
         <v>0</v>
       </c>
       <c r="O39" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P39" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q39" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="R39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U39" s="1">
         <v>0</v>
@@ -3977,28 +3977,28 @@
         <v>0</v>
       </c>
       <c r="O40" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P40" s="1">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q40" s="1">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="R40" s="1">
-        <v>200</v>
+        <v>8000</v>
       </c>
       <c r="S40" s="1">
+        <v>40</v>
+      </c>
+      <c r="T40" s="1">
         <v>8000</v>
       </c>
-      <c r="T40" s="1">
-        <v>40</v>
-      </c>
       <c r="U40" s="1">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="V40" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" s="1" t="s">
         <v>73</v>
@@ -4177,16 +4177,16 @@
         <v>0</v>
       </c>
       <c r="Q45" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R45" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S45" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T45" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="U45" s="1">
         <v>0</v>
@@ -4270,10 +4270,10 @@
         <v>0</v>
       </c>
       <c r="Q46" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R46" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S46" s="1">
         <v>0</v>
@@ -4361,22 +4361,22 @@
         <v>0</v>
       </c>
       <c r="O49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P49" s="1">
         <v>0</v>
       </c>
       <c r="Q49" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S49" s="1">
         <v>0</v>
       </c>
-      <c r="T49" s="1">
-        <v>0</v>
+      <c r="U49" s="1">
+        <v>1</v>
       </c>
       <c r="V49" s="1">
         <v>1</v>
@@ -4422,10 +4422,10 @@
       <c r="J52" s="1"/>
       <c r="O52" s="1"/>
       <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
-      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Z52" s="1"/>
@@ -4466,9 +4466,9 @@
       <c r="E54" s="1"/>
       <c r="I54" s="1"/>
       <c r="J54" s="1"/>
-      <c r="O54" s="1"/>
+      <c r="S54" s="1"/>
       <c r="T54" s="1"/>
-      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
@@ -4483,7 +4483,7 @@
       <c r="K55" s="1"/>
       <c r="L55" s="2"/>
       <c r="M55" s="1"/>
-      <c r="Q55" s="2"/>
+      <c r="P55" s="2"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1"/>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -4555,9 +4555,9 @@
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
       <c r="L78" s="2"/>
-      <c r="Q78" s="2"/>
+      <c r="P78" s="2"/>
+      <c r="S78" s="2"/>
       <c r="T78" s="2"/>
-      <c r="U78" s="2"/>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G79" s="2"/>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -74,18 +74,44 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-1 攻击技能
-2 召唤技能
-3 场景技能
-4 回复技能
-5 盾类技能
-6 专精技能
-7 野蛮
-8 被动</t>
+0 特殊技能，单独逻辑
+1 被动技能
+2 单体攻击
+3 范围攻击
+4 召唤技能
+5 火墙技能
+6 盾类技能
+7 专精技能
+8 恢复技能
+9 直线攻击</t>
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="1">
+    <comment ref="I3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+Self 自身
+Enemy 敌人
+Team 队友</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -108,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="M3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -130,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L3" authorId="1">
+    <comment ref="N3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -158,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="O3" authorId="0">
+    <comment ref="Q3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -180,7 +206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -202,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="U3" authorId="0">
+    <comment ref="W3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -225,82 +251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="V3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-0 被动
-1 单体（施毒术属于单体）
-2 范围
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="W3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-Self 自身
-Enemy 敌人
-Team 队友</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="X3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-FrontRow 直线
-FullBox 十字
-Square 矩形
-Diamond 菱形
-FullBox 全图</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AF3" authorId="0">
+    <comment ref="AE3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -327,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="134">
   <si>
     <t>_ID</t>
   </si>
@@ -347,6 +298,9 @@
     <t>类型</t>
   </si>
   <si>
+    <t>中心目标</t>
+  </si>
+  <si>
     <t>互斥技能</t>
   </si>
   <si>
@@ -383,15 +337,6 @@
     <t>攻击距离</t>
   </si>
   <si>
-    <t>施法类型</t>
-  </si>
-  <si>
-    <t>中心目标</t>
-  </si>
-  <si>
-    <t>攻击区域</t>
-  </si>
-  <si>
     <t>最大敌人数量</t>
   </si>
   <si>
@@ -434,6 +379,12 @@
     <t>Type</t>
   </si>
   <si>
+    <t>Center</t>
+  </si>
+  <si>
+    <t>Area</t>
+  </si>
+  <si>
     <t>Repet</t>
   </si>
   <si>
@@ -473,15 +424,6 @@
     <t>Dis</t>
   </si>
   <si>
-    <t>CastType</t>
-  </si>
-  <si>
-    <t>Center</t>
-  </si>
-  <si>
-    <t>Area</t>
-  </si>
-  <si>
     <t>EnemyMax</t>
   </si>
   <si>
@@ -521,49 +463,43 @@
     <t>基础心法</t>
   </si>
   <si>
+    <t>Self</t>
+  </si>
+  <si>
     <t>被动增加{0}%的物攻加成和{1}点物攻，无需上阵</t>
   </si>
   <si>
-    <t>Self</t>
+    <t>流光剑诀</t>
+  </si>
+  <si>
+    <t>刺杀</t>
   </si>
   <si>
     <t>FrontRow</t>
   </si>
   <si>
-    <t>流光剑诀</t>
-  </si>
-  <si>
-    <t>刺杀</t>
-  </si>
-  <si>
     <t>对直线攻击距离内的敌人造成{0}%物攻+{1}点技能伤害</t>
   </si>
   <si>
     <t>四方剑阵</t>
   </si>
   <si>
-    <t>半月弯刀</t>
+    <t>剑二十三</t>
+  </si>
+  <si>
+    <t>Enemy</t>
+  </si>
+  <si>
+    <t>Square</t>
   </si>
   <si>
     <t>施展{4}*{5}范围的剑阵，持续{2}s，对其内的敌人造成{0}%物攻+{1}点伤害，按攻速结算</t>
   </si>
   <si>
-    <t>Enemy</t>
-  </si>
-  <si>
-    <t>Arc</t>
-  </si>
-  <si>
-    <t>重击剑术</t>
-  </si>
-  <si>
-    <t>野蛮撞击</t>
-  </si>
-  <si>
-    <t>对目标敌人造成{0}%物攻+{1}点技能伤害，并且晕眩{2}秒</t>
-  </si>
-  <si>
-    <t>Chase</t>
+    <t>背刺剑法</t>
+  </si>
+  <si>
+    <t>瞬移到敌人身后造成{0}%物攻+{1}点技能伤害，并且晕眩{2}秒</t>
   </si>
   <si>
     <t>武神盾</t>
@@ -575,9 +511,6 @@
     <t>提高人物{0}防御，并且生成一个{1}%生命的护盾，持续{2}秒</t>
   </si>
   <si>
-    <t>Square</t>
-  </si>
-  <si>
     <t>无求易决</t>
   </si>
   <si>
@@ -587,9 +520,6 @@
     <t>战士技能增加{0}%技能系数增幅，无需上阵</t>
   </si>
   <si>
-    <t>FullBox</t>
-  </si>
-  <si>
     <t>火麟剑诀</t>
   </si>
   <si>
@@ -605,13 +535,13 @@
     <t>被动增加{0}%的魔攻加成和{1}点魔攻，无需上阵</t>
   </si>
   <si>
+    <t>神雷术</t>
+  </si>
+  <si>
+    <t>雷电术</t>
+  </si>
+  <si>
     <t>Circle</t>
-  </si>
-  <si>
-    <t>神雷术</t>
-  </si>
-  <si>
-    <t>雷电术</t>
   </si>
   <si>
     <t>对{3}个敌人造成{0}%魔法+{1}点技能伤害</t>
@@ -762,7 +692,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -781,6 +711,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1263,137 +1199,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1403,6 +1339,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1723,7 +1660,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:AG79"/>
+  <dimension ref="C2:AF79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
@@ -1731,35 +1668,33 @@
     <col min="3" max="5" width="9" style="2"/>
     <col min="6" max="6" width="11.5083333333333" style="2" customWidth="1"/>
     <col min="7" max="7" width="9" style="2" customWidth="1"/>
-    <col min="8" max="8" width="6.375" style="2" customWidth="1"/>
-    <col min="9" max="9" width="9.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="9.33333333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="5.25" style="2" customWidth="1"/>
-    <col min="12" max="12" width="57.25" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="6.50833333333333" style="2" customWidth="1"/>
-    <col min="15" max="15" width="7.16666666666667" style="2" customWidth="1"/>
-    <col min="16" max="16" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="17" max="18" width="7.875" style="2" customWidth="1"/>
-    <col min="19" max="19" width="8.66666666666667" style="2" customWidth="1"/>
-    <col min="20" max="20" width="9.5" style="2" customWidth="1"/>
-    <col min="21" max="21" width="7.375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="8.375" style="2" customWidth="1"/>
-    <col min="23" max="23" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="24" max="24" width="8.25" style="2" customWidth="1"/>
-    <col min="25" max="27" width="7.625" style="2" customWidth="1"/>
-    <col min="28" max="28" width="9.625" style="2" customWidth="1"/>
-    <col min="29" max="30" width="7.875" style="2" customWidth="1"/>
-    <col min="31" max="31" width="9.75" style="2" customWidth="1"/>
-    <col min="32" max="32" width="21.75" style="2" customWidth="1"/>
-    <col min="33" max="33" width="11.75" style="2" customWidth="1"/>
-    <col min="34" max="16384" width="9" style="2"/>
+    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
+    <col min="9" max="10" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.33333333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="5.25" style="2" customWidth="1"/>
+    <col min="14" max="14" width="57.25" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="6.50833333333333" style="2" customWidth="1"/>
+    <col min="17" max="17" width="7.16666666666667" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="19" max="20" width="7.875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="8.66666666666667" style="2" customWidth="1"/>
+    <col min="22" max="22" width="9.5" style="2" customWidth="1"/>
+    <col min="23" max="23" width="7.375" style="2" customWidth="1"/>
+    <col min="24" max="26" width="7.625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="9.625" style="2" customWidth="1"/>
+    <col min="28" max="29" width="7.875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="9.75" style="2" customWidth="1"/>
+    <col min="31" max="31" width="21.75" style="2" customWidth="1"/>
+    <col min="32" max="32" width="11.75" style="2" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" ht="33" customHeight="1" spans="3:33">
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" customHeight="1" spans="3:33">
+    <row r="2" ht="33" customHeight="1" spans="3:32">
+      <c r="N2" s="3"/>
+    </row>
+    <row r="3" customHeight="1" spans="3:32">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1781,35 +1716,33 @@
       <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="M3" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="N3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="S3" s="4" t="s">
         <v>15</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>16</v>
       </c>
       <c r="T3" s="4" t="s">
         <v>16</v>
@@ -1818,233 +1751,224 @@
         <v>17</v>
       </c>
       <c r="V3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="W3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="X3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="Y3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Z3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="AA3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AB3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AC3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AD3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AE3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AF3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="AF3" s="4" t="s">
+    </row>
+    <row r="4" customHeight="1" spans="3:32">
+      <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AG3" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:33">
-      <c r="C4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>31</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="K4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="L4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="O4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="Q4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="R4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="S4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="V4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="W4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="X4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="Y4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="Z4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="AA4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="AB4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AC4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AB4" s="4" t="s">
+      <c r="AD4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AC4" s="4" t="s">
+      <c r="AE4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AD4" s="4" t="s">
+      <c r="AF4" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="AE4" s="4" t="s">
+    </row>
+    <row r="5" customHeight="1" spans="3:32">
+      <c r="C5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AF4" s="4" t="s">
+      <c r="D5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="AG4" s="4" t="s">
+      <c r="G5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AE5" s="4" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:33">
-      <c r="C5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Z5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AA5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AB5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AD5" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="AE5" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="AF5" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="AG5" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:33">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2055,41 +1979,38 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
-        <v>8</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="K6" s="1">
-        <v>10</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>64</v>
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="O6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q6" s="1">
         <v>1</v>
       </c>
       <c r="R6" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="S6" s="1">
         <v>1</v>
@@ -2098,16 +2019,16 @@
         <v>100</v>
       </c>
       <c r="U6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V6" s="1">
-        <v>0</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>66</v>
+        <v>100</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0</v>
       </c>
       <c r="Y6" s="1">
         <v>0</v>
@@ -2127,14 +2048,11 @@
       <c r="AD6" s="1">
         <v>0</v>
       </c>
-      <c r="AE6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG6" s="1">
+      <c r="AF6" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2145,64 +2063,64 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="H7" s="1">
+        <v>9</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J7" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1">
+        <v>10</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="O7" s="1">
+        <v>5</v>
+      </c>
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
         <v>1</v>
       </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>10</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="M7" s="1">
-        <v>5</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>1</v>
-      </c>
-      <c r="P7" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="1">
+      <c r="R7" s="1">
+        <v>10</v>
+      </c>
+      <c r="S7" s="1">
         <v>120</v>
-      </c>
-      <c r="R7" s="1">
-        <v>1000</v>
-      </c>
-      <c r="S7" s="1">
-        <v>10</v>
       </c>
       <c r="T7" s="1">
         <v>1000</v>
       </c>
       <c r="U7" s="1">
+        <v>10</v>
+      </c>
+      <c r="V7" s="1">
+        <v>1000</v>
+      </c>
+      <c r="W7" s="1">
         <v>2</v>
       </c>
-      <c r="V7" s="1">
-        <v>1</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>66</v>
+      <c r="X7" s="1">
+        <v>2</v>
       </c>
       <c r="Y7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z7" s="1">
         <v>0</v>
@@ -2219,14 +2137,11 @@
       <c r="AD7" s="1">
         <v>0</v>
       </c>
-      <c r="AE7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG7" s="1">
+      <c r="AF7" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2237,70 +2152,70 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="1">
+        <v>5</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>10</v>
+      </c>
+      <c r="N8" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="1">
+      <c r="O8" s="1">
+        <v>10</v>
+      </c>
+      <c r="P8" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="1">
         <v>1</v>
       </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>10</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="M8" s="1">
-        <v>10</v>
-      </c>
-      <c r="N8" s="1">
-        <v>5</v>
-      </c>
-      <c r="O8" s="1">
-        <v>1</v>
-      </c>
-      <c r="P8" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q8" s="1">
+      <c r="R8" s="1">
+        <v>10</v>
+      </c>
+      <c r="S8" s="1">
         <v>80</v>
-      </c>
-      <c r="R8" s="1">
-        <v>800</v>
-      </c>
-      <c r="S8" s="1">
-        <v>5</v>
       </c>
       <c r="T8" s="1">
         <v>800</v>
       </c>
       <c r="U8" s="1">
+        <v>5</v>
+      </c>
+      <c r="V8" s="1">
+        <v>800</v>
+      </c>
+      <c r="W8" s="1">
         <v>3</v>
       </c>
-      <c r="V8" s="1">
-        <v>2</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>74</v>
+      <c r="X8" s="1">
+        <v>0</v>
       </c>
       <c r="Y8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z8" s="1">
         <v>3</v>
       </c>
       <c r="AA8" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB8" s="1">
         <v>0</v>
@@ -2311,15 +2226,12 @@
       <c r="AD8" s="1">
         <v>0</v>
       </c>
-      <c r="AE8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1">
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2330,64 +2242,59 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="G9" s="1"/>
       <c r="H9" s="1">
-        <v>7</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="K9" s="1">
-        <v>10</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>77</v>
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
       </c>
       <c r="M9" s="1">
+        <v>10</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="O9" s="1">
         <v>8</v>
       </c>
-      <c r="N9" s="1">
+      <c r="P9" s="1">
         <v>2</v>
       </c>
-      <c r="O9" s="1">
+      <c r="Q9" s="1">
         <v>1</v>
       </c>
-      <c r="P9" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q9" s="1">
+      <c r="R9" s="1">
+        <v>10</v>
+      </c>
+      <c r="S9" s="1">
         <v>150</v>
-      </c>
-      <c r="R9" s="1">
-        <v>2000</v>
-      </c>
-      <c r="S9" s="1">
-        <v>20</v>
       </c>
       <c r="T9" s="1">
         <v>2000</v>
       </c>
       <c r="U9" s="1">
+        <v>20</v>
+      </c>
+      <c r="V9" s="1">
+        <v>2000</v>
+      </c>
+      <c r="W9" s="1">
         <v>4</v>
       </c>
-      <c r="V9" s="1">
+      <c r="X9" s="1">
         <v>1</v>
       </c>
-      <c r="W9" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="Y9" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" s="1">
         <v>0</v>
@@ -2404,15 +2311,12 @@
       <c r="AD9" s="1">
         <v>0</v>
       </c>
-      <c r="AE9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1">
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2423,61 +2327,58 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H10" s="1">
+        <v>6</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K10" s="1">
         <v>5</v>
       </c>
-      <c r="I10" s="1">
-        <v>5</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1">
         <v>50</v>
       </c>
-      <c r="L10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="M10" s="1">
+      <c r="N10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="O10" s="1">
         <v>60</v>
       </c>
-      <c r="N10" s="1">
+      <c r="P10" s="1">
         <v>30</v>
       </c>
-      <c r="O10" s="1">
+      <c r="Q10" s="1">
         <v>1</v>
       </c>
-      <c r="P10" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q10" s="1">
+      <c r="R10" s="1">
+        <v>10</v>
+      </c>
+      <c r="S10" s="1">
         <v>50</v>
-      </c>
-      <c r="R10" s="1">
-        <v>50</v>
-      </c>
-      <c r="S10" s="1">
-        <v>10</v>
       </c>
       <c r="T10" s="1">
         <v>50</v>
       </c>
       <c r="U10" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V10" s="1">
-        <v>1</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>82</v>
+        <v>50</v>
+      </c>
+      <c r="W10" s="1">
+        <v>0</v>
+      </c>
+      <c r="X10" s="1">
+        <v>0</v>
       </c>
       <c r="Y10" s="1">
         <v>0</v>
@@ -2497,15 +2398,12 @@
       <c r="AD10" s="1">
         <v>0</v>
       </c>
-      <c r="AE10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF10" s="1"/>
-      <c r="AG10" s="1">
+      <c r="AE10" s="1"/>
+      <c r="AF10" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2516,43 +2414,40 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="H11" s="1">
-        <v>6</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="K11" s="1">
-        <v>10</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>85</v>
+        <v>0</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>79</v>
       </c>
       <c r="O11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P11" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="1">
         <v>1</v>
       </c>
       <c r="R11" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S11" s="1">
         <v>1</v>
@@ -2561,16 +2456,16 @@
         <v>0</v>
       </c>
       <c r="U11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" s="1">
         <v>0</v>
       </c>
-      <c r="W11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X11" s="1" t="s">
-        <v>86</v>
+      <c r="W11" s="1">
+        <v>0</v>
+      </c>
+      <c r="X11" s="1">
+        <v>0</v>
       </c>
       <c r="Y11" s="1">
         <v>0</v>
@@ -2590,14 +2485,11 @@
       <c r="AD11" s="1">
         <v>0</v>
       </c>
-      <c r="AE11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="1">
+      <c r="AF11" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2608,64 +2500,64 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H12" s="1">
+        <v>9</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="K12" s="1">
+        <v>0</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>10</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="O12" s="1">
+        <v>10</v>
+      </c>
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
         <v>1</v>
       </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>10</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="M12" s="1">
-        <v>10</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1">
-        <v>1</v>
-      </c>
-      <c r="P12" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q12" s="1">
+      <c r="R12" s="1">
+        <v>10</v>
+      </c>
+      <c r="S12" s="1">
         <v>300</v>
-      </c>
-      <c r="R12" s="1">
-        <v>10000</v>
-      </c>
-      <c r="S12" s="1">
-        <v>50</v>
       </c>
       <c r="T12" s="1">
         <v>10000</v>
       </c>
       <c r="U12" s="1">
+        <v>50</v>
+      </c>
+      <c r="V12" s="1">
+        <v>10000</v>
+      </c>
+      <c r="W12" s="1">
         <v>1</v>
       </c>
-      <c r="V12" s="1">
+      <c r="X12" s="1">
         <v>1</v>
       </c>
-      <c r="W12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="Y12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z12" s="1">
         <v>0</v>
@@ -2682,36 +2574,33 @@
       <c r="AD12" s="1">
         <v>0</v>
       </c>
-      <c r="AE12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1">
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G13" s="2"/>
     </row>
-    <row r="14" customFormat="1" customHeight="1" spans="3:33">
-      <c r="AF14" s="1"/>
-    </row>
-    <row r="15" customFormat="1" customHeight="1" spans="3:33">
-      <c r="AF15" s="1"/>
-    </row>
-    <row r="16" customFormat="1" customHeight="1" spans="3:33">
-      <c r="AF16" s="1"/>
-    </row>
-    <row r="17" customFormat="1" customHeight="1" spans="3:33">
-      <c r="AF17" s="1"/>
-    </row>
-    <row r="18" customFormat="1" customHeight="1" spans="3:33">
-      <c r="AF18" s="1"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="14" customFormat="1" customHeight="1" spans="3:32">
+      <c r="AE14" s="1"/>
+    </row>
+    <row r="15" customFormat="1" customHeight="1" spans="3:32">
+      <c r="AE15" s="1"/>
+    </row>
+    <row r="16" customFormat="1" customHeight="1" spans="3:32">
+      <c r="AE16" s="1"/>
+    </row>
+    <row r="17" customFormat="1" customHeight="1" spans="3:32">
+      <c r="AE17" s="1"/>
+    </row>
+    <row r="18" customFormat="1" customHeight="1" spans="3:32">
+      <c r="AE18" s="1"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G19" s="2"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C20" s="1">
         <v>2001</v>
       </c>
@@ -2722,41 +2611,38 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
-        <v>8</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="K20" s="1">
-        <v>10</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>91</v>
+        <v>0</v>
+      </c>
+      <c r="L20" s="1">
+        <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="O20" s="1">
+        <v>0</v>
+      </c>
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
         <v>2</v>
       </c>
-      <c r="P20" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>1</v>
-      </c>
       <c r="R20" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="S20" s="1">
         <v>1</v>
@@ -2765,16 +2651,16 @@
         <v>100</v>
       </c>
       <c r="U20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V20" s="1">
-        <v>0</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
+      </c>
+      <c r="W20" s="1">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1">
+        <v>0</v>
       </c>
       <c r="Y20" s="1">
         <v>0</v>
@@ -2794,14 +2680,11 @@
       <c r="AD20" s="1">
         <v>0</v>
       </c>
-      <c r="AE20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="1">
+      <c r="AF20" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C21" s="1">
         <v>2002</v>
       </c>
@@ -2812,64 +2695,64 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="H21" s="1">
-        <v>1</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J21" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="K21" s="1">
-        <v>10</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>95</v>
+        <v>0</v>
+      </c>
+      <c r="L21" s="1">
+        <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>0</v>
-      </c>
-      <c r="N21" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="O21" s="1">
+        <v>0</v>
+      </c>
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
         <v>2</v>
       </c>
-      <c r="P21" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q21" s="1">
+      <c r="R21" s="1">
+        <v>10</v>
+      </c>
+      <c r="S21" s="1">
         <v>120</v>
-      </c>
-      <c r="R21" s="1">
-        <v>1000</v>
-      </c>
-      <c r="S21" s="1">
-        <v>12</v>
       </c>
       <c r="T21" s="1">
         <v>1000</v>
       </c>
       <c r="U21" s="1">
+        <v>12</v>
+      </c>
+      <c r="V21" s="1">
+        <v>1000</v>
+      </c>
+      <c r="W21" s="1">
         <v>3</v>
       </c>
-      <c r="V21" s="1">
+      <c r="X21" s="1">
         <v>1</v>
       </c>
-      <c r="W21" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="Y21" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z21" s="1">
         <v>0</v>
@@ -2886,14 +2769,11 @@
       <c r="AD21" s="1">
         <v>0</v>
       </c>
-      <c r="AE21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="1">
+      <c r="AF21" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C22" s="1">
         <v>2003</v>
       </c>
@@ -2904,70 +2784,70 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="H22" s="1">
-        <v>3</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J22" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="K22" s="1">
-        <v>10</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>98</v>
+        <v>0</v>
+      </c>
+      <c r="L22" s="1">
+        <v>0</v>
       </c>
       <c r="M22" s="1">
         <v>10</v>
       </c>
-      <c r="N22" s="1">
+      <c r="N22" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O22" s="1">
+        <v>10</v>
+      </c>
+      <c r="P22" s="1">
         <v>5</v>
       </c>
-      <c r="O22" s="1">
+      <c r="Q22" s="1">
         <v>2</v>
       </c>
-      <c r="P22" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q22" s="1">
+      <c r="R22" s="1">
+        <v>10</v>
+      </c>
+      <c r="S22" s="1">
         <v>80</v>
-      </c>
-      <c r="R22" s="1">
-        <v>800</v>
-      </c>
-      <c r="S22" s="1">
-        <v>5</v>
       </c>
       <c r="T22" s="1">
         <v>800</v>
       </c>
       <c r="U22" s="1">
+        <v>5</v>
+      </c>
+      <c r="V22" s="1">
+        <v>800</v>
+      </c>
+      <c r="W22" s="1">
         <v>3</v>
       </c>
-      <c r="V22" s="1">
-        <v>2</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X22" s="1" t="s">
-        <v>82</v>
+      <c r="X22" s="1">
+        <v>0</v>
       </c>
       <c r="Y22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z22" s="1">
         <v>3</v>
       </c>
       <c r="AA22" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -2978,14 +2858,11 @@
       <c r="AD22" s="1">
         <v>0</v>
       </c>
-      <c r="AE22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG22" s="1">
+      <c r="AF22" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C23" s="1">
         <v>2004</v>
       </c>
@@ -2996,70 +2873,70 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="H23" s="1">
-        <v>1</v>
-      </c>
-      <c r="I23" s="1">
-        <v>0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J23" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="K23" s="1">
-        <v>10</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>101</v>
+        <v>0</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
         <v>2</v>
       </c>
-      <c r="P23" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q23" s="1">
+      <c r="R23" s="1">
+        <v>10</v>
+      </c>
+      <c r="S23" s="1">
         <v>120</v>
-      </c>
-      <c r="R23" s="1">
-        <v>2000</v>
-      </c>
-      <c r="S23" s="1">
-        <v>10</v>
       </c>
       <c r="T23" s="1">
         <v>2000</v>
       </c>
       <c r="U23" s="1">
+        <v>10</v>
+      </c>
+      <c r="V23" s="1">
+        <v>2000</v>
+      </c>
+      <c r="W23" s="1">
         <v>4</v>
       </c>
-      <c r="V23" s="1">
-        <v>2</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>82</v>
+      <c r="X23" s="1">
+        <v>0</v>
       </c>
       <c r="Y23" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z23" s="1">
         <v>3</v>
       </c>
       <c r="AA23" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB23" s="1">
         <v>0</v>
@@ -3070,15 +2947,12 @@
       <c r="AD23" s="1">
         <v>0</v>
       </c>
-      <c r="AE23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1">
+      <c r="AE23" s="1"/>
+      <c r="AF23" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C24" s="1">
         <v>2005</v>
       </c>
@@ -3089,61 +2963,58 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="H24" s="1">
+        <v>6</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K24" s="1">
         <v>5</v>
       </c>
-      <c r="I24" s="1">
-        <v>5</v>
-      </c>
-      <c r="J24" s="1">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
+        <v>0</v>
+      </c>
+      <c r="M24" s="1">
         <v>50</v>
       </c>
-      <c r="L24" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="M24" s="1">
+      <c r="N24" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="O24" s="1">
         <v>60</v>
       </c>
-      <c r="N24" s="1">
+      <c r="P24" s="1">
         <v>30</v>
       </c>
-      <c r="O24" s="1">
+      <c r="Q24" s="1">
         <v>2</v>
       </c>
-      <c r="P24" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q24" s="1">
+      <c r="R24" s="1">
+        <v>10</v>
+      </c>
+      <c r="S24" s="1">
         <v>50</v>
-      </c>
-      <c r="R24" s="1">
-        <v>50</v>
-      </c>
-      <c r="S24" s="1">
-        <v>10</v>
       </c>
       <c r="T24" s="1">
         <v>50</v>
       </c>
       <c r="U24" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V24" s="1">
-        <v>1</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>82</v>
+        <v>50</v>
+      </c>
+      <c r="W24" s="1">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1">
+        <v>0</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -3163,15 +3034,12 @@
       <c r="AD24" s="1">
         <v>0</v>
       </c>
-      <c r="AE24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF24" s="1"/>
-      <c r="AG24" s="1">
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C25" s="1">
         <v>2006</v>
       </c>
@@ -3182,43 +3050,40 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="H25" s="1">
-        <v>6</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="K25" s="1">
-        <v>10</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>107</v>
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
       </c>
       <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="O25" s="1">
+        <v>0</v>
+      </c>
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1">
         <v>2</v>
       </c>
-      <c r="P25" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>1</v>
-      </c>
       <c r="R25" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S25" s="1">
         <v>1</v>
@@ -3227,16 +3092,16 @@
         <v>0</v>
       </c>
       <c r="U25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" s="1">
         <v>0</v>
       </c>
-      <c r="W25" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>86</v>
+      <c r="W25" s="1">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1">
+        <v>0</v>
       </c>
       <c r="Y25" s="1">
         <v>0</v>
@@ -3256,14 +3121,11 @@
       <c r="AD25" s="1">
         <v>0</v>
       </c>
-      <c r="AE25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG25" s="1">
+      <c r="AF25" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C26" s="1">
         <v>2007</v>
       </c>
@@ -3274,70 +3136,70 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="H26" s="1">
-        <v>1</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="K26" s="1">
-        <v>10</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>110</v>
+        <v>0</v>
+      </c>
+      <c r="L26" s="1">
+        <v>0</v>
       </c>
       <c r="M26" s="1">
+        <v>10</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O26" s="1">
         <v>15</v>
       </c>
-      <c r="N26" s="1">
-        <v>0</v>
-      </c>
-      <c r="O26" s="1">
+      <c r="P26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="1">
         <v>2</v>
       </c>
-      <c r="P26" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q26" s="1">
+      <c r="R26" s="1">
+        <v>10</v>
+      </c>
+      <c r="S26" s="1">
         <v>150</v>
-      </c>
-      <c r="R26" s="1">
-        <v>5000</v>
-      </c>
-      <c r="S26" s="1">
-        <v>30</v>
       </c>
       <c r="T26" s="1">
         <v>5000</v>
       </c>
       <c r="U26" s="1">
+        <v>30</v>
+      </c>
+      <c r="V26" s="1">
+        <v>5000</v>
+      </c>
+      <c r="W26" s="1">
         <v>5</v>
       </c>
-      <c r="V26" s="1">
-        <v>2</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X26" s="1" t="s">
-        <v>82</v>
+      <c r="X26" s="1">
+        <v>0</v>
       </c>
       <c r="Y26" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z26" s="1">
         <v>3</v>
       </c>
       <c r="AA26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB26" s="1">
         <v>0</v>
@@ -3348,46 +3210,37 @@
       <c r="AD26" s="1">
         <v>0</v>
       </c>
-      <c r="AE26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF26" s="1"/>
-      <c r="AG26" s="1">
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G27" s="2"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G28" s="2"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G30" s="2"/>
       <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="N30" s="2"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G31" s="2"/>
       <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:33">
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="N31" s="2"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:32">
+      <c r="N32" s="2"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G33" s="2"/>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C34" s="1">
         <v>3001</v>
       </c>
@@ -3398,41 +3251,38 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
-        <v>8</v>
-      </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1">
         <v>20</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="M34" s="1">
-        <v>0</v>
-      </c>
-      <c r="N34" s="1">
-        <v>0</v>
+      <c r="N34" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="O34" s="1">
+        <v>0</v>
+      </c>
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="1">
         <v>3</v>
       </c>
-      <c r="P34" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q34" s="1">
-        <v>1</v>
-      </c>
       <c r="R34" s="1">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="S34" s="1">
         <v>1</v>
@@ -3441,16 +3291,16 @@
         <v>100</v>
       </c>
       <c r="U34" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34" s="1">
-        <v>0</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>92</v>
+        <v>100</v>
+      </c>
+      <c r="W34" s="1">
+        <v>0</v>
+      </c>
+      <c r="X34" s="1">
+        <v>0</v>
       </c>
       <c r="Y34" s="1">
         <v>0</v>
@@ -3470,14 +3320,11 @@
       <c r="AD34" s="1">
         <v>0</v>
       </c>
-      <c r="AE34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG34" s="1">
+      <c r="AF34" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C35" s="1">
         <v>3002</v>
       </c>
@@ -3488,64 +3335,64 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="H35" s="1">
-        <v>1</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="K35" s="1">
-        <v>10</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>115</v>
+        <v>0</v>
+      </c>
+      <c r="L35" s="1">
+        <v>0</v>
       </c>
       <c r="M35" s="1">
-        <v>0</v>
-      </c>
-      <c r="N35" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="O35" s="1">
+        <v>0</v>
+      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
         <v>3</v>
       </c>
-      <c r="P35" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q35" s="1">
+      <c r="R35" s="1">
+        <v>10</v>
+      </c>
+      <c r="S35" s="1">
         <v>120</v>
-      </c>
-      <c r="R35" s="1">
-        <v>1000</v>
-      </c>
-      <c r="S35" s="1">
-        <v>10</v>
       </c>
       <c r="T35" s="1">
         <v>1000</v>
       </c>
       <c r="U35" s="1">
+        <v>10</v>
+      </c>
+      <c r="V35" s="1">
+        <v>1000</v>
+      </c>
+      <c r="W35" s="1">
         <v>3</v>
       </c>
-      <c r="V35" s="1">
+      <c r="X35" s="1">
         <v>1</v>
       </c>
-      <c r="W35" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X35" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="Y35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" s="1">
         <v>0</v>
@@ -3562,14 +3409,11 @@
       <c r="AD35" s="1">
         <v>0</v>
       </c>
-      <c r="AE35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG35" s="1">
+      <c r="AF35" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C36" s="1">
         <v>3003</v>
       </c>
@@ -3580,64 +3424,64 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="H36" s="1">
-        <v>1</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="J36" s="5" t="s">
+        <v>87</v>
       </c>
       <c r="K36" s="1">
-        <v>10</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>118</v>
+        <v>0</v>
+      </c>
+      <c r="L36" s="1">
+        <v>0</v>
       </c>
       <c r="M36" s="1">
         <v>10</v>
       </c>
-      <c r="N36" s="1">
+      <c r="N36" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="O36" s="1">
+        <v>10</v>
+      </c>
+      <c r="P36" s="1">
         <v>5</v>
       </c>
-      <c r="O36" s="1">
+      <c r="Q36" s="1">
         <v>3</v>
       </c>
-      <c r="P36" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q36" s="1">
+      <c r="R36" s="1">
+        <v>10</v>
+      </c>
+      <c r="S36" s="1">
         <v>80</v>
-      </c>
-      <c r="R36" s="1">
-        <v>800</v>
-      </c>
-      <c r="S36" s="1">
-        <v>5</v>
       </c>
       <c r="T36" s="1">
         <v>800</v>
       </c>
       <c r="U36" s="1">
+        <v>5</v>
+      </c>
+      <c r="V36" s="1">
+        <v>800</v>
+      </c>
+      <c r="W36" s="1">
         <v>4</v>
       </c>
-      <c r="V36" s="1">
-        <v>1</v>
-      </c>
-      <c r="W36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X36" s="1" t="s">
-        <v>92</v>
+      <c r="X36" s="1">
+        <v>3</v>
       </c>
       <c r="Y36" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z36" s="1">
         <v>0</v>
@@ -3654,15 +3498,12 @@
       <c r="AD36" s="1">
         <v>0</v>
       </c>
-      <c r="AE36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF36" s="1"/>
-      <c r="AG36" s="1">
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C37" s="1">
         <v>3004</v>
       </c>
@@ -3673,43 +3514,43 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="H37" s="1">
-        <v>4</v>
-      </c>
-      <c r="I37" s="1">
+        <v>8</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J37" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="K37" s="1">
         <v>6</v>
       </c>
-      <c r="J37" s="1">
-        <v>0</v>
-      </c>
-      <c r="K37" s="1">
+      <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
         <v>100</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="M37" s="1">
-        <v>10</v>
-      </c>
-      <c r="N37" s="1">
-        <v>0</v>
+      <c r="N37" s="1" t="s">
+        <v>114</v>
       </c>
       <c r="O37" s="1">
+        <v>10</v>
+      </c>
+      <c r="P37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1">
         <v>3</v>
       </c>
-      <c r="P37" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q37" s="1">
-        <v>1000</v>
-      </c>
       <c r="R37" s="1">
-        <v>100000</v>
+        <v>10</v>
       </c>
       <c r="S37" s="1">
         <v>1000</v>
@@ -3718,19 +3559,19 @@
         <v>100000</v>
       </c>
       <c r="U37" s="1">
+        <v>1000</v>
+      </c>
+      <c r="V37" s="1">
+        <v>100000</v>
+      </c>
+      <c r="W37" s="1">
         <v>5</v>
       </c>
-      <c r="V37" s="1">
-        <v>1</v>
-      </c>
-      <c r="W37" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X37" s="1" t="s">
-        <v>86</v>
+      <c r="X37" s="1">
+        <v>3</v>
       </c>
       <c r="Y37" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z37" s="1">
         <v>0</v>
@@ -3747,14 +3588,11 @@
       <c r="AD37" s="1">
         <v>0</v>
       </c>
-      <c r="AE37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG37" s="1">
+      <c r="AF37" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C38" s="1">
         <v>3005</v>
       </c>
@@ -3765,61 +3603,58 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H38" s="1">
+        <v>6</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="K38" s="1">
         <v>5</v>
       </c>
-      <c r="I38" s="1">
-        <v>5</v>
-      </c>
-      <c r="J38" s="1">
-        <v>0</v>
-      </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
         <v>50</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M38" s="1">
+      <c r="N38" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="O38" s="1">
         <v>60</v>
       </c>
-      <c r="N38" s="1">
+      <c r="P38" s="1">
         <v>30</v>
       </c>
-      <c r="O38" s="1">
+      <c r="Q38" s="1">
         <v>3</v>
       </c>
-      <c r="P38" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q38" s="1">
+      <c r="R38" s="1">
+        <v>10</v>
+      </c>
+      <c r="S38" s="1">
         <v>50</v>
-      </c>
-      <c r="R38" s="1">
-        <v>50</v>
-      </c>
-      <c r="S38" s="1">
-        <v>10</v>
       </c>
       <c r="T38" s="1">
         <v>50</v>
       </c>
       <c r="U38" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V38" s="1">
-        <v>1</v>
-      </c>
-      <c r="W38" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X38" s="1" t="s">
-        <v>82</v>
+        <v>50</v>
+      </c>
+      <c r="W38" s="1">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1">
+        <v>0</v>
       </c>
       <c r="Y38" s="1">
         <v>0</v>
@@ -3839,15 +3674,12 @@
       <c r="AD38" s="1">
         <v>0</v>
       </c>
-      <c r="AE38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF38" s="5"/>
-      <c r="AG38" s="1">
+      <c r="AE38" s="6"/>
+      <c r="AF38" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C39" s="1">
         <v>3006</v>
       </c>
@@ -3858,43 +3690,40 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="H39" s="1">
-        <v>6</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="I39" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="K39" s="1">
-        <v>10</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>127</v>
+        <v>0</v>
+      </c>
+      <c r="L39" s="1">
+        <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>0</v>
-      </c>
-      <c r="N39" s="1">
-        <v>0</v>
+        <v>10</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>120</v>
       </c>
       <c r="O39" s="1">
+        <v>0</v>
+      </c>
+      <c r="P39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="1">
         <v>3</v>
       </c>
-      <c r="P39" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q39" s="1">
-        <v>1</v>
-      </c>
       <c r="R39" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S39" s="1">
         <v>1</v>
@@ -3903,16 +3732,16 @@
         <v>0</v>
       </c>
       <c r="U39" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" s="1">
         <v>0</v>
       </c>
-      <c r="W39" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X39" s="1" t="s">
-        <v>86</v>
+      <c r="W39" s="1">
+        <v>0</v>
+      </c>
+      <c r="X39" s="1">
+        <v>0</v>
       </c>
       <c r="Y39" s="1">
         <v>0</v>
@@ -3932,14 +3761,11 @@
       <c r="AD39" s="1">
         <v>0</v>
       </c>
-      <c r="AE39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG39" s="1">
+      <c r="AF39" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C40" s="1">
         <v>3007</v>
       </c>
@@ -3950,64 +3776,61 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="H40" s="1">
-        <v>2</v>
-      </c>
-      <c r="I40" s="1">
+        <v>4</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="K40" s="1">
         <v>6</v>
       </c>
-      <c r="J40" s="1">
-        <v>0</v>
-      </c>
-      <c r="K40" s="1">
+      <c r="L40" s="1">
+        <v>0</v>
+      </c>
+      <c r="M40" s="1">
         <v>100</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="M40" s="1">
+      <c r="N40" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="O40" s="1">
         <v>30</v>
       </c>
-      <c r="N40" s="1">
-        <v>0</v>
-      </c>
-      <c r="O40" s="1">
+      <c r="P40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="1">
         <v>3</v>
       </c>
-      <c r="P40" s="1">
-        <v>10</v>
-      </c>
-      <c r="Q40" s="1">
+      <c r="R40" s="1">
+        <v>10</v>
+      </c>
+      <c r="S40" s="1">
         <v>200</v>
-      </c>
-      <c r="R40" s="1">
-        <v>8000</v>
-      </c>
-      <c r="S40" s="1">
-        <v>40</v>
       </c>
       <c r="T40" s="1">
         <v>8000</v>
       </c>
       <c r="U40" s="1">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V40" s="1">
-        <v>1</v>
-      </c>
-      <c r="W40" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="X40" s="1" t="s">
-        <v>82</v>
+        <v>8000</v>
+      </c>
+      <c r="W40" s="1">
+        <v>0</v>
+      </c>
+      <c r="X40" s="1">
+        <v>2</v>
       </c>
       <c r="Y40" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z40" s="1">
         <v>0</v>
@@ -4024,23 +3847,20 @@
       <c r="AD40" s="1">
         <v>0</v>
       </c>
-      <c r="AE40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG40" s="1">
+      <c r="AF40" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G41" s="2"/>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G42" s="2"/>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G43" s="2"/>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C44" s="1">
         <v>4001</v>
       </c>
@@ -4051,38 +3871,35 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H44" s="1">
-        <v>4001</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="K44" s="1">
+        <v>0</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
         <v>-100</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M44" s="1">
+      <c r="N44" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="O44" s="1">
         <v>30</v>
       </c>
-      <c r="N44" s="1">
+      <c r="P44" s="1">
         <v>2</v>
       </c>
-      <c r="O44" s="1">
-        <v>0</v>
-      </c>
-      <c r="P44" s="1">
-        <v>0</v>
-      </c>
       <c r="Q44" s="1">
         <v>0</v>
       </c>
@@ -4101,11 +3918,11 @@
       <c r="V44" s="1">
         <v>0</v>
       </c>
-      <c r="W44" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X44" s="1" t="s">
-        <v>82</v>
+      <c r="W44" s="1">
+        <v>0</v>
+      </c>
+      <c r="X44" s="1">
+        <v>0</v>
       </c>
       <c r="Y44" s="1">
         <v>0</v>
@@ -4125,15 +3942,12 @@
       <c r="AD44" s="1">
         <v>0</v>
       </c>
-      <c r="AE44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF44" s="1"/>
-      <c r="AG44" s="1">
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C45" s="1">
         <v>4002</v>
       </c>
@@ -4144,61 +3958,58 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="H45" s="1">
-        <v>4002</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="K45" s="1">
+        <v>0</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
         <v>200</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="M45" s="1">
+      <c r="N45" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="O45" s="1">
         <v>60</v>
       </c>
-      <c r="N45" s="1">
-        <v>0</v>
-      </c>
-      <c r="O45" s="1">
-        <v>0</v>
-      </c>
       <c r="P45" s="1">
         <v>0</v>
       </c>
       <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>0</v>
+      </c>
+      <c r="S45" s="1">
         <v>100</v>
       </c>
-      <c r="R45" s="1">
-        <v>0</v>
-      </c>
-      <c r="S45" s="1">
-        <v>10</v>
-      </c>
       <c r="T45" s="1">
         <v>0</v>
       </c>
       <c r="U45" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V45" s="1">
         <v>0</v>
       </c>
-      <c r="W45" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X45" s="1" t="s">
-        <v>82</v>
+      <c r="W45" s="1">
+        <v>0</v>
+      </c>
+      <c r="X45" s="1">
+        <v>0</v>
       </c>
       <c r="Y45" s="1">
         <v>0</v>
@@ -4218,15 +4029,12 @@
       <c r="AD45" s="1">
         <v>0</v>
       </c>
-      <c r="AE45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF45" s="5"/>
-      <c r="AG45" s="1">
+      <c r="AE45" s="6"/>
+      <c r="AF45" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C46" s="1">
         <v>4003</v>
       </c>
@@ -4237,47 +4045,44 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="H46" s="1">
-        <v>4003</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
-      <c r="J46" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="K46" s="1">
+        <v>0</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
         <v>-1</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="M46" s="1">
+      <c r="N46" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="O46" s="1">
         <v>60</v>
       </c>
-      <c r="N46" s="1">
-        <v>0</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
       <c r="P46" s="1">
         <v>0</v>
       </c>
       <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
         <v>100</v>
       </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
       <c r="T46" s="1">
         <v>0</v>
       </c>
@@ -4287,11 +4092,11 @@
       <c r="V46" s="1">
         <v>0</v>
       </c>
-      <c r="W46" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X46" s="1" t="s">
-        <v>82</v>
+      <c r="W46" s="1">
+        <v>0</v>
+      </c>
+      <c r="X46" s="1">
+        <v>0</v>
       </c>
       <c r="Y46" s="1">
         <v>0</v>
@@ -4311,22 +4116,19 @@
       <c r="AD46" s="1">
         <v>0</v>
       </c>
-      <c r="AE46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AF46" s="1"/>
-      <c r="AG46" s="1">
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G47" s="2"/>
     </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C49" s="1">
         <v>9001</v>
       </c>
@@ -4337,29 +4139,29 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="H49" s="1">
-        <v>9</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="I49" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>65</v>
       </c>
       <c r="K49" s="1">
         <v>0</v>
       </c>
+      <c r="L49" s="1">
+        <v>0</v>
+      </c>
       <c r="M49" s="1">
         <v>0</v>
       </c>
-      <c r="N49" s="1">
-        <v>0</v>
-      </c>
       <c r="O49" s="1">
         <v>0</v>
       </c>
@@ -4367,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+      <c r="S49" s="1">
         <v>100</v>
       </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1">
+      <c r="T49" s="1">
         <v>0</v>
       </c>
       <c r="U49" s="1">
+        <v>0</v>
+      </c>
+      <c r="W49" s="1">
         <v>1</v>
       </c>
-      <c r="V49" s="1">
+      <c r="X49" s="1">
         <v>1</v>
       </c>
-      <c r="W49" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="X49" s="1" t="s">
-        <v>92</v>
-      </c>
       <c r="Y49" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z49" s="1">
         <v>0</v>
@@ -4405,29 +4207,26 @@
       <c r="AD49" s="1">
         <v>0</v>
       </c>
-      <c r="AE49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG49" s="1">
+      <c r="AF49" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1"/>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G51" s="2"/>
     </row>
-    <row r="52" customHeight="1" spans="3:33">
+    <row r="52" customHeight="1" spans="3:32">
       <c r="E52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
-      <c r="S52" s="1"/>
       <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
       <c r="V52" s="1"/>
-      <c r="W52" s="1"/>
-      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
@@ -4435,14 +4234,13 @@
       <c r="AD52" s="1"/>
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
-      <c r="AG52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="3:33">
+    </row>
+    <row r="53" customHeight="1" spans="3:32">
       <c r="E53" s="1"/>
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
@@ -4460,111 +4258,97 @@
       <c r="AD53" s="1"/>
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
-      <c r="AG53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="3:33">
+    </row>
+    <row r="54" customHeight="1" spans="3:32">
       <c r="E54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="S54" s="1"/>
-      <c r="T54" s="1"/>
+      <c r="K54" s="1"/>
+      <c r="L54" s="1"/>
+      <c r="U54" s="1"/>
       <c r="V54" s="1"/>
+      <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
-      <c r="AB54" s="1"/>
-      <c r="AG54" s="1"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF54" s="1"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="1"/>
-      <c r="P55" s="2"/>
+      <c r="N55" s="2"/>
+      <c r="O55" s="1"/>
+      <c r="R55" s="2"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1"/>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G58" s="2"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G59" s="2"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1"/>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G61" s="2"/>
       <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="AF61" s="5"/>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AE61" s="6"/>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G62" s="2"/>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G63" s="2"/>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1"/>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G65" s="2"/>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G66" s="2"/>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G67" s="2"/>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G68" s="2"/>
       <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="AF68" s="5"/>
+      <c r="AE68" s="6"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1"/>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G70" s="2"/>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G71" s="2"/>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1"/>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G73" s="2"/>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G74" s="2"/>
     </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G75" s="2"/>
       <c r="H75" s="1"/>
-      <c r="I75" s="1"/>
-      <c r="J75" s="1"/>
-      <c r="K75" s="1"/>
-      <c r="AF75" s="5"/>
+      <c r="AE75" s="6"/>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1"/>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G77" s="2"/>
     </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-      <c r="L78" s="2"/>
-      <c r="P78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="T78" s="2"/>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:32">
+      <c r="N78" s="2"/>
+      <c r="R78" s="2"/>
+      <c r="U78" s="2"/>
+      <c r="V78" s="2"/>
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G79" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:M5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:O5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -692,7 +692,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -711,12 +711,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1199,133 +1193,133 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1333,13 +1327,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1661,310 +1655,310 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="C2:AF79"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="3.50833333333333" style="2" customWidth="1"/>
-    <col min="3" max="5" width="9" style="2"/>
-    <col min="6" max="6" width="11.5083333333333" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9" style="2" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
-    <col min="9" max="10" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.33333333333333" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.25" style="2" customWidth="1"/>
-    <col min="14" max="14" width="57.25" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="6.50833333333333" style="2" customWidth="1"/>
-    <col min="17" max="17" width="7.16666666666667" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="19" max="20" width="7.875" style="2" customWidth="1"/>
-    <col min="21" max="21" width="8.66666666666667" style="2" customWidth="1"/>
-    <col min="22" max="22" width="9.5" style="2" customWidth="1"/>
-    <col min="23" max="23" width="7.375" style="2" customWidth="1"/>
-    <col min="24" max="26" width="7.625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="9.625" style="2" customWidth="1"/>
-    <col min="28" max="29" width="7.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="9.75" style="2" customWidth="1"/>
-    <col min="31" max="31" width="21.75" style="2" customWidth="1"/>
-    <col min="32" max="32" width="11.75" style="2" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="5.625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="3.50833333333333" style="3" customWidth="1"/>
+    <col min="3" max="5" width="9" style="3"/>
+    <col min="6" max="6" width="11.5083333333333" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9" style="3" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="3" customWidth="1"/>
+    <col min="9" max="10" width="7.50833333333333" style="3" customWidth="1"/>
+    <col min="11" max="11" width="9.375" style="3" customWidth="1"/>
+    <col min="12" max="12" width="9.33333333333333" style="3" customWidth="1"/>
+    <col min="13" max="13" width="5.25" style="3" customWidth="1"/>
+    <col min="14" max="14" width="57.25" style="3" customWidth="1"/>
+    <col min="15" max="15" width="5.875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="6.50833333333333" style="3" customWidth="1"/>
+    <col min="17" max="17" width="7.16666666666667" style="3" customWidth="1"/>
+    <col min="18" max="18" width="7.50833333333333" style="3" customWidth="1"/>
+    <col min="19" max="20" width="7.875" style="3" customWidth="1"/>
+    <col min="21" max="21" width="8.66666666666667" style="3" customWidth="1"/>
+    <col min="22" max="22" width="9.5" style="3" customWidth="1"/>
+    <col min="23" max="23" width="7.375" style="3" customWidth="1"/>
+    <col min="24" max="26" width="7.625" style="3" customWidth="1"/>
+    <col min="27" max="27" width="9.625" style="3" customWidth="1"/>
+    <col min="28" max="29" width="7.875" style="3" customWidth="1"/>
+    <col min="30" max="30" width="9.75" style="3" customWidth="1"/>
+    <col min="31" max="31" width="21.75" style="3" customWidth="1"/>
+    <col min="32" max="32" width="11.75" style="3" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" ht="33" customHeight="1" spans="3:32">
-      <c r="N2" s="3"/>
+    <row r="2" customHeight="1" spans="3:32">
+      <c r="N2" s="4"/>
     </row>
     <row r="3" customHeight="1" spans="3:32">
-      <c r="C3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="s">
+      <c r="C3" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="O3" s="4" t="s">
+      <c r="N3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="4" t="s">
+      <c r="Q3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="4" t="s">
+      <c r="R3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="S3" s="4" t="s">
+      <c r="S3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="T3" s="4" t="s">
+      <c r="T3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="4" t="s">
+      <c r="U3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="4" t="s">
+      <c r="V3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="4" t="s">
+      <c r="W3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="X3" s="4" t="s">
+      <c r="X3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="Y3" s="4" t="s">
+      <c r="Y3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="Z3" s="4" t="s">
+      <c r="Z3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AA3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="AB3" s="4" t="s">
+      <c r="AB3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="AC3" s="4" t="s">
+      <c r="AC3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="AD3" s="4" t="s">
+      <c r="AD3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="AE3" s="4" t="s">
+      <c r="AE3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="AF3" s="4" t="s">
+      <c r="AF3" s="5" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="3:32">
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="N4" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="Q4" s="4" t="s">
+      <c r="Q4" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="R4" s="4" t="s">
+      <c r="R4" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="4" t="s">
+      <c r="S4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="U4" s="4" t="s">
+      <c r="U4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="V4" s="4" t="s">
+      <c r="V4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="W4" s="4" t="s">
+      <c r="W4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="X4" s="4" t="s">
+      <c r="X4" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Y4" s="4" t="s">
+      <c r="Y4" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="4" t="s">
+      <c r="Z4" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AA4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="AB4" s="4" t="s">
+      <c r="AB4" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="AC4" s="4" t="s">
+      <c r="AC4" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="AD4" s="4" t="s">
+      <c r="AD4" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="AE4" s="4" t="s">
+      <c r="AE4" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="AF4" s="4" t="s">
+      <c r="AF4" s="5" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="3:32">
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="R5" s="4" t="s">
+      <c r="R5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="S5" s="4" t="s">
+      <c r="S5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="T5" s="4" t="s">
+      <c r="T5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="U5" s="4" t="s">
+      <c r="U5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="V5" s="4" t="s">
+      <c r="V5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="W5" s="4" t="s">
+      <c r="W5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="X5" s="4" t="s">
+      <c r="X5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="Y5" s="4" t="s">
+      <c r="Y5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="Z5" s="4" t="s">
+      <c r="Z5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AA5" s="4" t="s">
+      <c r="AA5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AB5" s="4" t="s">
+      <c r="AB5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AC5" s="4" t="s">
+      <c r="AC5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AD5" s="4" t="s">
+      <c r="AD5" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="AE5" s="4" t="s">
+      <c r="AE5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="AF5" s="4" t="s">
+      <c r="AF5" s="5" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2065,7 +2059,7 @@
       <c r="F7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>64</v>
       </c>
       <c r="H7" s="1">
@@ -2074,7 +2068,7 @@
       <c r="I7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="1" t="s">
         <v>65</v>
       </c>
       <c r="K7" s="1">
@@ -2154,7 +2148,7 @@
       <c r="F8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="3" t="s">
         <v>68</v>
       </c>
       <c r="H8" s="1">
@@ -2163,7 +2157,7 @@
       <c r="I8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K8" s="1">
@@ -2329,7 +2323,7 @@
       <c r="F10" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="3" t="s">
         <v>75</v>
       </c>
       <c r="H10" s="1">
@@ -2416,7 +2410,7 @@
       <c r="F11" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="3" t="s">
         <v>78</v>
       </c>
       <c r="H11" s="1">
@@ -2502,7 +2496,7 @@
       <c r="F12" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="G12" s="3" t="s">
         <v>81</v>
       </c>
       <c r="H12" s="1">
@@ -2511,7 +2505,7 @@
       <c r="I12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="1" t="s">
         <v>65</v>
       </c>
       <c r="K12" s="1">
@@ -2580,25 +2574,25 @@
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" customFormat="1" customHeight="1" spans="3:32">
+      <c r="G13" s="3"/>
+    </row>
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="AE14" s="1"/>
     </row>
-    <row r="15" customFormat="1" customHeight="1" spans="3:32">
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="AE15" s="1"/>
     </row>
-    <row r="16" customFormat="1" customHeight="1" spans="3:32">
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="AE16" s="1"/>
     </row>
-    <row r="17" customFormat="1" customHeight="1" spans="3:32">
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="AE17" s="1"/>
     </row>
-    <row r="18" customFormat="1" customHeight="1" spans="3:32">
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="AE18" s="1"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G19" s="2"/>
+      <c r="G19" s="3"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C20" s="1">
@@ -2697,7 +2691,7 @@
       <c r="F21" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="2" t="s">
+      <c r="G21" s="3" t="s">
         <v>86</v>
       </c>
       <c r="H21" s="1">
@@ -2706,7 +2700,7 @@
       <c r="I21" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="1" t="s">
         <v>87</v>
       </c>
       <c r="K21" s="1">
@@ -2786,7 +2780,7 @@
       <c r="F22" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G22" s="2" t="s">
+      <c r="G22" s="3" t="s">
         <v>90</v>
       </c>
       <c r="H22" s="1">
@@ -2795,7 +2789,7 @@
       <c r="I22" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K22" s="1">
@@ -2875,7 +2869,7 @@
       <c r="F23" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="G23" s="3" t="s">
         <v>93</v>
       </c>
       <c r="H23" s="1">
@@ -2884,7 +2878,7 @@
       <c r="I23" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K23" s="1">
@@ -2965,7 +2959,7 @@
       <c r="F24" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="G24" s="2" t="s">
+      <c r="G24" s="3" t="s">
         <v>96</v>
       </c>
       <c r="H24" s="1">
@@ -3138,7 +3132,7 @@
       <c r="F26" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="G26" s="2" t="s">
+      <c r="G26" s="3" t="s">
         <v>102</v>
       </c>
       <c r="H26" s="1">
@@ -3147,7 +3141,7 @@
       <c r="I26" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="1" t="s">
         <v>70</v>
       </c>
       <c r="K26" s="1">
@@ -3216,29 +3210,29 @@
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G27" s="2"/>
+      <c r="G27" s="3"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G28" s="2"/>
+      <c r="G28" s="3"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G29" s="2"/>
+      <c r="G29" s="3"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G30" s="2"/>
+      <c r="G30" s="3"/>
       <c r="H30" s="1"/>
-      <c r="N30" s="2"/>
+      <c r="N30" s="3"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G31" s="2"/>
+      <c r="G31" s="3"/>
       <c r="H31" s="1"/>
-      <c r="N31" s="2"/>
+      <c r="N31" s="3"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="N32" s="2"/>
+      <c r="N32" s="3"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G33" s="2"/>
+      <c r="G33" s="3"/>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C34" s="1">
@@ -3253,7 +3247,7 @@
       <c r="F34" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="G34" s="2"/>
+      <c r="G34" s="3"/>
       <c r="H34" s="1">
         <v>1</v>
       </c>
@@ -3346,7 +3340,7 @@
       <c r="I35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J35" s="5" t="s">
+      <c r="J35" s="1" t="s">
         <v>87</v>
       </c>
       <c r="K35" s="1">
@@ -3426,7 +3420,7 @@
       <c r="F36" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G36" s="3" t="s">
         <v>110</v>
       </c>
       <c r="H36" s="1">
@@ -3435,7 +3429,7 @@
       <c r="I36" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="1" t="s">
         <v>87</v>
       </c>
       <c r="K36" s="1">
@@ -3516,7 +3510,7 @@
       <c r="F37" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G37" s="2" t="s">
+      <c r="G37" s="3" t="s">
         <v>113</v>
       </c>
       <c r="H37" s="1">
@@ -3525,7 +3519,7 @@
       <c r="I37" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="1" t="s">
         <v>87</v>
       </c>
       <c r="K37" s="1">
@@ -3605,7 +3599,7 @@
       <c r="F38" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="G38" s="2" t="s">
+      <c r="G38" s="3" t="s">
         <v>116</v>
       </c>
       <c r="H38" s="1">
@@ -3778,7 +3772,7 @@
       <c r="F40" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G40" s="2" t="s">
+      <c r="G40" s="3" t="s">
         <v>122</v>
       </c>
       <c r="H40" s="1">
@@ -3852,13 +3846,13 @@
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G41" s="2"/>
+      <c r="G41" s="3"/>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G42" s="2"/>
+      <c r="G42" s="3"/>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G43" s="2"/>
+      <c r="G43" s="3"/>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C44" s="1">
@@ -3870,10 +3864,10 @@
       <c r="E44" s="1">
         <v>0</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="F44" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="G44" s="3" t="s">
         <v>125</v>
       </c>
       <c r="H44" s="1">
@@ -3957,10 +3951,10 @@
       <c r="E45" s="1">
         <v>0</v>
       </c>
-      <c r="F45" s="2" t="s">
+      <c r="F45" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="G45" s="3" t="s">
         <v>128</v>
       </c>
       <c r="H45" s="1">
@@ -4044,10 +4038,10 @@
       <c r="E46" s="1">
         <v>0</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F46" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="G46" s="3" t="s">
         <v>131</v>
       </c>
       <c r="H46" s="1">
@@ -4122,11 +4116,11 @@
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G47" s="2"/>
+      <c r="G47" s="3"/>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C49" s="1">
@@ -4150,7 +4144,7 @@
       <c r="I49" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="J49" s="5" t="s">
+      <c r="J49" s="1" t="s">
         <v>65</v>
       </c>
       <c r="K49" s="1">
@@ -4213,7 +4207,7 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1"/>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G51" s="2"/>
+      <c r="G51" s="3"/>
     </row>
     <row r="52" customHeight="1" spans="3:32">
       <c r="E52" s="1"/>
@@ -4271,80 +4265,80 @@
       <c r="AF54" s="1"/>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
       <c r="H55" s="1"/>
-      <c r="N55" s="2"/>
+      <c r="N55" s="3"/>
       <c r="O55" s="1"/>
-      <c r="R55" s="2"/>
+      <c r="R55" s="3"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1"/>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G58" s="2"/>
+      <c r="G58" s="3"/>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G59" s="2"/>
+      <c r="G59" s="3"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1"/>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G61" s="2"/>
+      <c r="G61" s="3"/>
       <c r="H61" s="1"/>
       <c r="AE61" s="6"/>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G62" s="2"/>
+      <c r="G62" s="3"/>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G63" s="2"/>
+      <c r="G63" s="3"/>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1"/>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G65" s="2"/>
+      <c r="G65" s="3"/>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G66" s="2"/>
+      <c r="G66" s="3"/>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G67" s="2"/>
+      <c r="G67" s="3"/>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G68" s="2"/>
+      <c r="G68" s="3"/>
       <c r="H68" s="1"/>
       <c r="AE68" s="6"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1"/>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G70" s="2"/>
+      <c r="G70" s="3"/>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G71" s="2"/>
+      <c r="G71" s="3"/>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1"/>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G73" s="2"/>
+      <c r="G73" s="3"/>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G74" s="2"/>
+      <c r="G74" s="3"/>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G75" s="2"/>
+      <c r="G75" s="3"/>
       <c r="H75" s="1"/>
       <c r="AE75" s="6"/>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1"/>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G77" s="2"/>
+      <c r="G77" s="3"/>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="U78" s="2"/>
-      <c r="V78" s="2"/>
+      <c r="F78" s="3"/>
+      <c r="G78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="R78" s="3"/>
+      <c r="U78" s="3"/>
+      <c r="V78" s="3"/>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G79" s="2"/>
+      <c r="G79" s="3"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -278,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="135">
   <si>
     <t>_ID</t>
   </si>
@@ -481,7 +481,7 @@
     <t>对直线攻击距离内的敌人造成{0}%物攻+{1}点技能伤害</t>
   </si>
   <si>
-    <t>四方剑阵</t>
+    <t>月华剑阵</t>
   </si>
   <si>
     <t>剑二十三</t>
@@ -496,13 +496,16 @@
     <t>施展{4}*{5}范围的剑阵，持续{2}s，对其内的敌人造成{0}%物攻+{1}点伤害，按攻速结算</t>
   </si>
   <si>
-    <t>背刺剑法</t>
+    <t>蛮牛冲撞</t>
+  </si>
+  <si>
+    <t>野蛮</t>
   </si>
   <si>
     <t>瞬移到敌人身后造成{0}%物攻+{1}点技能伤害，并且晕眩{2}秒</t>
   </si>
   <si>
-    <t>武神盾</t>
+    <t>龙魂护体</t>
   </si>
   <si>
     <t>武力盾</t>
@@ -535,7 +538,7 @@
     <t>被动增加{0}%的魔攻加成和{1}点魔攻，无需上阵</t>
   </si>
   <si>
-    <t>神雷术</t>
+    <t>紫电神雷</t>
   </si>
   <si>
     <t>雷电术</t>
@@ -547,7 +550,7 @@
     <t>对{3}个敌人造成{0}%魔法+{1}点技能伤害</t>
   </si>
   <si>
-    <t>火海术</t>
+    <t>火狱阵法</t>
   </si>
   <si>
     <t>火墙</t>
@@ -556,7 +559,7 @@
     <t>施展{4}*{5}范围的烈焰，持续{2}s，对其内的敌人造成{0}%魔法+{1}点伤害，按攻速结算</t>
   </si>
   <si>
-    <t>烈焰术</t>
+    <t>烈焰焚天</t>
   </si>
   <si>
     <t>抗拒火环</t>
@@ -565,7 +568,7 @@
     <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点技能伤害</t>
   </si>
   <si>
-    <t>念力盾</t>
+    <t>炎凰法盾</t>
   </si>
   <si>
     <t>魔法盾</t>
@@ -574,7 +577,7 @@
     <t>提高人物{0}魔攻，并且生成一个{1}%生命的护盾，持续{2}秒</t>
   </si>
   <si>
-    <t>冰心诀</t>
+    <t>万法归宗</t>
   </si>
   <si>
     <t>法术精通</t>
@@ -583,7 +586,7 @@
     <t>法师技能增加{0}%技能系数增幅，无需上阵</t>
   </si>
   <si>
-    <t>冰封术</t>
+    <t>极寒冰暴</t>
   </si>
   <si>
     <t>冰咆哮</t>
@@ -592,13 +595,13 @@
     <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点伤害，冰封所有敌人2秒</t>
   </si>
   <si>
-    <t>祈福心法</t>
+    <t>清心咒</t>
   </si>
   <si>
     <t>被动增加{0}%的道攻加成和{1}点道攻，无需上阵</t>
   </si>
   <si>
-    <t>灭魔符</t>
+    <t>破魔符咒</t>
   </si>
   <si>
     <t>火符术</t>
@@ -616,7 +619,7 @@
     <t>对{3}个敌人造成{0}%道术+{1}点技能伤害的持续{2}秒，按攻速结算</t>
   </si>
   <si>
-    <t>疗伤术</t>
+    <t>圣疗术</t>
   </si>
   <si>
     <t>治疗术</t>
@@ -625,7 +628,7 @@
     <t>恢复自己和队友的{0}%道术+{1}点生命</t>
   </si>
   <si>
-    <t>护魂盾</t>
+    <t>太虚麟盾</t>
   </si>
   <si>
     <t>道力盾</t>
@@ -634,7 +637,7 @@
     <t>提高人物{0}生命，并且生成一个{1}%生命的护盾，持续{2}秒</t>
   </si>
   <si>
-    <t>圣心诀</t>
+    <t>道法自然</t>
   </si>
   <si>
     <t>道力精通</t>
@@ -643,7 +646,7 @@
     <t>被动道士技能增加{0}%技能系数增幅，无需上阵</t>
   </si>
   <si>
-    <t>唤神咒</t>
+    <t>召唤英灵</t>
   </si>
   <si>
     <t>召唤神兽</t>
@@ -858,12 +861,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1323,10 +1326,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1657,308 +1659,308 @@
   <dimension ref="C2:AF79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="5.625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="3.50833333333333" style="3" customWidth="1"/>
-    <col min="3" max="5" width="9" style="3"/>
-    <col min="6" max="6" width="11.5083333333333" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9" style="3" customWidth="1"/>
-    <col min="8" max="8" width="9.25" style="3" customWidth="1"/>
-    <col min="9" max="10" width="7.50833333333333" style="3" customWidth="1"/>
-    <col min="11" max="11" width="9.375" style="3" customWidth="1"/>
-    <col min="12" max="12" width="9.33333333333333" style="3" customWidth="1"/>
-    <col min="13" max="13" width="5.25" style="3" customWidth="1"/>
-    <col min="14" max="14" width="57.25" style="3" customWidth="1"/>
-    <col min="15" max="15" width="5.875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="6.50833333333333" style="3" customWidth="1"/>
-    <col min="17" max="17" width="7.16666666666667" style="3" customWidth="1"/>
-    <col min="18" max="18" width="7.50833333333333" style="3" customWidth="1"/>
-    <col min="19" max="20" width="7.875" style="3" customWidth="1"/>
-    <col min="21" max="21" width="8.66666666666667" style="3" customWidth="1"/>
-    <col min="22" max="22" width="9.5" style="3" customWidth="1"/>
-    <col min="23" max="23" width="7.375" style="3" customWidth="1"/>
-    <col min="24" max="26" width="7.625" style="3" customWidth="1"/>
-    <col min="27" max="27" width="9.625" style="3" customWidth="1"/>
-    <col min="28" max="29" width="7.875" style="3" customWidth="1"/>
-    <col min="30" max="30" width="9.75" style="3" customWidth="1"/>
-    <col min="31" max="31" width="21.75" style="3" customWidth="1"/>
-    <col min="32" max="32" width="11.75" style="3" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="3.50833333333333" style="2" customWidth="1"/>
+    <col min="3" max="5" width="9" style="2"/>
+    <col min="6" max="6" width="11.5083333333333" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9" style="2" customWidth="1"/>
+    <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
+    <col min="9" max="10" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="11" max="11" width="9.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.33333333333333" style="2" customWidth="1"/>
+    <col min="13" max="13" width="5.25" style="2" customWidth="1"/>
+    <col min="14" max="14" width="57.25" style="2" customWidth="1"/>
+    <col min="15" max="15" width="5.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="6.50833333333333" style="2" customWidth="1"/>
+    <col min="17" max="17" width="7.16666666666667" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="19" max="20" width="7.875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="8.66666666666667" style="2" customWidth="1"/>
+    <col min="22" max="22" width="9.5" style="2" customWidth="1"/>
+    <col min="23" max="23" width="7.375" style="2" customWidth="1"/>
+    <col min="24" max="26" width="7.625" style="2" customWidth="1"/>
+    <col min="27" max="27" width="9.625" style="2" customWidth="1"/>
+    <col min="28" max="29" width="7.875" style="2" customWidth="1"/>
+    <col min="30" max="30" width="9.75" style="2" customWidth="1"/>
+    <col min="31" max="31" width="21.75" style="2" customWidth="1"/>
+    <col min="32" max="32" width="11.75" style="2" customWidth="1"/>
+    <col min="33" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="2" customHeight="1" spans="3:32">
-      <c r="N2" s="4"/>
+      <c r="N2" s="3"/>
     </row>
     <row r="3" customHeight="1" spans="3:32">
-      <c r="C3" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="O3" s="5" t="s">
+      <c r="N3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="P3" s="5" t="s">
+      <c r="P3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="5" t="s">
+      <c r="Q3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="R3" s="5" t="s">
+      <c r="R3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="S3" s="5" t="s">
+      <c r="S3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="T3" s="5" t="s">
+      <c r="T3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="V3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="5" t="s">
+      <c r="W3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="X3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Y3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="Z3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="AA3" s="5" t="s">
+      <c r="AA3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="AB3" s="5" t="s">
+      <c r="AB3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AC3" s="5" t="s">
+      <c r="AC3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="AD3" s="5" t="s">
+      <c r="AD3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AE3" s="5" t="s">
+      <c r="AE3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="AF3" s="5" t="s">
+      <c r="AF3" s="4" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="3:32">
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="K4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M4" s="5" t="s">
+      <c r="M4" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="N4" s="5" t="s">
+      <c r="N4" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="O4" s="5" t="s">
+      <c r="O4" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="5" t="s">
+      <c r="P4" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="Q4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="R4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="S4" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="T4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="U4" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="V4" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="W4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="X4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Y4" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="Z4" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AA4" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AB4" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AC4" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="AD4" s="5" t="s">
+      <c r="AD4" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="AE4" s="5" t="s">
+      <c r="AE4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="AF4" s="5" t="s">
+      <c r="AF4" s="4" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="3:32">
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="5" t="s">
+      <c r="K5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="L5" s="5" t="s">
+      <c r="L5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M5" s="5" t="s">
+      <c r="M5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="N5" s="5" t="s">
+      <c r="N5" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="O5" s="5" t="s">
+      <c r="O5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="Q5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R5" s="5" t="s">
+      <c r="R5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S5" s="5" t="s">
+      <c r="S5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="T5" s="5" t="s">
+      <c r="T5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="U5" s="5" t="s">
+      <c r="U5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="V5" s="5" t="s">
+      <c r="V5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="W5" s="5" t="s">
+      <c r="W5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="X5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="Y5" s="5" t="s">
+      <c r="Y5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="Z5" s="5" t="s">
+      <c r="Z5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AA5" s="5" t="s">
+      <c r="AA5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AB5" s="5" t="s">
+      <c r="AB5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AC5" s="5" t="s">
+      <c r="AC5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AD5" s="5" t="s">
+      <c r="AD5" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="AE5" s="5" t="s">
+      <c r="AE5" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="AF5" s="5" t="s">
+      <c r="AF5" s="4" t="s">
         <v>57</v>
       </c>
     </row>
@@ -2059,7 +2061,7 @@
       <c r="F7" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="2" t="s">
         <v>64</v>
       </c>
       <c r="H7" s="1">
@@ -2148,7 +2150,7 @@
       <c r="F8" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>68</v>
       </c>
       <c r="H8" s="1">
@@ -2238,7 +2240,9 @@
       <c r="F9" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1" t="s">
+        <v>73</v>
+      </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
@@ -2255,7 +2259,7 @@
         <v>10</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O9" s="1">
         <v>8</v>
@@ -2321,10 +2325,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="G10" s="3" t="s">
         <v>75</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="H10" s="1">
         <v>6</v>
@@ -2342,7 +2346,7 @@
         <v>50</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="O10" s="1">
         <v>60</v>
@@ -2408,10 +2412,10 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="3" t="s">
         <v>78</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="H11" s="1">
         <v>7</v>
@@ -2429,7 +2433,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -2494,10 +2498,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G12" s="3" t="s">
         <v>81</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="H12" s="1">
         <v>9</v>
@@ -2518,7 +2522,7 @@
         <v>10</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O12" s="1">
         <v>10</v>
@@ -2574,7 +2578,7 @@
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G13" s="3"/>
+      <c r="G13" s="2"/>
     </row>
     <row r="14" s="2" customFormat="1" customHeight="1" spans="3:32">
       <c r="AE14" s="1"/>
@@ -2592,7 +2596,7 @@
       <c r="AE18" s="1"/>
     </row>
     <row r="19" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G19" s="3"/>
+      <c r="G19" s="2"/>
     </row>
     <row r="20" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C20" s="1">
@@ -2605,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2624,7 +2628,7 @@
         <v>10</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -2689,10 +2693,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="G21" s="3" t="s">
         <v>86</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -2701,7 +2705,7 @@
         <v>69</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -2713,7 +2717,7 @@
         <v>10</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -2778,10 +2782,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="G22" s="3" t="s">
         <v>90</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
@@ -2802,7 +2806,7 @@
         <v>10</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O22" s="1">
         <v>10</v>
@@ -2867,10 +2871,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G23" s="3" t="s">
         <v>93</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="H23" s="1">
         <v>3</v>
@@ -2891,7 +2895,7 @@
         <v>10</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="O23" s="1">
         <v>0</v>
@@ -2957,10 +2961,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="G24" s="3" t="s">
         <v>96</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -2978,7 +2982,7 @@
         <v>50</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O24" s="1">
         <v>60</v>
@@ -3044,10 +3048,10 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H25" s="1">
         <v>7</v>
@@ -3065,7 +3069,7 @@
         <v>10</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -3130,10 +3134,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G26" s="3" t="s">
         <v>102</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>103</v>
       </c>
       <c r="H26" s="1">
         <v>3</v>
@@ -3154,7 +3158,7 @@
         <v>10</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O26" s="1">
         <v>15</v>
@@ -3210,29 +3214,29 @@
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G27" s="3"/>
+      <c r="G27" s="2"/>
     </row>
     <row r="28" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G28" s="3"/>
+      <c r="G28" s="2"/>
     </row>
     <row r="29" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G29" s="3"/>
+      <c r="G29" s="2"/>
     </row>
     <row r="30" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G30" s="3"/>
+      <c r="G30" s="2"/>
       <c r="H30" s="1"/>
-      <c r="N30" s="3"/>
+      <c r="N30" s="2"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G31" s="3"/>
+      <c r="G31" s="2"/>
       <c r="H31" s="1"/>
-      <c r="N31" s="3"/>
+      <c r="N31" s="2"/>
     </row>
     <row r="32" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="N32" s="3"/>
+      <c r="N32" s="2"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G33" s="3"/>
+      <c r="G33" s="2"/>
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C34" s="1">
@@ -3245,9 +3249,9 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G34" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="G34" s="2"/>
       <c r="H34" s="1">
         <v>1</v>
       </c>
@@ -3264,7 +3268,7 @@
         <v>20</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -3329,10 +3333,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -3341,7 +3345,7 @@
         <v>69</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -3353,7 +3357,7 @@
         <v>10</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O35" s="1">
         <v>0</v>
@@ -3418,10 +3422,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="G36" s="3" t="s">
         <v>110</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>111</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -3430,7 +3434,7 @@
         <v>69</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -3442,7 +3446,7 @@
         <v>10</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O36" s="1">
         <v>10</v>
@@ -3508,10 +3512,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G37" s="3" t="s">
         <v>113</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>114</v>
       </c>
       <c r="H37" s="1">
         <v>8</v>
@@ -3520,7 +3524,7 @@
         <v>61</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K37" s="1">
         <v>6</v>
@@ -3532,7 +3536,7 @@
         <v>100</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O37" s="1">
         <v>10</v>
@@ -3597,10 +3601,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="G38" s="3" t="s">
         <v>116</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>117</v>
       </c>
       <c r="H38" s="1">
         <v>6</v>
@@ -3618,7 +3622,7 @@
         <v>50</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O38" s="1">
         <v>60</v>
@@ -3668,7 +3672,7 @@
       <c r="AD38" s="1">
         <v>0</v>
       </c>
-      <c r="AE38" s="6"/>
+      <c r="AE38" s="5"/>
       <c r="AF38" s="1">
         <v>100</v>
       </c>
@@ -3684,10 +3688,10 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H39" s="1">
         <v>7</v>
@@ -3705,7 +3709,7 @@
         <v>10</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -3770,10 +3774,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="G40" s="3" t="s">
         <v>122</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="H40" s="1">
         <v>4</v>
@@ -3791,7 +3795,7 @@
         <v>100</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O40" s="1">
         <v>30</v>
@@ -3846,13 +3850,13 @@
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G41" s="3"/>
+      <c r="G41" s="2"/>
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G42" s="3"/>
+      <c r="G42" s="2"/>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G43" s="3"/>
+      <c r="G43" s="2"/>
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C44" s="1">
@@ -3864,11 +3868,11 @@
       <c r="E44" s="1">
         <v>0</v>
       </c>
-      <c r="F44" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G44" s="3" t="s">
+      <c r="F44" s="2" t="s">
         <v>125</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>126</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -3886,7 +3890,7 @@
         <v>-100</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="O44" s="1">
         <v>30</v>
@@ -3951,11 +3955,11 @@
       <c r="E45" s="1">
         <v>0</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="G45" s="3" t="s">
+      <c r="F45" s="2" t="s">
         <v>128</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>129</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -3973,7 +3977,7 @@
         <v>200</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O45" s="1">
         <v>60</v>
@@ -4023,7 +4027,7 @@
       <c r="AD45" s="1">
         <v>0</v>
       </c>
-      <c r="AE45" s="6"/>
+      <c r="AE45" s="5"/>
       <c r="AF45" s="1">
         <v>99999</v>
       </c>
@@ -4038,11 +4042,11 @@
       <c r="E46" s="1">
         <v>0</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="G46" s="3" t="s">
+      <c r="F46" s="2" t="s">
         <v>131</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>132</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -4060,7 +4064,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="O46" s="1">
         <v>60</v>
@@ -4116,11 +4120,11 @@
       </c>
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G47" s="3"/>
+      <c r="G47" s="2"/>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="C49" s="1">
@@ -4133,10 +4137,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
@@ -4207,7 +4211,7 @@
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1"/>
     <row r="51" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G51" s="3"/>
+      <c r="G51" s="2"/>
     </row>
     <row r="52" customHeight="1" spans="3:32">
       <c r="E52" s="1"/>
@@ -4265,80 +4269,80 @@
       <c r="AF54" s="1"/>
     </row>
     <row r="55" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
       <c r="H55" s="1"/>
-      <c r="N55" s="3"/>
+      <c r="N55" s="2"/>
       <c r="O55" s="1"/>
-      <c r="R55" s="3"/>
+      <c r="R55" s="2"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1"/>
     <row r="58" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G58" s="3"/>
+      <c r="G58" s="2"/>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G59" s="3"/>
+      <c r="G59" s="2"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1"/>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G61" s="3"/>
+      <c r="G61" s="2"/>
       <c r="H61" s="1"/>
-      <c r="AE61" s="6"/>
+      <c r="AE61" s="5"/>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G62" s="3"/>
+      <c r="G62" s="2"/>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="G63" s="3"/>
+      <c r="G63" s="2"/>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1"/>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G65" s="3"/>
+      <c r="G65" s="2"/>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G66" s="3"/>
+      <c r="G66" s="2"/>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G67" s="3"/>
+      <c r="G67" s="2"/>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G68" s="3"/>
+      <c r="G68" s="2"/>
       <c r="H68" s="1"/>
-      <c r="AE68" s="6"/>
+      <c r="AE68" s="5"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1"/>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G70" s="3"/>
+      <c r="G70" s="2"/>
     </row>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G71" s="3"/>
+      <c r="G71" s="2"/>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1"/>
     <row r="73" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G73" s="3"/>
+      <c r="G73" s="2"/>
     </row>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G74" s="3"/>
+      <c r="G74" s="2"/>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G75" s="3"/>
+      <c r="G75" s="2"/>
       <c r="H75" s="1"/>
-      <c r="AE75" s="6"/>
+      <c r="AE75" s="5"/>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1"/>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G77" s="3"/>
+      <c r="G77" s="2"/>
     </row>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="F78" s="3"/>
-      <c r="G78" s="3"/>
-      <c r="N78" s="3"/>
-      <c r="R78" s="3"/>
-      <c r="U78" s="3"/>
-      <c r="V78" s="3"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="N78" s="2"/>
+      <c r="R78" s="2"/>
+      <c r="U78" s="2"/>
+      <c r="V78" s="2"/>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="6:31">
-      <c r="G79" s="3"/>
+      <c r="G79" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -861,12 +861,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2086,7 +2086,7 @@
         <v>66</v>
       </c>
       <c r="O7" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>89</v>
       </c>
       <c r="O21" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P21" s="1">
         <v>0</v>
@@ -2898,7 +2898,7 @@
         <v>95</v>
       </c>
       <c r="O23" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P23" s="1">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>109</v>
       </c>
       <c r="O35" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P35" s="1">
         <v>0</v>
@@ -3539,7 +3539,7 @@
         <v>115</v>
       </c>
       <c r="O37" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="P37" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -2187,10 +2187,10 @@
         <v>10</v>
       </c>
       <c r="S8" s="1">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="T8" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="U8" s="1">
         <v>5</v>
@@ -2821,10 +2821,10 @@
         <v>10</v>
       </c>
       <c r="S22" s="1">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="T22" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="U22" s="1">
         <v>5</v>
@@ -3461,10 +3461,10 @@
         <v>10</v>
       </c>
       <c r="S36" s="1">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="T36" s="1">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="U36" s="1">
         <v>5</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -2086,7 +2086,7 @@
         <v>66</v>
       </c>
       <c r="O7" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P7" s="1">
         <v>0</v>
@@ -2720,7 +2720,7 @@
         <v>89</v>
       </c>
       <c r="O21" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P21" s="1">
         <v>0</v>
@@ -3360,7 +3360,7 @@
         <v>109</v>
       </c>
       <c r="O35" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="P35" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -278,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="136">
   <si>
     <t>_ID</t>
   </si>
@@ -500,6 +500,9 @@
   </si>
   <si>
     <t>野蛮</t>
+  </si>
+  <si>
+    <t>Chase</t>
   </si>
   <si>
     <t>瞬移到敌人身后造成{0}%物攻+{1}点技能伤害，并且晕眩{2}秒</t>
@@ -695,7 +698,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -714,6 +717,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1196,137 +1205,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1337,6 +1346,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2249,6 +2259,9 @@
       <c r="I9" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="J9" s="1" t="s">
+        <v>74</v>
+      </c>
       <c r="K9" s="1">
         <v>0</v>
       </c>
@@ -2259,7 +2272,7 @@
         <v>10</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O9" s="1">
         <v>8</v>
@@ -2286,7 +2299,7 @@
         <v>2000</v>
       </c>
       <c r="W9" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="X9" s="1">
         <v>1</v>
@@ -2325,10 +2338,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H10" s="1">
         <v>6</v>
@@ -2346,7 +2359,7 @@
         <v>50</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="O10" s="1">
         <v>60</v>
@@ -2412,10 +2425,10 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H11" s="1">
         <v>7</v>
@@ -2433,7 +2446,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -2498,10 +2511,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H12" s="1">
         <v>9</v>
@@ -2522,7 +2535,7 @@
         <v>10</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O12" s="1">
         <v>10</v>
@@ -2609,7 +2622,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2628,7 +2641,7 @@
         <v>10</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -2693,10 +2706,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -2705,7 +2718,7 @@
         <v>69</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -2717,7 +2730,7 @@
         <v>10</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="O21" s="1">
         <v>1</v>
@@ -2782,10 +2795,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
@@ -2806,7 +2819,7 @@
         <v>10</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O22" s="1">
         <v>10</v>
@@ -2871,10 +2884,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H23" s="1">
         <v>3</v>
@@ -2895,7 +2908,7 @@
         <v>10</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="O23" s="1">
         <v>5</v>
@@ -2961,10 +2974,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -2982,7 +2995,7 @@
         <v>50</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O24" s="1">
         <v>60</v>
@@ -3048,10 +3061,10 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H25" s="1">
         <v>7</v>
@@ -3069,7 +3082,7 @@
         <v>10</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -3134,10 +3147,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H26" s="1">
         <v>3</v>
@@ -3158,7 +3171,7 @@
         <v>10</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O26" s="1">
         <v>15</v>
@@ -3249,7 +3262,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
@@ -3268,7 +3281,7 @@
         <v>20</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -3333,10 +3346,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -3345,7 +3358,7 @@
         <v>69</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -3357,7 +3370,7 @@
         <v>10</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O35" s="1">
         <v>1</v>
@@ -3422,10 +3435,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -3434,7 +3447,7 @@
         <v>69</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -3446,7 +3459,7 @@
         <v>10</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="O36" s="1">
         <v>10</v>
@@ -3512,10 +3525,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H37" s="1">
         <v>8</v>
@@ -3524,7 +3537,7 @@
         <v>61</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="K37" s="1">
         <v>6</v>
@@ -3536,7 +3549,7 @@
         <v>100</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="O37" s="1">
         <v>15</v>
@@ -3601,10 +3614,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H38" s="1">
         <v>6</v>
@@ -3622,7 +3635,7 @@
         <v>50</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O38" s="1">
         <v>60</v>
@@ -3688,10 +3701,10 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H39" s="1">
         <v>7</v>
@@ -3709,7 +3722,7 @@
         <v>10</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -3774,10 +3787,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H40" s="1">
         <v>4</v>
@@ -3785,6 +3798,9 @@
       <c r="I40" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="J40" s="6" t="s">
+        <v>70</v>
+      </c>
       <c r="K40" s="1">
         <v>6</v>
       </c>
@@ -3795,7 +3811,7 @@
         <v>100</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="O40" s="1">
         <v>30</v>
@@ -3869,10 +3885,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -3890,7 +3906,7 @@
         <v>-100</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O44" s="1">
         <v>30</v>
@@ -3956,10 +3972,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -3977,7 +3993,7 @@
         <v>200</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="O45" s="1">
         <v>60</v>
@@ -4043,10 +4059,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -4064,7 +4080,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="O46" s="1">
         <v>60</v>
@@ -4137,10 +4153,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -870,12 +870,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -269,7 +269,7 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-效果id,持续时间，叠加层数，百分比系数</t>
+EffectId，EffectValue,持续时间，叠加层数</t>
         </r>
       </text>
     </comment>
@@ -278,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="137">
   <si>
     <t>_ID</t>
   </si>
@@ -514,7 +514,10 @@
     <t>武力盾</t>
   </si>
   <si>
-    <t>提高人物{0}防御，并且生成一个{1}%生命的护盾，持续{2}秒</t>
+    <t>生成一个{1}%生命的护盾</t>
+  </si>
+  <si>
+    <t>"12,10,30,3"</t>
   </si>
   <si>
     <t>无求易决</t>
@@ -532,7 +535,7 @@
     <t>烈火</t>
   </si>
   <si>
-    <t>对单个敌人造成{0}%物攻+{1}点伤害，降低敌人一半的防御和减伤</t>
+    <t>对单个敌人造成{0}%物攻+{1}点伤害</t>
   </si>
   <si>
     <t>冥想心法</t>
@@ -577,7 +580,7 @@
     <t>魔法盾</t>
   </si>
   <si>
-    <t>提高人物{0}魔攻，并且生成一个{1}%生命的护盾，持续{2}秒</t>
+    <t>"13,10,30,3"</t>
   </si>
   <si>
     <t>万法归宗</t>
@@ -595,7 +598,7 @@
     <t>冰咆哮</t>
   </si>
   <si>
-    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点伤害，冰封所有敌人2秒</t>
+    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点伤害</t>
   </si>
   <si>
     <t>清心咒</t>
@@ -637,7 +640,7 @@
     <t>道力盾</t>
   </si>
   <si>
-    <t>提高人物{0}生命，并且生成一个{1}%生命的护盾，持续{2}秒</t>
+    <t>"11,10,30,3"</t>
   </si>
   <si>
     <t>道法自然</t>
@@ -870,12 +873,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1345,8 +1348,8 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2365,7 +2368,7 @@
         <v>60</v>
       </c>
       <c r="P10" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q10" s="1">
         <v>1</v>
@@ -2409,7 +2412,9 @@
       <c r="AD10" s="1">
         <v>0</v>
       </c>
-      <c r="AE10" s="1"/>
+      <c r="AE10" s="1" t="s">
+        <v>79</v>
+      </c>
       <c r="AF10" s="1">
         <v>100</v>
       </c>
@@ -2425,10 +2430,10 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H11" s="1">
         <v>7</v>
@@ -2446,7 +2451,7 @@
         <v>10</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O11" s="1">
         <v>0</v>
@@ -2511,10 +2516,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H12" s="1">
         <v>9</v>
@@ -2535,7 +2540,7 @@
         <v>10</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="O12" s="1">
         <v>10</v>
@@ -2622,7 +2627,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2641,7 +2646,7 @@
         <v>10</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="O20" s="1">
         <v>0</v>
@@ -2706,10 +2711,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -2718,7 +2723,7 @@
         <v>69</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K21" s="1">
         <v>0</v>
@@ -2730,7 +2735,7 @@
         <v>10</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O21" s="1">
         <v>1</v>
@@ -2795,10 +2800,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
@@ -2819,7 +2824,7 @@
         <v>10</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O22" s="1">
         <v>10</v>
@@ -2884,10 +2889,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H23" s="1">
         <v>3</v>
@@ -2908,7 +2913,7 @@
         <v>10</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="O23" s="1">
         <v>5</v>
@@ -2974,10 +2979,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -2995,7 +3000,7 @@
         <v>50</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>99</v>
+        <v>78</v>
       </c>
       <c r="O24" s="1">
         <v>60</v>
@@ -3045,7 +3050,9 @@
       <c r="AD24" s="1">
         <v>0</v>
       </c>
-      <c r="AE24" s="1"/>
+      <c r="AE24" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="AF24" s="1">
         <v>100</v>
       </c>
@@ -3061,10 +3068,10 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H25" s="1">
         <v>7</v>
@@ -3082,7 +3089,7 @@
         <v>10</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O25" s="1">
         <v>0</v>
@@ -3147,10 +3154,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H26" s="1">
         <v>3</v>
@@ -3171,7 +3178,7 @@
         <v>10</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O26" s="1">
         <v>15</v>
@@ -3262,7 +3269,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
@@ -3281,7 +3288,7 @@
         <v>20</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O34" s="1">
         <v>0</v>
@@ -3346,10 +3353,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -3358,7 +3365,7 @@
         <v>69</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K35" s="1">
         <v>0</v>
@@ -3370,7 +3377,7 @@
         <v>10</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O35" s="1">
         <v>1</v>
@@ -3435,10 +3442,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -3447,7 +3454,7 @@
         <v>69</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K36" s="1">
         <v>0</v>
@@ -3459,7 +3466,7 @@
         <v>10</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O36" s="1">
         <v>10</v>
@@ -3525,10 +3532,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H37" s="1">
         <v>8</v>
@@ -3537,7 +3544,7 @@
         <v>61</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K37" s="1">
         <v>6</v>
@@ -3549,7 +3556,7 @@
         <v>100</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O37" s="1">
         <v>15</v>
@@ -3614,10 +3621,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H38" s="1">
         <v>6</v>
@@ -3635,7 +3642,7 @@
         <v>50</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>119</v>
+        <v>78</v>
       </c>
       <c r="O38" s="1">
         <v>60</v>
@@ -3685,7 +3692,9 @@
       <c r="AD38" s="1">
         <v>0</v>
       </c>
-      <c r="AE38" s="5"/>
+      <c r="AE38" s="1" t="s">
+        <v>120</v>
+      </c>
       <c r="AF38" s="1">
         <v>100</v>
       </c>
@@ -3701,10 +3710,10 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H39" s="1">
         <v>7</v>
@@ -3722,7 +3731,7 @@
         <v>10</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O39" s="1">
         <v>0</v>
@@ -3787,10 +3796,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H40" s="1">
         <v>4</v>
@@ -3798,7 +3807,7 @@
       <c r="I40" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J40" s="6" t="s">
+      <c r="J40" s="5" t="s">
         <v>70</v>
       </c>
       <c r="K40" s="1">
@@ -3811,7 +3820,7 @@
         <v>100</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O40" s="1">
         <v>30</v>
@@ -3885,10 +3894,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -3906,7 +3915,7 @@
         <v>-100</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O44" s="1">
         <v>30</v>
@@ -3972,10 +3981,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -3993,7 +4002,7 @@
         <v>200</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="O45" s="1">
         <v>60</v>
@@ -4043,7 +4052,7 @@
       <c r="AD45" s="1">
         <v>0</v>
       </c>
-      <c r="AE45" s="5"/>
+      <c r="AE45" s="6"/>
       <c r="AF45" s="1">
         <v>99999</v>
       </c>
@@ -4059,10 +4068,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -4080,7 +4089,7 @@
         <v>-1</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O46" s="1">
         <v>60</v>
@@ -4153,10 +4162,10 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
@@ -4303,7 +4312,7 @@
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G61" s="2"/>
       <c r="H61" s="1"/>
-      <c r="AE61" s="5"/>
+      <c r="AE61" s="6"/>
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:32">
       <c r="G62" s="2"/>
@@ -4324,7 +4333,7 @@
     <row r="68" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G68" s="2"/>
       <c r="H68" s="1"/>
-      <c r="AE68" s="5"/>
+      <c r="AE68" s="6"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1"/>
     <row r="70" s="1" customFormat="1" customHeight="1" spans="6:31">
@@ -4343,7 +4352,7 @@
     <row r="75" s="1" customFormat="1" customHeight="1" spans="6:31">
       <c r="G75" s="2"/>
       <c r="H75" s="1"/>
-      <c r="AE75" s="5"/>
+      <c r="AE75" s="6"/>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1"/>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="6:31">

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -514,7 +514,7 @@
     <t>武力盾</t>
   </si>
   <si>
-    <t>生成一个{1}%生命的护盾</t>
+    <t>生成一个{0}%生命的护盾</t>
   </si>
   <si>
     <t>"12,10,30,3"</t>
@@ -2380,13 +2380,13 @@
         <v>50</v>
       </c>
       <c r="T10" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U10" s="1">
         <v>10</v>
       </c>
       <c r="V10" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
@@ -3018,13 +3018,13 @@
         <v>50</v>
       </c>
       <c r="T24" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U24" s="1">
         <v>10</v>
       </c>
       <c r="V24" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W24" s="1">
         <v>0</v>
@@ -3660,13 +3660,13 @@
         <v>50</v>
       </c>
       <c r="T38" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U38" s="1">
         <v>10</v>
       </c>
       <c r="V38" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="W38" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -87,7 +87,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I3" authorId="0">
+    <comment ref="J3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -111,7 +111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="1">
+    <comment ref="L3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -134,7 +134,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M3" authorId="0">
+    <comment ref="N3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -156,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="N3" authorId="1">
+    <comment ref="O3" authorId="1">
       <text>
         <r>
           <rPr>
@@ -184,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0">
+    <comment ref="R3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -206,7 +206,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S3" authorId="0">
+    <comment ref="T3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -228,7 +228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W3" authorId="0">
+    <comment ref="X3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -251,7 +251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE3" authorId="0">
+    <comment ref="AF3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -278,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="136">
   <si>
     <t>_ID</t>
   </si>
@@ -298,6 +298,9 @@
     <t>类型</t>
   </si>
   <si>
+    <t>是否享受精通加成</t>
+  </si>
+  <si>
     <t>中心目标</t>
   </si>
   <si>
@@ -379,6 +382,9 @@
     <t>Type</t>
   </si>
   <si>
+    <t>RiseType</t>
+  </si>
+  <si>
     <t>Center</t>
   </si>
   <si>
@@ -523,9 +529,6 @@
     <t>无求易决</t>
   </si>
   <si>
-    <t>武力精通</t>
-  </si>
-  <si>
     <t>战士技能增加{0}%技能系数增幅，无需上阵</t>
   </si>
   <si>
@@ -586,9 +589,6 @@
     <t>万法归宗</t>
   </si>
   <si>
-    <t>法术精通</t>
-  </si>
-  <si>
     <t>法师技能增加{0}%技能系数增幅，无需上阵</t>
   </si>
   <si>
@@ -644,9 +644,6 @@
   </si>
   <si>
     <t>道法自然</t>
-  </si>
-  <si>
-    <t>道力精通</t>
   </si>
   <si>
     <t>被动道士技能增加{0}%技能系数增幅，无需上阵</t>
@@ -1669,7 +1666,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:AF79"/>
+  <dimension ref="C2:AG79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
@@ -1678,32 +1675,33 @@
     <col min="6" max="6" width="11.5083333333333" style="2" customWidth="1"/>
     <col min="7" max="7" width="9" style="2" customWidth="1"/>
     <col min="8" max="8" width="9.25" style="2" customWidth="1"/>
-    <col min="9" max="10" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="11" max="11" width="9.375" style="2" customWidth="1"/>
-    <col min="12" max="12" width="9.33333333333333" style="2" customWidth="1"/>
-    <col min="13" max="13" width="5.25" style="2" customWidth="1"/>
-    <col min="14" max="14" width="57.25" style="2" customWidth="1"/>
-    <col min="15" max="15" width="5.875" style="2" customWidth="1"/>
-    <col min="16" max="16" width="6.50833333333333" style="2" customWidth="1"/>
-    <col min="17" max="17" width="7.16666666666667" style="2" customWidth="1"/>
-    <col min="18" max="18" width="7.50833333333333" style="2" customWidth="1"/>
-    <col min="19" max="20" width="7.875" style="2" customWidth="1"/>
-    <col min="21" max="21" width="8.66666666666667" style="2" customWidth="1"/>
-    <col min="22" max="22" width="9.5" style="2" customWidth="1"/>
-    <col min="23" max="23" width="7.375" style="2" customWidth="1"/>
-    <col min="24" max="26" width="7.625" style="2" customWidth="1"/>
-    <col min="27" max="27" width="9.625" style="2" customWidth="1"/>
-    <col min="28" max="29" width="7.875" style="2" customWidth="1"/>
-    <col min="30" max="30" width="9.75" style="2" customWidth="1"/>
-    <col min="31" max="31" width="21.75" style="2" customWidth="1"/>
-    <col min="32" max="32" width="11.75" style="2" customWidth="1"/>
-    <col min="33" max="16384" width="9" style="2"/>
+    <col min="9" max="9" width="12.8333333333333" style="2" customWidth="1"/>
+    <col min="10" max="11" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="9.375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="9.33333333333333" style="2" customWidth="1"/>
+    <col min="14" max="14" width="5.25" style="2" customWidth="1"/>
+    <col min="15" max="15" width="57.25" style="2" customWidth="1"/>
+    <col min="16" max="16" width="5.875" style="2" customWidth="1"/>
+    <col min="17" max="17" width="6.50833333333333" style="2" customWidth="1"/>
+    <col min="18" max="18" width="7.16666666666667" style="2" customWidth="1"/>
+    <col min="19" max="19" width="7.50833333333333" style="2" customWidth="1"/>
+    <col min="20" max="21" width="7.875" style="2" customWidth="1"/>
+    <col min="22" max="22" width="8.66666666666667" style="2" customWidth="1"/>
+    <col min="23" max="23" width="9.5" style="2" customWidth="1"/>
+    <col min="24" max="24" width="7.375" style="2" customWidth="1"/>
+    <col min="25" max="27" width="7.625" style="2" customWidth="1"/>
+    <col min="28" max="28" width="9.625" style="2" customWidth="1"/>
+    <col min="29" max="30" width="7.875" style="2" customWidth="1"/>
+    <col min="31" max="31" width="9.75" style="2" customWidth="1"/>
+    <col min="32" max="32" width="21.75" style="2" customWidth="1"/>
+    <col min="33" max="33" width="11.75" style="2" customWidth="1"/>
+    <col min="34" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" customHeight="1" spans="3:32">
-      <c r="N2" s="3"/>
-    </row>
-    <row r="3" customHeight="1" spans="3:32">
+    <row r="2" customHeight="1" spans="3:33">
+      <c r="O2" s="3"/>
+    </row>
+    <row r="3" customHeight="1" spans="3:33">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1725,10 +1723,10 @@
       <c r="I3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>7</v>
       </c>
+      <c r="K3" s="4"/>
       <c r="L3" s="4" t="s">
         <v>8</v>
       </c>
@@ -1760,7 +1758,7 @@
         <v>17</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="W3" s="4" t="s">
         <v>18</v>
@@ -1792,192 +1790,201 @@
       <c r="AF3" s="4" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:32">
+      <c r="AG3" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:33">
       <c r="C4" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:32">
+        <v>57</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="3:33">
       <c r="C5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="AE5" s="4" t="s">
         <v>59</v>
       </c>
       <c r="AF5" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:32">
+        <v>61</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -1988,54 +1995,54 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
         <v>1</v>
       </c>
-      <c r="I6" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
+      <c r="I6" s="1">
+        <v>1</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
       </c>
       <c r="M6" s="1">
-        <v>10</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>10</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
       </c>
       <c r="Q6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R6" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S6" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T6" s="1">
+        <v>1</v>
+      </c>
+      <c r="U6" s="1">
         <v>100</v>
       </c>
-      <c r="U6" s="1">
-        <v>1</v>
-      </c>
       <c r="V6" s="1">
+        <v>1</v>
+      </c>
+      <c r="W6" s="1">
         <v>100</v>
       </c>
-      <c r="W6" s="1">
-        <v>0</v>
-      </c>
       <c r="X6" s="1">
         <v>0</v>
       </c>
@@ -2057,11 +2064,14 @@
       <c r="AD6" s="1">
         <v>0</v>
       </c>
-      <c r="AF6" s="1">
+      <c r="AE6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2072,64 +2082,64 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H7" s="1">
         <v>9</v>
       </c>
-      <c r="I7" s="1" t="s">
-        <v>61</v>
+      <c r="I7" s="1">
+        <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
       </c>
       <c r="M7" s="1">
-        <v>10</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="O7" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>10</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="P7" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S7" s="1">
+        <v>10</v>
+      </c>
+      <c r="T7" s="1">
         <v>120</v>
       </c>
-      <c r="T7" s="1">
+      <c r="U7" s="1">
         <v>1000</v>
       </c>
-      <c r="U7" s="1">
-        <v>10</v>
-      </c>
       <c r="V7" s="1">
+        <v>10</v>
+      </c>
+      <c r="W7" s="1">
         <v>1000</v>
-      </c>
-      <c r="W7" s="1">
-        <v>2</v>
       </c>
       <c r="X7" s="1">
         <v>2</v>
       </c>
       <c r="Y7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z7" s="1">
         <v>0</v>
@@ -2146,11 +2156,14 @@
       <c r="AD7" s="1">
         <v>0</v>
       </c>
-      <c r="AF7" s="1">
+      <c r="AE7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2161,70 +2174,70 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H8" s="1">
         <v>5</v>
       </c>
-      <c r="I8" s="1" t="s">
-        <v>69</v>
+      <c r="I8" s="1">
+        <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
       </c>
       <c r="M8" s="1">
-        <v>10</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>10</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>73</v>
       </c>
       <c r="P8" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="1">
         <v>5</v>
       </c>
-      <c r="Q8" s="1">
-        <v>1</v>
-      </c>
       <c r="R8" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S8" s="1">
+        <v>10</v>
+      </c>
+      <c r="T8" s="1">
         <v>50</v>
       </c>
-      <c r="T8" s="1">
+      <c r="U8" s="1">
         <v>500</v>
       </c>
-      <c r="U8" s="1">
+      <c r="V8" s="1">
         <v>5</v>
       </c>
-      <c r="V8" s="1">
+      <c r="W8" s="1">
         <v>800</v>
       </c>
-      <c r="W8" s="1">
+      <c r="X8" s="1">
         <v>3</v>
       </c>
-      <c r="X8" s="1">
-        <v>0</v>
-      </c>
       <c r="Y8" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z8" s="1">
         <v>3</v>
       </c>
       <c r="AA8" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB8" s="1">
         <v>0</v>
@@ -2235,12 +2248,15 @@
       <c r="AD8" s="1">
         <v>0</v>
       </c>
-      <c r="AE8" s="1"/>
-      <c r="AF8" s="1">
+      <c r="AE8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2251,64 +2267,64 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
       </c>
-      <c r="I9" s="1" t="s">
-        <v>69</v>
+      <c r="I9" s="1">
+        <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>76</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
       </c>
       <c r="M9" s="1">
-        <v>10</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="O9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>10</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" s="1">
         <v>8</v>
       </c>
-      <c r="P9" s="1">
+      <c r="Q9" s="1">
         <v>2</v>
       </c>
-      <c r="Q9" s="1">
-        <v>1</v>
-      </c>
       <c r="R9" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S9" s="1">
+        <v>10</v>
+      </c>
+      <c r="T9" s="1">
         <v>150</v>
       </c>
-      <c r="T9" s="1">
+      <c r="U9" s="1">
         <v>2000</v>
       </c>
-      <c r="U9" s="1">
+      <c r="V9" s="1">
         <v>20</v>
       </c>
-      <c r="V9" s="1">
+      <c r="W9" s="1">
         <v>2000</v>
       </c>
-      <c r="W9" s="1">
+      <c r="X9" s="1">
         <v>6</v>
       </c>
-      <c r="X9" s="1">
-        <v>1</v>
-      </c>
       <c r="Y9" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z9" s="1">
         <v>0</v>
@@ -2325,12 +2341,15 @@
       <c r="AD9" s="1">
         <v>0</v>
       </c>
-      <c r="AE9" s="1"/>
-      <c r="AF9" s="1">
+      <c r="AE9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2341,52 +2360,52 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="H10" s="1">
         <v>6</v>
       </c>
-      <c r="I10" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="I10" s="1">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L10" s="1">
         <v>5</v>
       </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
       <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
         <v>50</v>
       </c>
-      <c r="N10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O10" s="1">
+      <c r="O10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P10" s="1">
         <v>60</v>
       </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
       <c r="Q10" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R10" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S10" s="1">
+        <v>10</v>
+      </c>
+      <c r="T10" s="1">
         <v>50</v>
       </c>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
       <c r="U10" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V10" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
@@ -2412,14 +2431,17 @@
       <c r="AD10" s="1">
         <v>0</v>
       </c>
-      <c r="AE10" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="AF10" s="1">
+      <c r="AE10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="AG10" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2430,52 +2452,50 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>81</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="G11" s="1"/>
       <c r="H11" s="1">
         <v>7</v>
       </c>
-      <c r="I11" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <v>10</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>10</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
       </c>
       <c r="Q11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S11" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T11" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W11" s="1">
         <v>0</v>
@@ -2501,11 +2521,14 @@
       <c r="AD11" s="1">
         <v>0</v>
       </c>
-      <c r="AF11" s="1">
+      <c r="AE11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2516,64 +2539,64 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H12" s="1">
         <v>9</v>
       </c>
-      <c r="I12" s="1" t="s">
-        <v>61</v>
+      <c r="I12" s="1">
+        <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
       </c>
       <c r="M12" s="1">
-        <v>10</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="O12" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>10</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="P12" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="S12" s="1">
+        <v>10</v>
+      </c>
+      <c r="T12" s="1">
         <v>300</v>
       </c>
-      <c r="T12" s="1">
+      <c r="U12" s="1">
         <v>10000</v>
       </c>
-      <c r="U12" s="1">
+      <c r="V12" s="1">
         <v>50</v>
       </c>
-      <c r="V12" s="1">
+      <c r="W12" s="1">
         <v>10000</v>
       </c>
-      <c r="W12" s="1">
-        <v>1</v>
-      </c>
       <c r="X12" s="1">
         <v>1</v>
       </c>
       <c r="Y12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" s="1">
         <v>0</v>
@@ -2590,33 +2613,36 @@
       <c r="AD12" s="1">
         <v>0</v>
       </c>
-      <c r="AE12" s="1"/>
-      <c r="AF12" s="1">
+      <c r="AE12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G13" s="2"/>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:32">
-      <c r="AE14" s="1"/>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:32">
-      <c r="AE15" s="1"/>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:32">
-      <c r="AE16" s="1"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:32">
-      <c r="AE17" s="1"/>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:32">
-      <c r="AE18" s="1"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF14" s="1"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF15" s="1"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF16" s="1"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF17" s="1"/>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AF18" s="1"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G19" s="2"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C20" s="1">
         <v>2001</v>
       </c>
@@ -2627,54 +2653,54 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
         <v>1</v>
       </c>
-      <c r="I20" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
+      <c r="I20" s="1">
+        <v>1</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
       </c>
       <c r="M20" s="1">
-        <v>10</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>10</v>
+      </c>
+      <c r="O20" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="P20" s="1">
         <v>0</v>
       </c>
       <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
         <v>2</v>
       </c>
-      <c r="R20" s="1">
-        <v>10</v>
-      </c>
       <c r="S20" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" s="1">
+        <v>1</v>
+      </c>
+      <c r="U20" s="1">
         <v>100</v>
       </c>
-      <c r="U20" s="1">
-        <v>1</v>
-      </c>
       <c r="V20" s="1">
+        <v>1</v>
+      </c>
+      <c r="W20" s="1">
         <v>100</v>
       </c>
-      <c r="W20" s="1">
-        <v>0</v>
-      </c>
       <c r="X20" s="1">
         <v>0</v>
       </c>
@@ -2696,11 +2722,14 @@
       <c r="AD20" s="1">
         <v>0</v>
       </c>
-      <c r="AF20" s="1">
+      <c r="AE20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C21" s="1">
         <v>2002</v>
       </c>
@@ -2711,64 +2740,64 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
       </c>
-      <c r="I21" s="1" t="s">
-        <v>69</v>
+      <c r="I21" s="1">
+        <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
       </c>
       <c r="M21" s="1">
-        <v>10</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="O21" s="1">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>10</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>92</v>
       </c>
       <c r="P21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
         <v>2</v>
       </c>
-      <c r="R21" s="1">
-        <v>10</v>
-      </c>
       <c r="S21" s="1">
+        <v>10</v>
+      </c>
+      <c r="T21" s="1">
         <v>120</v>
       </c>
-      <c r="T21" s="1">
+      <c r="U21" s="1">
         <v>1000</v>
       </c>
-      <c r="U21" s="1">
+      <c r="V21" s="1">
         <v>12</v>
       </c>
-      <c r="V21" s="1">
+      <c r="W21" s="1">
         <v>1000</v>
       </c>
-      <c r="W21" s="1">
+      <c r="X21" s="1">
         <v>3</v>
       </c>
-      <c r="X21" s="1">
-        <v>1</v>
-      </c>
       <c r="Y21" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z21" s="1">
         <v>0</v>
@@ -2785,11 +2814,14 @@
       <c r="AD21" s="1">
         <v>0</v>
       </c>
-      <c r="AF21" s="1">
+      <c r="AE21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C22" s="1">
         <v>2003</v>
       </c>
@@ -2800,70 +2832,70 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
       </c>
-      <c r="I22" s="1" t="s">
-        <v>69</v>
+      <c r="I22" s="1">
+        <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
       </c>
       <c r="M22" s="1">
-        <v>10</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="O22" s="1">
-        <v>10</v>
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>10</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="P22" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q22" s="1">
         <v>5</v>
       </c>
-      <c r="Q22" s="1">
+      <c r="R22" s="1">
         <v>2</v>
       </c>
-      <c r="R22" s="1">
-        <v>10</v>
-      </c>
       <c r="S22" s="1">
+        <v>10</v>
+      </c>
+      <c r="T22" s="1">
         <v>50</v>
       </c>
-      <c r="T22" s="1">
+      <c r="U22" s="1">
         <v>500</v>
       </c>
-      <c r="U22" s="1">
+      <c r="V22" s="1">
         <v>5</v>
       </c>
-      <c r="V22" s="1">
+      <c r="W22" s="1">
         <v>800</v>
       </c>
-      <c r="W22" s="1">
+      <c r="X22" s="1">
         <v>3</v>
       </c>
-      <c r="X22" s="1">
-        <v>0</v>
-      </c>
       <c r="Y22" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z22" s="1">
         <v>3</v>
       </c>
       <c r="AA22" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -2874,11 +2906,14 @@
       <c r="AD22" s="1">
         <v>0</v>
       </c>
-      <c r="AF22" s="1">
+      <c r="AE22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C23" s="1">
         <v>2004</v>
       </c>
@@ -2889,70 +2924,70 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H23" s="1">
         <v>3</v>
       </c>
-      <c r="I23" s="1" t="s">
-        <v>69</v>
+      <c r="I23" s="1">
+        <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
       </c>
       <c r="M23" s="1">
-        <v>10</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>10</v>
+      </c>
+      <c r="O23" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="P23" s="1">
         <v>5</v>
       </c>
-      <c r="P23" s="1">
-        <v>0</v>
-      </c>
       <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
         <v>2</v>
       </c>
-      <c r="R23" s="1">
-        <v>10</v>
-      </c>
       <c r="S23" s="1">
+        <v>10</v>
+      </c>
+      <c r="T23" s="1">
         <v>120</v>
       </c>
-      <c r="T23" s="1">
+      <c r="U23" s="1">
         <v>2000</v>
       </c>
-      <c r="U23" s="1">
-        <v>10</v>
-      </c>
       <c r="V23" s="1">
+        <v>10</v>
+      </c>
+      <c r="W23" s="1">
         <v>2000</v>
       </c>
-      <c r="W23" s="1">
+      <c r="X23" s="1">
         <v>4</v>
       </c>
-      <c r="X23" s="1">
-        <v>0</v>
-      </c>
       <c r="Y23" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z23" s="1">
         <v>3</v>
       </c>
       <c r="AA23" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB23" s="1">
         <v>0</v>
@@ -2963,12 +2998,15 @@
       <c r="AD23" s="1">
         <v>0</v>
       </c>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1">
+      <c r="AE23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="1"/>
+      <c r="AG23" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C24" s="1">
         <v>2005</v>
       </c>
@@ -2979,52 +3017,52 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
       </c>
-      <c r="I24" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K24" s="1">
+      <c r="I24" s="1">
+        <v>1</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L24" s="1">
         <v>5</v>
       </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
       <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
         <v>50</v>
       </c>
-      <c r="N24" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O24" s="1">
+      <c r="O24" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P24" s="1">
         <v>60</v>
       </c>
-      <c r="P24" s="1">
+      <c r="Q24" s="1">
         <v>30</v>
       </c>
-      <c r="Q24" s="1">
+      <c r="R24" s="1">
         <v>2</v>
       </c>
-      <c r="R24" s="1">
-        <v>10</v>
-      </c>
       <c r="S24" s="1">
+        <v>10</v>
+      </c>
+      <c r="T24" s="1">
         <v>50</v>
       </c>
-      <c r="T24" s="1">
-        <v>0</v>
-      </c>
       <c r="U24" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V24" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W24" s="1">
         <v>0</v>
@@ -3050,14 +3088,17 @@
       <c r="AD24" s="1">
         <v>0</v>
       </c>
-      <c r="AE24" s="1" t="s">
+      <c r="AE24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AG24" s="1">
         <v>100</v>
       </c>
-      <c r="AF24" s="1">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:32">
+    </row>
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C25" s="1">
         <v>2006</v>
       </c>
@@ -3068,52 +3109,50 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="G25" s="1" t="s">
         <v>102</v>
       </c>
+      <c r="G25" s="1"/>
       <c r="H25" s="1">
         <v>7</v>
       </c>
-      <c r="I25" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
       </c>
       <c r="M25" s="1">
-        <v>10</v>
-      </c>
-      <c r="N25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>10</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
       <c r="P25" s="1">
         <v>0</v>
       </c>
       <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
         <v>2</v>
       </c>
-      <c r="R25" s="1">
-        <v>10</v>
-      </c>
       <c r="S25" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T25" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U25" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W25" s="1">
         <v>0</v>
@@ -3139,11 +3178,14 @@
       <c r="AD25" s="1">
         <v>0</v>
       </c>
-      <c r="AF25" s="1">
+      <c r="AE25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C26" s="1">
         <v>2007</v>
       </c>
@@ -3162,62 +3204,62 @@
       <c r="H26" s="1">
         <v>3</v>
       </c>
-      <c r="I26" s="1" t="s">
-        <v>69</v>
+      <c r="I26" s="1">
+        <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
       </c>
       <c r="M26" s="1">
-        <v>10</v>
-      </c>
-      <c r="N26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>10</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="O26" s="1">
+      <c r="P26" s="1">
         <v>15</v>
       </c>
-      <c r="P26" s="1">
-        <v>0</v>
-      </c>
       <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1">
         <v>2</v>
       </c>
-      <c r="R26" s="1">
-        <v>10</v>
-      </c>
       <c r="S26" s="1">
+        <v>10</v>
+      </c>
+      <c r="T26" s="1">
         <v>150</v>
       </c>
-      <c r="T26" s="1">
+      <c r="U26" s="1">
         <v>5000</v>
       </c>
-      <c r="U26" s="1">
+      <c r="V26" s="1">
         <v>30</v>
       </c>
-      <c r="V26" s="1">
+      <c r="W26" s="1">
         <v>5000</v>
       </c>
-      <c r="W26" s="1">
+      <c r="X26" s="1">
         <v>5</v>
       </c>
-      <c r="X26" s="1">
-        <v>0</v>
-      </c>
       <c r="Y26" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z26" s="1">
         <v>3</v>
       </c>
       <c r="AA26" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB26" s="1">
         <v>0</v>
@@ -3228,37 +3270,40 @@
       <c r="AD26" s="1">
         <v>0</v>
       </c>
-      <c r="AE26" s="1"/>
-      <c r="AF26" s="1">
+      <c r="AE26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G27" s="2"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G28" s="2"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G30" s="2"/>
       <c r="H30" s="1"/>
-      <c r="N30" s="2"/>
-    </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:32">
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G31" s="2"/>
       <c r="H31" s="1"/>
-      <c r="N31" s="2"/>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:32">
-      <c r="N32" s="2"/>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:32">
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G33" s="2"/>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C34" s="1">
         <v>3001</v>
       </c>
@@ -3275,48 +3320,48 @@
       <c r="H34" s="1">
         <v>1</v>
       </c>
-      <c r="I34" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
+      <c r="I34" s="1">
+        <v>1</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
       </c>
       <c r="M34" s="1">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1">
         <v>20</v>
       </c>
-      <c r="N34" s="1" t="s">
+      <c r="O34" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="O34" s="1">
-        <v>0</v>
-      </c>
       <c r="P34" s="1">
         <v>0</v>
       </c>
       <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1">
         <v>3</v>
       </c>
-      <c r="R34" s="1">
-        <v>10</v>
-      </c>
       <c r="S34" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" s="1">
+        <v>1</v>
+      </c>
+      <c r="U34" s="1">
         <v>100</v>
       </c>
-      <c r="U34" s="1">
-        <v>1</v>
-      </c>
       <c r="V34" s="1">
+        <v>1</v>
+      </c>
+      <c r="W34" s="1">
         <v>100</v>
       </c>
-      <c r="W34" s="1">
-        <v>0</v>
-      </c>
       <c r="X34" s="1">
         <v>0</v>
       </c>
@@ -3338,11 +3383,14 @@
       <c r="AD34" s="1">
         <v>0</v>
       </c>
-      <c r="AF34" s="1">
+      <c r="AE34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C35" s="1">
         <v>3002</v>
       </c>
@@ -3361,56 +3409,56 @@
       <c r="H35" s="1">
         <v>2</v>
       </c>
-      <c r="I35" s="1" t="s">
-        <v>69</v>
+      <c r="I35" s="1">
+        <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
       </c>
       <c r="M35" s="1">
-        <v>10</v>
-      </c>
-      <c r="N35" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N35" s="1">
+        <v>10</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="O35" s="1">
-        <v>1</v>
-      </c>
       <c r="P35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1">
         <v>3</v>
       </c>
-      <c r="R35" s="1">
-        <v>10</v>
-      </c>
       <c r="S35" s="1">
+        <v>10</v>
+      </c>
+      <c r="T35" s="1">
         <v>120</v>
       </c>
-      <c r="T35" s="1">
+      <c r="U35" s="1">
         <v>1000</v>
       </c>
-      <c r="U35" s="1">
-        <v>10</v>
-      </c>
       <c r="V35" s="1">
+        <v>10</v>
+      </c>
+      <c r="W35" s="1">
         <v>1000</v>
       </c>
-      <c r="W35" s="1">
+      <c r="X35" s="1">
         <v>3</v>
       </c>
-      <c r="X35" s="1">
-        <v>1</v>
-      </c>
       <c r="Y35" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z35" s="1">
         <v>0</v>
@@ -3427,11 +3475,14 @@
       <c r="AD35" s="1">
         <v>0</v>
       </c>
-      <c r="AF35" s="1">
+      <c r="AE35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C36" s="1">
         <v>3003</v>
       </c>
@@ -3450,57 +3501,57 @@
       <c r="H36" s="1">
         <v>2</v>
       </c>
-      <c r="I36" s="1" t="s">
-        <v>69</v>
+      <c r="I36" s="1">
+        <v>1</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0</v>
+        <v>71</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>91</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
       </c>
       <c r="M36" s="1">
-        <v>10</v>
-      </c>
-      <c r="N36" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N36" s="1">
+        <v>10</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="O36" s="1">
-        <v>10</v>
-      </c>
       <c r="P36" s="1">
+        <v>10</v>
+      </c>
+      <c r="Q36" s="1">
         <v>5</v>
       </c>
-      <c r="Q36" s="1">
+      <c r="R36" s="1">
         <v>3</v>
       </c>
-      <c r="R36" s="1">
-        <v>10</v>
-      </c>
       <c r="S36" s="1">
+        <v>10</v>
+      </c>
+      <c r="T36" s="1">
         <v>50</v>
       </c>
-      <c r="T36" s="1">
+      <c r="U36" s="1">
         <v>500</v>
       </c>
-      <c r="U36" s="1">
+      <c r="V36" s="1">
         <v>5</v>
       </c>
-      <c r="V36" s="1">
+      <c r="W36" s="1">
         <v>800</v>
       </c>
-      <c r="W36" s="1">
+      <c r="X36" s="1">
         <v>4</v>
       </c>
-      <c r="X36" s="1">
+      <c r="Y36" s="1">
         <v>3</v>
       </c>
-      <c r="Y36" s="1">
-        <v>0</v>
-      </c>
       <c r="Z36" s="1">
         <v>0</v>
       </c>
@@ -3516,12 +3567,15 @@
       <c r="AD36" s="1">
         <v>0</v>
       </c>
-      <c r="AE36" s="1"/>
-      <c r="AF36" s="1">
+      <c r="AE36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C37" s="1">
         <v>3004</v>
       </c>
@@ -3540,57 +3594,57 @@
       <c r="H37" s="1">
         <v>8</v>
       </c>
-      <c r="I37" s="1" t="s">
-        <v>61</v>
+      <c r="I37" s="1">
+        <v>1</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="K37" s="1">
+        <v>63</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="L37" s="1">
         <v>6</v>
       </c>
-      <c r="L37" s="1">
-        <v>0</v>
-      </c>
       <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
         <v>100</v>
       </c>
-      <c r="N37" s="1" t="s">
+      <c r="O37" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="O37" s="1">
+      <c r="P37" s="1">
         <v>15</v>
       </c>
-      <c r="P37" s="1">
-        <v>0</v>
-      </c>
       <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1">
         <v>3</v>
       </c>
-      <c r="R37" s="1">
-        <v>10</v>
-      </c>
       <c r="S37" s="1">
+        <v>10</v>
+      </c>
+      <c r="T37" s="1">
         <v>1000</v>
       </c>
-      <c r="T37" s="1">
+      <c r="U37" s="1">
         <v>100000</v>
       </c>
-      <c r="U37" s="1">
+      <c r="V37" s="1">
         <v>1000</v>
       </c>
-      <c r="V37" s="1">
+      <c r="W37" s="1">
         <v>100000</v>
       </c>
-      <c r="W37" s="1">
+      <c r="X37" s="1">
         <v>5</v>
       </c>
-      <c r="X37" s="1">
+      <c r="Y37" s="1">
         <v>3</v>
       </c>
-      <c r="Y37" s="1">
-        <v>0</v>
-      </c>
       <c r="Z37" s="1">
         <v>0</v>
       </c>
@@ -3606,11 +3660,14 @@
       <c r="AD37" s="1">
         <v>0</v>
       </c>
-      <c r="AF37" s="1">
+      <c r="AE37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C38" s="1">
         <v>3005</v>
       </c>
@@ -3629,44 +3686,44 @@
       <c r="H38" s="1">
         <v>6</v>
       </c>
-      <c r="I38" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K38" s="1">
+      <c r="I38" s="1">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L38" s="1">
         <v>5</v>
       </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
       <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
         <v>50</v>
       </c>
-      <c r="N38" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="O38" s="1">
+      <c r="O38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="P38" s="1">
         <v>60</v>
       </c>
-      <c r="P38" s="1">
+      <c r="Q38" s="1">
         <v>30</v>
       </c>
-      <c r="Q38" s="1">
+      <c r="R38" s="1">
         <v>3</v>
       </c>
-      <c r="R38" s="1">
-        <v>10</v>
-      </c>
       <c r="S38" s="1">
+        <v>10</v>
+      </c>
+      <c r="T38" s="1">
         <v>50</v>
       </c>
-      <c r="T38" s="1">
-        <v>0</v>
-      </c>
       <c r="U38" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V38" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W38" s="1">
         <v>0</v>
@@ -3692,14 +3749,17 @@
       <c r="AD38" s="1">
         <v>0</v>
       </c>
-      <c r="AE38" s="1" t="s">
+      <c r="AE38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF38" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="AF38" s="1">
+      <c r="AG38" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C39" s="1">
         <v>3006</v>
       </c>
@@ -3712,50 +3772,48 @@
       <c r="F39" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G39" s="1" t="s">
-        <v>122</v>
-      </c>
+      <c r="G39" s="1"/>
       <c r="H39" s="1">
         <v>7</v>
       </c>
-      <c r="I39" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
+      <c r="I39" s="1">
+        <v>0</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
       </c>
       <c r="M39" s="1">
-        <v>10</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="O39" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="N39" s="1">
+        <v>10</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="P39" s="1">
         <v>0</v>
       </c>
       <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1">
         <v>3</v>
       </c>
-      <c r="R39" s="1">
-        <v>10</v>
-      </c>
       <c r="S39" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U39" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V39" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" s="1">
         <v>0</v>
@@ -3781,11 +3839,14 @@
       <c r="AD39" s="1">
         <v>0</v>
       </c>
-      <c r="AF39" s="1">
+      <c r="AE39" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG39" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C40" s="1">
         <v>3007</v>
       </c>
@@ -3796,65 +3857,65 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="H40" s="1">
         <v>4</v>
       </c>
-      <c r="I40" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="K40" s="1">
+      <c r="I40" s="1">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="L40" s="1">
         <v>6</v>
       </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
       <c r="M40" s="1">
+        <v>0</v>
+      </c>
+      <c r="N40" s="1">
         <v>100</v>
       </c>
-      <c r="N40" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="O40" s="1">
+      <c r="O40" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="P40" s="1">
         <v>30</v>
       </c>
-      <c r="P40" s="1">
-        <v>0</v>
-      </c>
       <c r="Q40" s="1">
+        <v>0</v>
+      </c>
+      <c r="R40" s="1">
         <v>3</v>
       </c>
-      <c r="R40" s="1">
-        <v>10</v>
-      </c>
       <c r="S40" s="1">
+        <v>10</v>
+      </c>
+      <c r="T40" s="1">
         <v>200</v>
       </c>
-      <c r="T40" s="1">
+      <c r="U40" s="1">
         <v>8000</v>
       </c>
-      <c r="U40" s="1">
+      <c r="V40" s="1">
         <v>40</v>
       </c>
-      <c r="V40" s="1">
+      <c r="W40" s="1">
         <v>8000</v>
       </c>
-      <c r="W40" s="1">
-        <v>0</v>
-      </c>
       <c r="X40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="1">
         <v>2</v>
       </c>
-      <c r="Y40" s="1">
-        <v>0</v>
-      </c>
       <c r="Z40" s="1">
         <v>0</v>
       </c>
@@ -3870,20 +3931,23 @@
       <c r="AD40" s="1">
         <v>0</v>
       </c>
-      <c r="AF40" s="1">
+      <c r="AE40" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG40" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G41" s="2"/>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G42" s="2"/>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G43" s="2"/>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C44" s="1">
         <v>4001</v>
       </c>
@@ -3894,38 +3958,38 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="1">
+        <v>0</v>
+      </c>
+      <c r="I44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
+        <v>-100</v>
+      </c>
+      <c r="O44" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H44" s="1">
-        <v>0</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K44" s="1">
-        <v>0</v>
-      </c>
-      <c r="L44" s="1">
-        <v>0</v>
-      </c>
-      <c r="M44" s="1">
-        <v>-100</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="O44" s="1">
+      <c r="P44" s="1">
         <v>30</v>
       </c>
-      <c r="P44" s="1">
+      <c r="Q44" s="1">
         <v>2</v>
       </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
       <c r="R44" s="1">
         <v>0</v>
       </c>
@@ -3965,12 +4029,15 @@
       <c r="AD44" s="1">
         <v>0</v>
       </c>
-      <c r="AE44" s="1"/>
-      <c r="AF44" s="1">
+      <c r="AE44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF44" s="1"/>
+      <c r="AG44" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C45" s="1">
         <v>4002</v>
       </c>
@@ -3981,35 +4048,35 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="H45" s="1">
+        <v>0</v>
+      </c>
+      <c r="I45" s="1">
+        <v>0</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
+        <v>200</v>
+      </c>
+      <c r="O45" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="H45" s="1">
-        <v>0</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
-      <c r="L45" s="1">
-        <v>0</v>
-      </c>
-      <c r="M45" s="1">
-        <v>200</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="O45" s="1">
+      <c r="P45" s="1">
         <v>60</v>
       </c>
-      <c r="P45" s="1">
-        <v>0</v>
-      </c>
       <c r="Q45" s="1">
         <v>0</v>
       </c>
@@ -4017,16 +4084,16 @@
         <v>0</v>
       </c>
       <c r="S45" s="1">
+        <v>0</v>
+      </c>
+      <c r="T45" s="1">
         <v>100</v>
       </c>
-      <c r="T45" s="1">
-        <v>0</v>
-      </c>
       <c r="U45" s="1">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V45" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W45" s="1">
         <v>0</v>
@@ -4052,12 +4119,15 @@
       <c r="AD45" s="1">
         <v>0</v>
       </c>
-      <c r="AE45" s="6"/>
-      <c r="AF45" s="1">
+      <c r="AE45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF45" s="6"/>
+      <c r="AG45" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C46" s="1">
         <v>4003</v>
       </c>
@@ -4068,35 +4138,35 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G46" s="2" t="s">
+      <c r="H46" s="1">
+        <v>0</v>
+      </c>
+      <c r="I46" s="1">
+        <v>0</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="L46" s="1">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
+        <v>-1</v>
+      </c>
+      <c r="O46" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H46" s="1">
-        <v>0</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="K46" s="1">
-        <v>0</v>
-      </c>
-      <c r="L46" s="1">
-        <v>0</v>
-      </c>
-      <c r="M46" s="1">
-        <v>-1</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O46" s="1">
+      <c r="P46" s="1">
         <v>60</v>
       </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
       <c r="Q46" s="1">
         <v>0</v>
       </c>
@@ -4104,11 +4174,11 @@
         <v>0</v>
       </c>
       <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1">
         <v>100</v>
       </c>
-      <c r="T46" s="1">
-        <v>0</v>
-      </c>
       <c r="U46" s="1">
         <v>0</v>
       </c>
@@ -4139,19 +4209,22 @@
       <c r="AD46" s="1">
         <v>0</v>
       </c>
-      <c r="AE46" s="1"/>
-      <c r="AF46" s="1">
+      <c r="AE46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AF46" s="1"/>
+      <c r="AG46" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G47" s="2"/>
     </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
     </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="C49" s="1">
         <v>9001</v>
       </c>
@@ -4162,22 +4235,22 @@
         <v>0</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H49" s="1">
         <v>0</v>
       </c>
-      <c r="I49" s="1" t="s">
-        <v>61</v>
+      <c r="I49" s="1">
+        <v>0</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0</v>
+        <v>63</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -4185,7 +4258,7 @@
       <c r="M49" s="1">
         <v>0</v>
       </c>
-      <c r="O49" s="1">
+      <c r="N49" s="1">
         <v>0</v>
       </c>
       <c r="P49" s="1">
@@ -4198,22 +4271,22 @@
         <v>0</v>
       </c>
       <c r="S49" s="1">
+        <v>0</v>
+      </c>
+      <c r="T49" s="1">
         <v>100</v>
       </c>
-      <c r="T49" s="1">
-        <v>0</v>
-      </c>
       <c r="U49" s="1">
         <v>0</v>
       </c>
-      <c r="W49" s="1">
-        <v>1</v>
+      <c r="V49" s="1">
+        <v>0</v>
       </c>
       <c r="X49" s="1">
         <v>1</v>
       </c>
       <c r="Y49" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z49" s="1">
         <v>0</v>
@@ -4230,26 +4303,28 @@
       <c r="AD49" s="1">
         <v>0</v>
       </c>
-      <c r="AF49" s="1">
+      <c r="AE49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="1">
         <v>50</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" customHeight="1"/>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G51" s="2"/>
     </row>
-    <row r="52" customHeight="1" spans="3:32">
+    <row r="52" customHeight="1" spans="3:33">
       <c r="E52" s="1"/>
-      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
-      <c r="Q52" s="1"/>
+      <c r="M52" s="1"/>
       <c r="R52" s="1"/>
-      <c r="T52" s="1"/>
+      <c r="S52" s="1"/>
       <c r="U52" s="1"/>
       <c r="V52" s="1"/>
-      <c r="Y52" s="1"/>
+      <c r="W52" s="1"/>
       <c r="Z52" s="1"/>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
@@ -4257,14 +4332,14 @@
       <c r="AD52" s="1"/>
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
-    </row>
-    <row r="53" customHeight="1" spans="3:32">
+      <c r="AG52" s="1"/>
+    </row>
+    <row r="53" customHeight="1" spans="3:33">
       <c r="E53" s="1"/>
-      <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
-      <c r="P53" s="1"/>
+      <c r="M53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
@@ -4281,97 +4356,98 @@
       <c r="AD53" s="1"/>
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="3:32">
+      <c r="AG53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="3:33">
       <c r="E54" s="1"/>
-      <c r="K54" s="1"/>
       <c r="L54" s="1"/>
-      <c r="U54" s="1"/>
+      <c r="M54" s="1"/>
       <c r="V54" s="1"/>
-      <c r="Y54" s="1"/>
+      <c r="W54" s="1"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
-      <c r="AF54" s="1"/>
-    </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:32">
+      <c r="AB54" s="1"/>
+      <c r="AG54" s="1"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
       <c r="H55" s="1"/>
-      <c r="N55" s="2"/>
-      <c r="O55" s="1"/>
-      <c r="R55" s="2"/>
+      <c r="O55" s="2"/>
+      <c r="P55" s="1"/>
+      <c r="S55" s="2"/>
     </row>
     <row r="57" s="1" customFormat="1" customHeight="1"/>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G58" s="2"/>
     </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G59" s="2"/>
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1"/>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G61" s="2"/>
       <c r="H61" s="1"/>
-      <c r="AE61" s="6"/>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:32">
+      <c r="AF61" s="6"/>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G62" s="2"/>
     </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:32">
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G63" s="2"/>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1"/>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G65" s="2"/>
     </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G66" s="2"/>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G67" s="2"/>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G68" s="2"/>
       <c r="H68" s="1"/>
-      <c r="AE68" s="6"/>
+      <c r="AF68" s="6"/>
     </row>
     <row r="69" s="1" customFormat="1" customHeight="1"/>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G70" s="2"/>
     </row>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G71" s="2"/>
     </row>
     <row r="72" s="1" customFormat="1" customHeight="1"/>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="73" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G73" s="2"/>
     </row>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G74" s="2"/>
     </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G75" s="2"/>
       <c r="H75" s="1"/>
-      <c r="AE75" s="6"/>
+      <c r="AF75" s="6"/>
     </row>
     <row r="76" s="1" customFormat="1" customHeight="1"/>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G77" s="2"/>
     </row>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:31">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="R78" s="2"/>
-      <c r="U78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="S78" s="2"/>
       <c r="V78" s="2"/>
-    </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:31">
+      <c r="W78" s="2"/>
+    </row>
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G79" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:O5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3 I4:I5 C3:H5 L3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -278,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="139">
   <si>
     <t>_ID</t>
   </si>
@@ -683,6 +683,15 @@
   </si>
   <si>
     <t>复活自己并且免疫2S所有伤害，CD60S</t>
+  </si>
+  <si>
+    <t>英灵普攻</t>
+  </si>
+  <si>
+    <t>地狱火</t>
+  </si>
+  <si>
+    <t>对直线攻击距离内的敌人造成{0}%道攻+{1}点技能伤害</t>
   </si>
   <si>
     <t>普攻</t>
@@ -1666,7 +1675,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:AG79"/>
+  <dimension ref="C2:AG80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
@@ -3899,22 +3908,22 @@
         <v>10</v>
       </c>
       <c r="T40" s="1">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="U40" s="1">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="V40" s="1">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="W40" s="1">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="X40" s="1">
         <v>0</v>
       </c>
       <c r="Y40" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z40" s="1">
         <v>0</v>
@@ -4221,118 +4230,190 @@
       <c r="G47" s="2"/>
     </row>
     <row r="48" s="1" customFormat="1" customHeight="1" spans="3:33">
-      <c r="F48" s="2"/>
-      <c r="G48" s="2"/>
+      <c r="C48" s="1">
+        <v>5001</v>
+      </c>
+      <c r="D48" s="1">
+        <v>5001</v>
+      </c>
+      <c r="E48" s="1">
+        <v>0</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H48" s="1">
+        <v>9</v>
+      </c>
+      <c r="I48" s="1">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>10</v>
+      </c>
+      <c r="O48" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>3</v>
+      </c>
+      <c r="S48" s="1">
+        <v>10</v>
+      </c>
+      <c r="T48" s="1">
+        <v>110</v>
+      </c>
+      <c r="U48" s="1">
+        <v>1000</v>
+      </c>
+      <c r="V48" s="1">
+        <v>5</v>
+      </c>
+      <c r="W48" s="1">
+        <v>1000</v>
+      </c>
+      <c r="X48" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y48" s="1">
+        <v>2</v>
+      </c>
+      <c r="Z48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG48" s="1">
+        <v>99999</v>
+      </c>
     </row>
     <row r="49" s="1" customFormat="1" customHeight="1" spans="3:33">
-      <c r="C49" s="1">
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+    </row>
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="C50" s="1">
         <v>9001</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D50" s="1">
         <v>9001</v>
       </c>
-      <c r="E49" s="1">
-        <v>0</v>
-      </c>
-      <c r="F49" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H49" s="1">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1" t="s">
+      <c r="E50" s="1">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="H50" s="1">
+        <v>0</v>
+      </c>
+      <c r="I50" s="1">
+        <v>0</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="L49" s="1">
-        <v>0</v>
-      </c>
-      <c r="M49" s="1">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1">
-        <v>0</v>
-      </c>
-      <c r="P49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="1">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1">
-        <v>0</v>
-      </c>
-      <c r="T49" s="1">
+      <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1">
         <v>100</v>
       </c>
-      <c r="U49" s="1">
-        <v>0</v>
-      </c>
-      <c r="V49" s="1">
-        <v>0</v>
-      </c>
-      <c r="X49" s="1">
-        <v>1</v>
-      </c>
-      <c r="Y49" s="1">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AB49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AD49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AE49" s="1">
-        <v>0</v>
-      </c>
-      <c r="AG49" s="1">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="50" s="1" customFormat="1" customHeight="1"/>
-    <row r="51" s="1" customFormat="1" customHeight="1" spans="3:33">
-      <c r="G51" s="2"/>
-    </row>
-    <row r="52" customHeight="1" spans="3:33">
-      <c r="E52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="R52" s="1"/>
-      <c r="S52" s="1"/>
-      <c r="U52" s="1"/>
-      <c r="V52" s="1"/>
-      <c r="W52" s="1"/>
-      <c r="Z52" s="1"/>
-      <c r="AA52" s="1"/>
-      <c r="AB52" s="1"/>
-      <c r="AC52" s="1"/>
-      <c r="AD52" s="1"/>
-      <c r="AE52" s="1"/>
-      <c r="AF52" s="1"/>
-      <c r="AG52" s="1"/>
+      <c r="U50" s="1">
+        <v>0</v>
+      </c>
+      <c r="V50" s="1">
+        <v>0</v>
+      </c>
+      <c r="X50" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y50" s="1">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AB50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AD50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AG50" s="1">
+        <v>99999</v>
+      </c>
+    </row>
+    <row r="51" s="1" customFormat="1" customHeight="1"/>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="G52" s="2"/>
     </row>
     <row r="53" customHeight="1" spans="3:33">
       <c r="E53" s="1"/>
@@ -4340,15 +4421,11 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
-      <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
-      <c r="T53" s="1"/>
       <c r="U53" s="1"/>
       <c r="V53" s="1"/>
       <c r="W53" s="1"/>
-      <c r="X53" s="1"/>
-      <c r="Y53" s="1"/>
       <c r="Z53" s="1"/>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
@@ -4360,46 +4437,67 @@
     </row>
     <row r="54" customHeight="1" spans="3:33">
       <c r="E54" s="1"/>
+      <c r="J54" s="1"/>
+      <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
+      <c r="Q54" s="1"/>
+      <c r="R54" s="1"/>
+      <c r="S54" s="1"/>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
       <c r="V54" s="1"/>
       <c r="W54" s="1"/>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
       <c r="Z54" s="1"/>
       <c r="AA54" s="1"/>
       <c r="AB54" s="1"/>
+      <c r="AC54" s="1"/>
+      <c r="AD54" s="1"/>
+      <c r="AE54" s="1"/>
+      <c r="AF54" s="1"/>
       <c r="AG54" s="1"/>
     </row>
-    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:33">
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="1"/>
-      <c r="O55" s="2"/>
-      <c r="P55" s="1"/>
-      <c r="S55" s="2"/>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1"/>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:33">
-      <c r="G58" s="2"/>
-    </row>
+    <row r="55" customHeight="1" spans="3:33">
+      <c r="E55" s="1"/>
+      <c r="L55" s="1"/>
+      <c r="M55" s="1"/>
+      <c r="V55" s="1"/>
+      <c r="W55" s="1"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+      <c r="AB55" s="1"/>
+      <c r="AG55" s="1"/>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="1"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="1"/>
+      <c r="S56" s="2"/>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1"/>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G59" s="2"/>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1"/>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:33">
-      <c r="G61" s="2"/>
-      <c r="H61" s="1"/>
-      <c r="AF61" s="6"/>
-    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="G60" s="2"/>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1"/>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G62" s="2"/>
+      <c r="H62" s="1"/>
+      <c r="AF62" s="6"/>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:33">
       <c r="G63" s="2"/>
     </row>
-    <row r="64" s="1" customFormat="1" customHeight="1"/>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="6:32">
-      <c r="G65" s="2"/>
-    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="G64" s="2"/>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1"/>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G66" s="2"/>
     </row>
@@ -4408,46 +4506,49 @@
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G68" s="2"/>
-      <c r="H68" s="1"/>
-      <c r="AF68" s="6"/>
-    </row>
-    <row r="69" s="1" customFormat="1" customHeight="1"/>
-    <row r="70" s="1" customFormat="1" customHeight="1" spans="6:32">
-      <c r="G70" s="2"/>
-    </row>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="6:32">
+      <c r="G69" s="2"/>
+      <c r="H69" s="1"/>
+      <c r="AF69" s="6"/>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1"/>
     <row r="71" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G71" s="2"/>
     </row>
-    <row r="72" s="1" customFormat="1" customHeight="1"/>
-    <row r="73" s="1" customFormat="1" customHeight="1" spans="6:32">
-      <c r="G73" s="2"/>
-    </row>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="6:32">
+      <c r="G72" s="2"/>
+    </row>
+    <row r="73" s="1" customFormat="1" customHeight="1"/>
     <row r="74" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G74" s="2"/>
     </row>
     <row r="75" s="1" customFormat="1" customHeight="1" spans="6:32">
       <c r="G75" s="2"/>
-      <c r="H75" s="1"/>
-      <c r="AF75" s="6"/>
-    </row>
-    <row r="76" s="1" customFormat="1" customHeight="1"/>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="6:32">
-      <c r="G77" s="2"/>
-    </row>
+    </row>
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="6:32">
+      <c r="G76" s="2"/>
+      <c r="H76" s="1"/>
+      <c r="AF76" s="6"/>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1"/>
     <row r="78" s="1" customFormat="1" customHeight="1" spans="6:32">
-      <c r="F78" s="2"/>
       <c r="G78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="S78" s="2"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="2"/>
     </row>
     <row r="79" s="1" customFormat="1" customHeight="1" spans="6:32">
+      <c r="F79" s="2"/>
       <c r="G79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="S79" s="2"/>
+      <c r="V79" s="2"/>
+      <c r="W79" s="2"/>
+    </row>
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="6:32">
+      <c r="G80" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="I3 I4:I5 C3:H5 L3:P5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5 L3:P5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -879,12 +879,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -3613,7 +3613,7 @@
         <v>91</v>
       </c>
       <c r="L37" s="1">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M37" s="1">
         <v>0</v>
@@ -3637,16 +3637,16 @@
         <v>10</v>
       </c>
       <c r="T37" s="1">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="U37" s="1">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="V37" s="1">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="W37" s="1">
-        <v>100000</v>
+        <v>20000</v>
       </c>
       <c r="X37" s="1">
         <v>5</v>
@@ -4294,10 +4294,10 @@
         <v>1000</v>
       </c>
       <c r="X48" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y48" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z48" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -879,12 +879,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2077,7 +2077,7 @@
         <v>0</v>
       </c>
       <c r="AG6" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -2169,7 +2169,7 @@
         <v>0</v>
       </c>
       <c r="AG7" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="AF8" s="1"/>
       <c r="AG8" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="AF9" s="1"/>
       <c r="AG9" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -2447,7 +2447,7 @@
         <v>81</v>
       </c>
       <c r="AG10" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="AG11" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AF12" s="1"/>
       <c r="AG12" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="AG20" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="21" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -2797,7 +2797,7 @@
         <v>1000</v>
       </c>
       <c r="V21" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W21" s="1">
         <v>1000</v>
@@ -2827,7 +2827,7 @@
         <v>0</v>
       </c>
       <c r="AG21" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="AG22" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="23" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="AF23" s="1"/>
       <c r="AG23" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3104,7 +3104,7 @@
         <v>101</v>
       </c>
       <c r="AG24" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3191,7 +3191,7 @@
         <v>0</v>
       </c>
       <c r="AG25" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="AF26" s="1"/>
       <c r="AG26" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3396,7 +3396,7 @@
         <v>0</v>
       </c>
       <c r="AG34" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="AG35" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3581,7 +3581,7 @@
       </c>
       <c r="AF36" s="1"/>
       <c r="AG36" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3643,7 +3643,7 @@
         <v>20000</v>
       </c>
       <c r="V37" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="W37" s="1">
         <v>20000</v>
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="AG37" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3765,7 +3765,7 @@
         <v>120</v>
       </c>
       <c r="AG38" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3852,7 +3852,7 @@
         <v>0</v>
       </c>
       <c r="AG39" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:33">
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="AG40" s="1">
-        <v>100</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:33">

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -278,7 +278,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="139">
   <si>
     <t>_ID</t>
   </si>
@@ -622,7 +622,7 @@
     <t>施毒术</t>
   </si>
   <si>
-    <t>对{3}个敌人造成{0}%道术+{1}点技能伤害的持续{2}秒，按攻速结算</t>
+    <t>"203,50,5,2"</t>
   </si>
   <si>
     <t>圣疗术</t>
@@ -3529,7 +3529,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="P36" s="1">
         <v>10</v>
@@ -3544,22 +3544,22 @@
         <v>10</v>
       </c>
       <c r="T36" s="1">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="U36" s="1">
         <v>500</v>
       </c>
       <c r="V36" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="W36" s="1">
         <v>800</v>
       </c>
       <c r="X36" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y36" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z36" s="1">
         <v>0</v>
@@ -3579,7 +3579,9 @@
       <c r="AE36" s="1">
         <v>0</v>
       </c>
-      <c r="AF36" s="1"/>
+      <c r="AF36" s="1" t="s">
+        <v>114</v>
+      </c>
       <c r="AG36" s="1">
         <v>10000</v>
       </c>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -269,6 +269,40 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
+1 percent
+2 damage
+3 duration
+4 enemyMax
+5 row
+6 colunm
+7 speed
+8 cd
+9 dis
+10 atkRise
+11 finalRise
+12 crit
+13 deadly</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AI3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
 EffectId，EffectValue,持续时间，叠加层数</t>
         </r>
       </text>
@@ -278,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="165">
   <si>
     <t>_ID</t>
   </si>
@@ -361,6 +395,15 @@
     <t>伤害加成</t>
   </si>
   <si>
+    <t>等级增加的属性id</t>
+  </si>
+  <si>
+    <t>增加的值</t>
+  </si>
+  <si>
+    <t>等级增加的属性值</t>
+  </si>
+  <si>
     <t>附带效果</t>
   </si>
   <si>
@@ -451,6 +494,15 @@
     <t>DamageIncrea</t>
   </si>
   <si>
+    <t>RiseId</t>
+  </si>
+  <si>
+    <t>RiseVue</t>
+  </si>
+  <si>
+    <t>RiseRequireLevel</t>
+  </si>
+  <si>
     <t>EffectList</t>
   </si>
   <si>
@@ -463,6 +515,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>int[]</t>
+  </si>
+  <si>
     <t>string[]</t>
   </si>
   <si>
@@ -475,6 +530,15 @@
     <t>被动增加{0}%的物攻加成和{1}点物攻，无需上阵</t>
   </si>
   <si>
+    <t>2,1,2,1</t>
+  </si>
+  <si>
+    <t>1000,5,10000,10</t>
+  </si>
+  <si>
+    <t>5,10,15,20</t>
+  </si>
+  <si>
     <t>流光剑诀</t>
   </si>
   <si>
@@ -487,6 +551,12 @@
     <t>对直线攻击距离内的敌人造成{0}%物攻+{1}点技能伤害</t>
   </si>
   <si>
+    <t>1,10,7,8</t>
+  </si>
+  <si>
+    <t>30,50,20,20</t>
+  </si>
+  <si>
     <t>月华剑阵</t>
   </si>
   <si>
@@ -502,6 +572,12 @@
     <t>施展{4}*{5}范围的剑阵，持续{2}s，对其内的敌人造成{0}%物攻+{1}点伤害，按攻速结算</t>
   </si>
   <si>
+    <t>5,6,10,11</t>
+  </si>
+  <si>
+    <t>1,1,50,50</t>
+  </si>
+  <si>
     <t>蛮牛冲撞</t>
   </si>
   <si>
@@ -514,6 +590,12 @@
     <t>瞬移到敌人身后造成{0}%物攻+{1}点技能伤害，并且晕眩{2}秒</t>
   </si>
   <si>
+    <t>9,1,10,11</t>
+  </si>
+  <si>
+    <t>1,50,50,50</t>
+  </si>
+  <si>
     <t>龙魂护体</t>
   </si>
   <si>
@@ -523,6 +605,12 @@
     <t>生成一个{0}%生命的护盾</t>
   </si>
   <si>
+    <t>1,8,1,1</t>
+  </si>
+  <si>
+    <t>10,20,20,30</t>
+  </si>
+  <si>
     <t>"12,10,30,3"</t>
   </si>
   <si>
@@ -532,6 +620,9 @@
     <t>战士技能增加{0}%技能系数增幅，无需上阵</t>
   </si>
   <si>
+    <t>1,1,1,1</t>
+  </si>
+  <si>
     <t>火麟剑诀</t>
   </si>
   <si>
@@ -541,6 +632,12 @@
     <t>对单个敌人造成{0}%物攻+{1}点伤害</t>
   </si>
   <si>
+    <t>1,10,11,8</t>
+  </si>
+  <si>
+    <t>200,50,50,20</t>
+  </si>
+  <si>
     <t>冥想心法</t>
   </si>
   <si>
@@ -622,6 +719,9 @@
     <t>施毒术</t>
   </si>
   <si>
+    <t>4,4,10,11</t>
+  </si>
+  <si>
     <t>"203,50,5,2"</t>
   </si>
   <si>
@@ -634,6 +734,12 @@
     <t>恢复自己和队友的{0}%道术+{1}点生命</t>
   </si>
   <si>
+    <t>1,4,8,10</t>
+  </si>
+  <si>
+    <t>100,1,20,50</t>
+  </si>
+  <si>
     <t>太虚麟盾</t>
   </si>
   <si>
@@ -656,6 +762,12 @@
   </si>
   <si>
     <t>召唤{3}只神将战斗，攻击为{0}%*道攻+{1}，其他全额继承</t>
+  </si>
+  <si>
+    <t>1,1,1,4</t>
+  </si>
+  <si>
+    <t>5,10,15,1</t>
   </si>
   <si>
     <t>定身指环</t>
@@ -1356,6 +1468,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1675,7 +1788,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:AG80"/>
+  <dimension ref="C2:AJ80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="5.625" style="2" customWidth="1"/>
@@ -1702,15 +1815,17 @@
     <col min="28" max="28" width="9.625" style="2" customWidth="1"/>
     <col min="29" max="30" width="7.875" style="2" customWidth="1"/>
     <col min="31" max="31" width="9.75" style="2" customWidth="1"/>
-    <col min="32" max="32" width="21.75" style="2" customWidth="1"/>
-    <col min="33" max="33" width="11.75" style="2" customWidth="1"/>
-    <col min="34" max="16384" width="9" style="2"/>
+    <col min="32" max="32" width="19.5833333333333" style="2" customWidth="1"/>
+    <col min="33" max="33" width="15.4166666666667" style="2" customWidth="1"/>
+    <col min="34" max="35" width="19.5833333333333" style="2" customWidth="1"/>
+    <col min="36" max="36" width="11.75" style="2" customWidth="1"/>
+    <col min="37" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" customHeight="1" spans="3:33">
+    <row r="2" customHeight="1" spans="3:36">
       <c r="O2" s="3"/>
     </row>
-    <row r="3" customHeight="1" spans="3:33">
+    <row r="3" customHeight="1" spans="3:36">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1802,198 +1917,225 @@
       <c r="AG3" s="4" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" customHeight="1" spans="3:33">
+      <c r="AH3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ3" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" customHeight="1" spans="3:36">
       <c r="C4" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>2</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="3:33">
+        <v>61</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI4" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ4" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="3:36">
       <c r="C5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AE5" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="AF5" s="4" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="AG5" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:33">
+        <v>67</v>
+      </c>
+      <c r="AH5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="AJ5" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C6" s="1">
         <v>1001</v>
       </c>
@@ -2004,7 +2146,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
@@ -2014,7 +2156,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -2026,7 +2168,7 @@
         <v>10</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -2076,11 +2218,20 @@
       <c r="AE6" s="1">
         <v>0</v>
       </c>
-      <c r="AG6" s="1">
+      <c r="AF6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH6" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ6" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C7" s="1">
         <v>1002</v>
       </c>
@@ -2091,10 +2242,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="H7" s="1">
         <v>9</v>
@@ -2103,10 +2254,10 @@
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -2118,7 +2269,7 @@
         <v>10</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="P7" s="1">
         <v>1</v>
@@ -2168,11 +2319,20 @@
       <c r="AE7" s="1">
         <v>0</v>
       </c>
-      <c r="AG7" s="1">
+      <c r="AF7" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ7" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C8" s="1">
         <v>1003</v>
       </c>
@@ -2183,10 +2343,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="H8" s="1">
         <v>5</v>
@@ -2195,10 +2355,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -2210,7 +2370,7 @@
         <v>10</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="P8" s="1">
         <v>10</v>
@@ -2260,12 +2420,21 @@
       <c r="AE8" s="1">
         <v>0</v>
       </c>
-      <c r="AF8" s="1"/>
-      <c r="AG8" s="1">
+      <c r="AF8" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG8" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C9" s="1">
         <v>1004</v>
       </c>
@@ -2276,10 +2445,10 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -2288,10 +2457,10 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -2303,7 +2472,7 @@
         <v>10</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="P9" s="1">
         <v>8</v>
@@ -2353,12 +2522,21 @@
       <c r="AE9" s="1">
         <v>0</v>
       </c>
-      <c r="AF9" s="1"/>
-      <c r="AG9" s="1">
+      <c r="AF9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH9" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C10" s="1">
         <v>1005</v>
       </c>
@@ -2369,10 +2547,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="H10" s="1">
         <v>6</v>
@@ -2381,7 +2559,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L10" s="1">
         <v>5</v>
@@ -2393,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="P10" s="1">
         <v>60</v>
@@ -2414,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="V10" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
@@ -2443,14 +2621,23 @@
       <c r="AE10" s="1">
         <v>0</v>
       </c>
-      <c r="AF10" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AG10" s="1">
+      <c r="AF10" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH10" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AJ10" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C11" s="1">
         <v>1006</v>
       </c>
@@ -2461,7 +2648,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1">
@@ -2471,7 +2658,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
@@ -2483,7 +2670,7 @@
         <v>10</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -2533,11 +2720,20 @@
       <c r="AE11" s="1">
         <v>0</v>
       </c>
-      <c r="AG11" s="1">
+      <c r="AF11" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ11" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C12" s="1">
         <v>1007</v>
       </c>
@@ -2548,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="H12" s="1">
         <v>9</v>
@@ -2560,10 +2756,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -2575,7 +2771,7 @@
         <v>10</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="P12" s="1">
         <v>10</v>
@@ -2625,33 +2821,57 @@
       <c r="AE12" s="1">
         <v>0</v>
       </c>
-      <c r="AF12" s="1"/>
-      <c r="AG12" s="1">
+      <c r="AF12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH12" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI12" s="1"/>
+      <c r="AJ12" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G13" s="2"/>
     </row>
-    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:33">
+    <row r="14" s="2" customFormat="1" customHeight="1" spans="3:36">
       <c r="AF14" s="1"/>
-    </row>
-    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="1"/>
+      <c r="AI14" s="1"/>
+    </row>
+    <row r="15" s="2" customFormat="1" customHeight="1" spans="3:36">
       <c r="AF15" s="1"/>
-    </row>
-    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AG15" s="1"/>
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1"/>
+    </row>
+    <row r="16" s="2" customFormat="1" customHeight="1" spans="3:36">
       <c r="AF16" s="1"/>
-    </row>
-    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
+      <c r="AI16" s="1"/>
+    </row>
+    <row r="17" s="2" customFormat="1" customHeight="1" spans="3:36">
       <c r="AF17" s="1"/>
-    </row>
-    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+      <c r="AI17" s="1"/>
+    </row>
+    <row r="18" s="2" customFormat="1" customHeight="1" spans="3:36">
       <c r="AF18" s="1"/>
-    </row>
-    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+      <c r="AI18" s="1"/>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G19" s="2"/>
     </row>
-    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C20" s="1">
         <v>2001</v>
       </c>
@@ -2662,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2672,7 +2892,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -2684,7 +2904,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="P20" s="1">
         <v>0</v>
@@ -2734,11 +2954,20 @@
       <c r="AE20" s="1">
         <v>0</v>
       </c>
-      <c r="AG20" s="1">
+      <c r="AF20" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH20" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ20" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="21" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C21" s="1">
         <v>2002</v>
       </c>
@@ -2749,10 +2978,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -2761,10 +2990,10 @@
         <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -2776,7 +3005,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="P21" s="1">
         <v>1</v>
@@ -2826,11 +3055,20 @@
       <c r="AE21" s="1">
         <v>0</v>
       </c>
-      <c r="AG21" s="1">
+      <c r="AF21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH21" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ21" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="22" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C22" s="1">
         <v>2003</v>
       </c>
@@ -2841,10 +3079,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>115</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
@@ -2853,10 +3091,10 @@
         <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -2868,7 +3106,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>95</v>
+        <v>116</v>
       </c>
       <c r="P22" s="1">
         <v>10</v>
@@ -2918,11 +3156,20 @@
       <c r="AE22" s="1">
         <v>0</v>
       </c>
-      <c r="AG22" s="1">
+      <c r="AF22" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH22" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ22" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="23" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C23" s="1">
         <v>2004</v>
       </c>
@@ -2933,10 +3180,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>96</v>
+        <v>117</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="H23" s="1">
         <v>3</v>
@@ -2945,10 +3192,10 @@
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
@@ -2960,7 +3207,7 @@
         <v>10</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="P23" s="1">
         <v>5</v>
@@ -3010,12 +3257,21 @@
       <c r="AE23" s="1">
         <v>0</v>
       </c>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1">
+      <c r="AF23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG23" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH23" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI23" s="1"/>
+      <c r="AJ23" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="24" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C24" s="1">
         <v>2005</v>
       </c>
@@ -3026,10 +3282,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -3038,7 +3294,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
@@ -3050,7 +3306,7 @@
         <v>50</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="P24" s="1">
         <v>60</v>
@@ -3071,7 +3327,7 @@
         <v>0</v>
       </c>
       <c r="V24" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W24" s="1">
         <v>0</v>
@@ -3100,14 +3356,23 @@
       <c r="AE24" s="1">
         <v>0</v>
       </c>
-      <c r="AF24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AG24" s="1">
+      <c r="AF24" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH24" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI24" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="AJ24" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="25" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C25" s="1">
         <v>2006</v>
       </c>
@@ -3118,7 +3383,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
@@ -3128,7 +3393,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -3140,7 +3405,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="P25" s="1">
         <v>0</v>
@@ -3190,11 +3455,20 @@
       <c r="AE25" s="1">
         <v>0</v>
       </c>
-      <c r="AG25" s="1">
+      <c r="AF25" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ25" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="26" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C26" s="1">
         <v>2007</v>
       </c>
@@ -3205,10 +3479,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="H26" s="1">
         <v>3</v>
@@ -3217,10 +3491,10 @@
         <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -3232,7 +3506,7 @@
         <v>10</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="P26" s="1">
         <v>15</v>
@@ -3282,37 +3556,46 @@
       <c r="AE26" s="1">
         <v>0</v>
       </c>
-      <c r="AF26" s="1"/>
-      <c r="AG26" s="1">
+      <c r="AF26" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AG26" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH26" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G27" s="2"/>
     </row>
-    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="28" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G28" s="2"/>
     </row>
-    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G29" s="2"/>
     </row>
-    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="30" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G30" s="2"/>
       <c r="H30" s="1"/>
       <c r="O30" s="2"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G31" s="2"/>
       <c r="H31" s="1"/>
       <c r="O31" s="2"/>
     </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="O32" s="2"/>
     </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G33" s="2"/>
     </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C34" s="1">
         <v>3001</v>
       </c>
@@ -3323,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
@@ -3333,7 +3616,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -3345,7 +3628,7 @@
         <v>20</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="P34" s="1">
         <v>0</v>
@@ -3395,11 +3678,20 @@
       <c r="AE34" s="1">
         <v>0</v>
       </c>
-      <c r="AG34" s="1">
+      <c r="AF34" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AG34" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH34" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ34" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C35" s="1">
         <v>3002</v>
       </c>
@@ -3410,10 +3702,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -3422,10 +3714,10 @@
         <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -3437,7 +3729,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="P35" s="1">
         <v>1</v>
@@ -3487,11 +3779,20 @@
       <c r="AE35" s="1">
         <v>0</v>
       </c>
-      <c r="AG35" s="1">
+      <c r="AF35" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="AG35" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="AH35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ35" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C36" s="1">
         <v>3003</v>
       </c>
@@ -3502,10 +3803,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>112</v>
+        <v>133</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -3514,10 +3815,10 @@
         <v>1</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -3529,7 +3830,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="P36" s="1">
         <v>10</v>
@@ -3579,14 +3880,23 @@
       <c r="AE36" s="1">
         <v>0</v>
       </c>
-      <c r="AF36" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="AG36" s="1">
+      <c r="AF36" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG36" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="AH36" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI36" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AJ36" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C37" s="1">
         <v>3004</v>
       </c>
@@ -3597,10 +3907,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="H37" s="1">
         <v>8</v>
@@ -3609,10 +3919,10 @@
         <v>1</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -3624,7 +3934,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="P37" s="1">
         <v>15</v>
@@ -3674,11 +3984,20 @@
       <c r="AE37" s="1">
         <v>0</v>
       </c>
-      <c r="AG37" s="1">
+      <c r="AF37" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AG37" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="AH37" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ37" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C38" s="1">
         <v>3005</v>
       </c>
@@ -3689,10 +4008,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>119</v>
+        <v>143</v>
       </c>
       <c r="H38" s="1">
         <v>6</v>
@@ -3701,7 +4020,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L38" s="1">
         <v>5</v>
@@ -3713,7 +4032,7 @@
         <v>50</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="P38" s="1">
         <v>60</v>
@@ -3734,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="V38" s="1">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="W38" s="1">
         <v>0</v>
@@ -3763,14 +4082,23 @@
       <c r="AE38" s="1">
         <v>0</v>
       </c>
-      <c r="AF38" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AG38" s="1">
+      <c r="AF38" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG38" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH38" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AI38" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AJ38" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C39" s="1">
         <v>3006</v>
       </c>
@@ -3781,7 +4109,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
@@ -3791,7 +4119,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -3803,7 +4131,7 @@
         <v>10</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>122</v>
+        <v>146</v>
       </c>
       <c r="P39" s="1">
         <v>0</v>
@@ -3853,11 +4181,20 @@
       <c r="AE39" s="1">
         <v>0</v>
       </c>
-      <c r="AG39" s="1">
+      <c r="AF39" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="AG39" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AH39" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ39" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C40" s="1">
         <v>3007</v>
       </c>
@@ -3868,10 +4205,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>124</v>
+        <v>148</v>
       </c>
       <c r="H40" s="1">
         <v>4</v>
@@ -3880,10 +4217,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
@@ -3895,7 +4232,7 @@
         <v>100</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="P40" s="1">
         <v>30</v>
@@ -3945,20 +4282,29 @@
       <c r="AE40" s="1">
         <v>0</v>
       </c>
-      <c r="AG40" s="1">
+      <c r="AF40" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="AG40" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="AH40" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="AJ40" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G41" s="2"/>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G42" s="2"/>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G43" s="2"/>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C44" s="1">
         <v>4001</v>
       </c>
@@ -3969,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>126</v>
+        <v>152</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -3981,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -3993,7 +4339,7 @@
         <v>-100</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>128</v>
+        <v>154</v>
       </c>
       <c r="P44" s="1">
         <v>30</v>
@@ -4043,12 +4389,11 @@
       <c r="AE44" s="1">
         <v>0</v>
       </c>
-      <c r="AF44" s="1"/>
-      <c r="AG44" s="1">
+      <c r="AJ44" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C45" s="1">
         <v>4002</v>
       </c>
@@ -4059,10 +4404,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -4071,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -4083,7 +4428,7 @@
         <v>200</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="P45" s="1">
         <v>60</v>
@@ -4134,11 +4479,14 @@
         <v>0</v>
       </c>
       <c r="AF45" s="6"/>
-      <c r="AG45" s="1">
+      <c r="AG45" s="6"/>
+      <c r="AH45" s="6"/>
+      <c r="AI45" s="6"/>
+      <c r="AJ45" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C46" s="1">
         <v>4003</v>
       </c>
@@ -4149,10 +4497,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -4161,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
@@ -4173,7 +4521,7 @@
         <v>-1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="P46" s="1">
         <v>60</v>
@@ -4223,15 +4571,14 @@
       <c r="AE46" s="1">
         <v>0</v>
       </c>
-      <c r="AF46" s="1"/>
-      <c r="AG46" s="1">
+      <c r="AJ46" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="47" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G47" s="2"/>
     </row>
-    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="48" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C48" s="1">
         <v>5001</v>
       </c>
@@ -4242,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>135</v>
+        <v>161</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>136</v>
+        <v>162</v>
       </c>
       <c r="H48" s="1">
         <v>9</v>
@@ -4254,10 +4601,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L48" s="1">
         <v>0</v>
@@ -4269,7 +4616,7 @@
         <v>10</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="P48" s="1">
         <v>0</v>
@@ -4319,15 +4666,15 @@
       <c r="AE48" s="1">
         <v>0</v>
       </c>
-      <c r="AG48" s="1">
+      <c r="AJ48" s="1">
         <v>99999</v>
       </c>
     </row>
-    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="49" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
     </row>
-    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="50" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="C50" s="1">
         <v>9001</v>
       </c>
@@ -4338,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -4350,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="L50" s="1">
         <v>0</v>
@@ -4409,15 +4756,15 @@
       <c r="AE50" s="1">
         <v>0</v>
       </c>
-      <c r="AG50" s="1">
+      <c r="AJ50" s="1">
         <v>99999</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" customHeight="1"/>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G52" s="2"/>
     </row>
-    <row r="53" customHeight="1" spans="3:33">
+    <row r="53" customHeight="1" spans="3:36">
       <c r="E53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
@@ -4436,8 +4783,11 @@
       <c r="AE53" s="1"/>
       <c r="AF53" s="1"/>
       <c r="AG53" s="1"/>
-    </row>
-    <row r="54" customHeight="1" spans="3:33">
+      <c r="AH53" s="1"/>
+      <c r="AI53" s="1"/>
+      <c r="AJ53" s="1"/>
+    </row>
+    <row r="54" customHeight="1" spans="3:36">
       <c r="E54" s="1"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
@@ -4460,8 +4810,11 @@
       <c r="AE54" s="1"/>
       <c r="AF54" s="1"/>
       <c r="AG54" s="1"/>
-    </row>
-    <row r="55" customHeight="1" spans="3:33">
+      <c r="AH54" s="1"/>
+      <c r="AI54" s="1"/>
+      <c r="AJ54" s="1"/>
+    </row>
+    <row r="55" customHeight="1" spans="3:36">
       <c r="E55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
@@ -4470,9 +4823,9 @@
       <c r="Z55" s="1"/>
       <c r="AA55" s="1"/>
       <c r="AB55" s="1"/>
-      <c r="AG55" s="1"/>
-    </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AJ55" s="1"/>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="F56" s="2"/>
       <c r="G56" s="2"/>
       <c r="H56" s="1"/>
@@ -4481,63 +4834,72 @@
       <c r="S56" s="2"/>
     </row>
     <row r="58" s="1" customFormat="1" customHeight="1"/>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G59" s="2"/>
     </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G60" s="2"/>
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1"/>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G62" s="2"/>
       <c r="H62" s="1"/>
       <c r="AF62" s="6"/>
-    </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:33">
+      <c r="AG62" s="6"/>
+      <c r="AH62" s="6"/>
+      <c r="AI62" s="6"/>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G63" s="2"/>
     </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:33">
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:36">
       <c r="G64" s="2"/>
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1"/>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G66" s="2"/>
     </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G67" s="2"/>
     </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G68" s="2"/>
     </row>
-    <row r="69" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G69" s="2"/>
       <c r="H69" s="1"/>
       <c r="AF69" s="6"/>
+      <c r="AG69" s="6"/>
+      <c r="AH69" s="6"/>
+      <c r="AI69" s="6"/>
     </row>
     <row r="70" s="1" customFormat="1" customHeight="1"/>
-    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G71" s="2"/>
     </row>
-    <row r="72" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G72" s="2"/>
     </row>
     <row r="73" s="1" customFormat="1" customHeight="1"/>
-    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="74" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G74" s="2"/>
     </row>
-    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="75" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G75" s="2"/>
     </row>
-    <row r="76" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="76" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G76" s="2"/>
       <c r="H76" s="1"/>
       <c r="AF76" s="6"/>
+      <c r="AG76" s="6"/>
+      <c r="AH76" s="6"/>
+      <c r="AI76" s="6"/>
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1"/>
-    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="78" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G78" s="2"/>
     </row>
-    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="79" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
       <c r="O79" s="2"/>
@@ -4545,7 +4907,7 @@
       <c r="V79" s="2"/>
       <c r="W79" s="2"/>
     </row>
-    <row r="80" s="1" customFormat="1" customHeight="1" spans="6:32">
+    <row r="80" s="1" customFormat="1" customHeight="1" spans="6:35">
       <c r="G80" s="2"/>
     </row>
   </sheetData>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -551,7 +551,7 @@
     <t>对直线攻击距离内的敌人造成{0}%物攻+{1}点技能伤害</t>
   </si>
   <si>
-    <t>1,10,7,8</t>
+    <t>1,10,8,7</t>
   </si>
   <si>
     <t>30,50,20,20</t>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -991,12 +991,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2403,10 +2403,10 @@
         <v>0</v>
       </c>
       <c r="Z8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA8" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB8" s="1">
         <v>0</v>
@@ -3139,10 +3139,10 @@
         <v>0</v>
       </c>
       <c r="Z22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AA22" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AB22" s="1">
         <v>0</v>
@@ -3857,10 +3857,10 @@
         <v>800</v>
       </c>
       <c r="X36" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y36" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z36" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -551,10 +551,10 @@
     <t>对直线攻击距离内的敌人造成{0}%物攻+{1}点技能伤害</t>
   </si>
   <si>
-    <t>1,10,8,7</t>
-  </si>
-  <si>
-    <t>30,50,20,20</t>
+    <t>8,7,1,10</t>
+  </si>
+  <si>
+    <t>20,20,30,50</t>
   </si>
   <si>
     <t>月华剑阵</t>
@@ -991,12 +991,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -3949,13 +3949,13 @@
         <v>10</v>
       </c>
       <c r="T37" s="1">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="U37" s="1">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="V37" s="1">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="W37" s="1">
         <v>20000</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -629,7 +629,10 @@
     <t>烈火</t>
   </si>
   <si>
-    <t>对单个敌人造成{0}%物攻+{1}点伤害</t>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>对3个敌人造成{0}%物攻+{1}点伤害</t>
   </si>
   <si>
     <t>1,10,11,8</t>
@@ -648,9 +651,6 @@
   </si>
   <si>
     <t>雷电术</t>
-  </si>
-  <si>
-    <t>Circle</t>
   </si>
   <si>
     <t>对{3}个敌人造成{0}%魔法+{1}点技能伤害</t>
@@ -2750,16 +2750,16 @@
         <v>104</v>
       </c>
       <c r="H12" s="1">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>10</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P12" s="1">
         <v>10</v>
@@ -2798,10 +2798,10 @@
         <v>10000</v>
       </c>
       <c r="X12" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y12" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Z12" s="1">
         <v>0</v>
@@ -2822,10 +2822,10 @@
         <v>0</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG12" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AH12" s="7" t="s">
         <v>74</v>
@@ -2882,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2904,7 +2904,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P20" s="1">
         <v>0</v>
@@ -2978,10 +2978,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -2993,7 +2993,7 @@
         <v>83</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -3717,7 +3717,7 @@
         <v>83</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -3818,7 +3818,7 @@
         <v>83</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -3922,7 +3922,7 @@
         <v>70</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="164">
   <si>
     <t>_ID</t>
   </si>
@@ -558,9 +558,6 @@
   </si>
   <si>
     <t>月华剑阵</t>
-  </si>
-  <si>
-    <t>剑二十三</t>
   </si>
   <si>
     <t>Enemy</t>
@@ -2345,8 +2342,8 @@
       <c r="F8" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>82</v>
+      <c r="G8" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="H8" s="1">
         <v>5</v>
@@ -2355,22 +2352,22 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>10</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>84</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>0</v>
-      </c>
-      <c r="N8" s="1">
-        <v>10</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>85</v>
       </c>
       <c r="P8" s="1">
         <v>10</v>
@@ -2421,10 +2418,10 @@
         <v>0</v>
       </c>
       <c r="AF8" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG8" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="AG8" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="AH8" s="7" t="s">
         <v>74</v>
@@ -2445,10 +2442,10 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>89</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -2457,22 +2454,22 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>10</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>10</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>91</v>
       </c>
       <c r="P9" s="1">
         <v>8</v>
@@ -2523,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="AF9" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="AG9" s="7" t="s">
         <v>92</v>
-      </c>
-      <c r="AG9" s="7" t="s">
-        <v>93</v>
       </c>
       <c r="AH9" s="7" t="s">
         <v>74</v>
@@ -2547,10 +2544,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="H10" s="1">
         <v>6</v>
@@ -2571,7 +2568,7 @@
         <v>50</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P10" s="1">
         <v>60</v>
@@ -2622,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="AF10" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG10" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="AG10" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="AH10" s="7" t="s">
         <v>74</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="AJ10" s="1">
         <v>10000</v>
@@ -2648,7 +2645,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1">
@@ -2670,7 +2667,7 @@
         <v>10</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -2721,7 +2718,7 @@
         <v>0</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG11" s="7" t="s">
         <v>74</v>
@@ -2744,10 +2741,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="H12" s="1">
         <v>2</v>
@@ -2756,22 +2753,22 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>10</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>105</v>
-      </c>
-      <c r="L12" s="1">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>10</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="P12" s="1">
         <v>10</v>
@@ -2822,10 +2819,10 @@
         <v>0</v>
       </c>
       <c r="AF12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AG12" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="AG12" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="AH12" s="7" t="s">
         <v>74</v>
@@ -2882,7 +2879,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2904,7 +2901,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P20" s="1">
         <v>0</v>
@@ -2978,10 +2975,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -2990,10 +2987,10 @@
         <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -3005,7 +3002,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P21" s="1">
         <v>1</v>
@@ -3079,10 +3076,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
@@ -3091,11 +3088,11 @@
         <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K22" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K22" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="L22" s="1">
         <v>0</v>
       </c>
@@ -3106,7 +3103,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P22" s="1">
         <v>10</v>
@@ -3157,10 +3154,10 @@
         <v>0</v>
       </c>
       <c r="AF22" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG22" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="AG22" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="AH22" s="7" t="s">
         <v>74</v>
@@ -3180,10 +3177,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="H23" s="1">
         <v>3</v>
@@ -3192,11 +3189,11 @@
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K23" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="L23" s="1">
         <v>0</v>
       </c>
@@ -3207,7 +3204,7 @@
         <v>10</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P23" s="1">
         <v>5</v>
@@ -3258,10 +3255,10 @@
         <v>0</v>
       </c>
       <c r="AF23" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG23" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="AG23" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="AH23" s="7" t="s">
         <v>74</v>
@@ -3282,10 +3279,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -3306,7 +3303,7 @@
         <v>50</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P24" s="1">
         <v>60</v>
@@ -3357,16 +3354,16 @@
         <v>0</v>
       </c>
       <c r="AF24" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG24" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="AG24" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="AH24" s="7" t="s">
         <v>74</v>
       </c>
       <c r="AI24" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AJ24" s="1">
         <v>10000</v>
@@ -3383,7 +3380,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
@@ -3405,7 +3402,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="P25" s="1">
         <v>0</v>
@@ -3456,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="AF25" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG25" s="7" t="s">
         <v>74</v>
@@ -3479,10 +3476,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="H26" s="1">
         <v>3</v>
@@ -3491,11 +3488,11 @@
         <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K26" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="K26" s="1" t="s">
-        <v>84</v>
-      </c>
       <c r="L26" s="1">
         <v>0</v>
       </c>
@@ -3506,7 +3503,7 @@
         <v>10</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P26" s="1">
         <v>15</v>
@@ -3557,10 +3554,10 @@
         <v>0</v>
       </c>
       <c r="AF26" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="AG26" s="7" t="s">
         <v>86</v>
-      </c>
-      <c r="AG26" s="7" t="s">
-        <v>87</v>
       </c>
       <c r="AH26" s="7" t="s">
         <v>74</v>
@@ -3606,7 +3603,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
@@ -3628,7 +3625,7 @@
         <v>20</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="P34" s="1">
         <v>0</v>
@@ -3702,10 +3699,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -3714,10 +3711,10 @@
         <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -3729,7 +3726,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P35" s="1">
         <v>1</v>
@@ -3803,10 +3800,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -3815,10 +3812,10 @@
         <v>1</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -3830,7 +3827,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P36" s="1">
         <v>10</v>
@@ -3881,16 +3878,16 @@
         <v>0</v>
       </c>
       <c r="AF36" s="7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AG36" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AH36" s="7" t="s">
         <v>74</v>
       </c>
       <c r="AI36" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="AJ36" s="1">
         <v>10000</v>
@@ -3907,10 +3904,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="H37" s="1">
         <v>8</v>
@@ -3922,7 +3919,7 @@
         <v>70</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -3934,7 +3931,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P37" s="1">
         <v>15</v>
@@ -3985,10 +3982,10 @@
         <v>0</v>
       </c>
       <c r="AF37" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="AG37" s="7" t="s">
         <v>140</v>
-      </c>
-      <c r="AG37" s="7" t="s">
-        <v>141</v>
       </c>
       <c r="AH37" s="7" t="s">
         <v>74</v>
@@ -4008,10 +4005,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="H38" s="1">
         <v>6</v>
@@ -4032,7 +4029,7 @@
         <v>50</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P38" s="1">
         <v>60</v>
@@ -4083,16 +4080,16 @@
         <v>0</v>
       </c>
       <c r="AF38" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="AG38" s="7" t="s">
         <v>97</v>
-      </c>
-      <c r="AG38" s="7" t="s">
-        <v>98</v>
       </c>
       <c r="AH38" s="7" t="s">
         <v>74</v>
       </c>
       <c r="AI38" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AJ38" s="1">
         <v>10000</v>
@@ -4109,7 +4106,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
@@ -4131,7 +4128,7 @@
         <v>10</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="P39" s="1">
         <v>0</v>
@@ -4182,7 +4179,7 @@
         <v>0</v>
       </c>
       <c r="AF39" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="AG39" s="7" t="s">
         <v>74</v>
@@ -4205,10 +4202,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G40" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="H40" s="1">
         <v>4</v>
@@ -4217,10 +4214,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="K40" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
@@ -4232,7 +4229,7 @@
         <v>100</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="P40" s="1">
         <v>30</v>
@@ -4283,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="AF40" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="AG40" s="7" t="s">
         <v>150</v>
-      </c>
-      <c r="AG40" s="7" t="s">
-        <v>151</v>
       </c>
       <c r="AH40" s="7" t="s">
         <v>74</v>
@@ -4315,10 +4312,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -4339,7 +4336,7 @@
         <v>-100</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="P44" s="1">
         <v>30</v>
@@ -4404,10 +4401,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G45" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -4428,7 +4425,7 @@
         <v>200</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="P45" s="1">
         <v>60</v>
@@ -4497,10 +4494,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G46" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -4521,7 +4518,7 @@
         <v>-1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="P46" s="1">
         <v>60</v>
@@ -4589,10 +4586,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="H48" s="1">
         <v>9</v>
@@ -4616,7 +4613,7 @@
         <v>10</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="P48" s="1">
         <v>0</v>
@@ -4685,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="165">
   <si>
     <t>_ID</t>
   </si>
@@ -555,6 +555,9 @@
   </si>
   <si>
     <t>20,20,30,50</t>
+  </si>
+  <si>
+    <t>月华剑网</t>
   </si>
   <si>
     <t>月华剑阵</t>
@@ -2343,7 +2346,7 @@
         <v>81</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H8" s="1">
         <v>5</v>
@@ -2352,10 +2355,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -2367,7 +2370,7 @@
         <v>10</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P8" s="1">
         <v>10</v>
@@ -2418,10 +2421,10 @@
         <v>0</v>
       </c>
       <c r="AF8" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG8" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH8" s="7" t="s">
         <v>74</v>
@@ -2442,10 +2445,10 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -2454,10 +2457,10 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -2469,7 +2472,7 @@
         <v>10</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="P9" s="1">
         <v>8</v>
@@ -2520,10 +2523,10 @@
         <v>0</v>
       </c>
       <c r="AF9" s="7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG9" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AH9" s="7" t="s">
         <v>74</v>
@@ -2544,10 +2547,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H10" s="1">
         <v>6</v>
@@ -2568,7 +2571,7 @@
         <v>50</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P10" s="1">
         <v>60</v>
@@ -2619,16 +2622,16 @@
         <v>0</v>
       </c>
       <c r="AF10" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG10" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AH10" s="7" t="s">
         <v>74</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AJ10" s="1">
         <v>10000</v>
@@ -2645,7 +2648,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1">
@@ -2667,7 +2670,7 @@
         <v>10</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -2718,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG11" s="7" t="s">
         <v>74</v>
@@ -2741,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H12" s="1">
         <v>2</v>
@@ -2753,10 +2756,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -2768,7 +2771,7 @@
         <v>10</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="P12" s="1">
         <v>10</v>
@@ -2819,10 +2822,10 @@
         <v>0</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG12" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AH12" s="7" t="s">
         <v>74</v>
@@ -2879,7 +2882,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2901,7 +2904,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="P20" s="1">
         <v>0</v>
@@ -2975,10 +2978,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -2987,10 +2990,10 @@
         <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -3002,7 +3005,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="P21" s="1">
         <v>1</v>
@@ -3076,10 +3079,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
@@ -3088,10 +3091,10 @@
         <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -3103,7 +3106,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="P22" s="1">
         <v>10</v>
@@ -3154,10 +3157,10 @@
         <v>0</v>
       </c>
       <c r="AF22" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG22" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH22" s="7" t="s">
         <v>74</v>
@@ -3177,10 +3180,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" s="1">
         <v>3</v>
@@ -3189,10 +3192,10 @@
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
@@ -3204,7 +3207,7 @@
         <v>10</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="P23" s="1">
         <v>5</v>
@@ -3255,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="AF23" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG23" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH23" s="7" t="s">
         <v>74</v>
@@ -3279,10 +3282,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -3303,7 +3306,7 @@
         <v>50</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P24" s="1">
         <v>60</v>
@@ -3354,16 +3357,16 @@
         <v>0</v>
       </c>
       <c r="AF24" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG24" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AH24" s="7" t="s">
         <v>74</v>
       </c>
       <c r="AI24" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AJ24" s="1">
         <v>10000</v>
@@ -3380,7 +3383,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
@@ -3402,7 +3405,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="P25" s="1">
         <v>0</v>
@@ -3453,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="AF25" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG25" s="7" t="s">
         <v>74</v>
@@ -3476,10 +3479,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H26" s="1">
         <v>3</v>
@@ -3488,10 +3491,10 @@
         <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -3503,7 +3506,7 @@
         <v>10</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="P26" s="1">
         <v>15</v>
@@ -3554,10 +3557,10 @@
         <v>0</v>
       </c>
       <c r="AF26" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AG26" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH26" s="7" t="s">
         <v>74</v>
@@ -3603,7 +3606,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
@@ -3625,7 +3628,7 @@
         <v>20</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P34" s="1">
         <v>0</v>
@@ -3699,10 +3702,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -3711,10 +3714,10 @@
         <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -3726,7 +3729,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P35" s="1">
         <v>1</v>
@@ -3800,10 +3803,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -3812,10 +3815,10 @@
         <v>1</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -3827,7 +3830,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P36" s="1">
         <v>10</v>
@@ -3878,16 +3881,16 @@
         <v>0</v>
       </c>
       <c r="AF36" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AG36" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AH36" s="7" t="s">
         <v>74</v>
       </c>
       <c r="AI36" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AJ36" s="1">
         <v>10000</v>
@@ -3904,10 +3907,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H37" s="1">
         <v>8</v>
@@ -3919,7 +3922,7 @@
         <v>70</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -3931,7 +3934,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="P37" s="1">
         <v>15</v>
@@ -3982,10 +3985,10 @@
         <v>0</v>
       </c>
       <c r="AF37" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG37" s="7" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AH37" s="7" t="s">
         <v>74</v>
@@ -4005,10 +4008,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H38" s="1">
         <v>6</v>
@@ -4029,7 +4032,7 @@
         <v>50</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="P38" s="1">
         <v>60</v>
@@ -4080,16 +4083,16 @@
         <v>0</v>
       </c>
       <c r="AF38" s="7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG38" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AH38" s="7" t="s">
         <v>74</v>
       </c>
       <c r="AI38" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AJ38" s="1">
         <v>10000</v>
@@ -4106,7 +4109,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
@@ -4128,7 +4131,7 @@
         <v>10</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="P39" s="1">
         <v>0</v>
@@ -4179,7 +4182,7 @@
         <v>0</v>
       </c>
       <c r="AF39" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AG39" s="7" t="s">
         <v>74</v>
@@ -4202,10 +4205,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H40" s="1">
         <v>4</v>
@@ -4214,10 +4217,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
@@ -4229,7 +4232,7 @@
         <v>100</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P40" s="1">
         <v>30</v>
@@ -4280,10 +4283,10 @@
         <v>0</v>
       </c>
       <c r="AF40" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG40" s="7" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AH40" s="7" t="s">
         <v>74</v>
@@ -4312,10 +4315,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -4336,7 +4339,7 @@
         <v>-100</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="P44" s="1">
         <v>30</v>
@@ -4401,10 +4404,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -4425,7 +4428,7 @@
         <v>200</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P45" s="1">
         <v>60</v>
@@ -4494,10 +4497,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -4518,7 +4521,7 @@
         <v>-1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P46" s="1">
         <v>60</v>
@@ -4586,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H48" s="1">
         <v>9</v>
@@ -4613,7 +4616,7 @@
         <v>10</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P48" s="1">
         <v>0</v>
@@ -4682,10 +4685,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -2577,7 +2577,7 @@
         <v>60</v>
       </c>
       <c r="Q10" s="1">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="R10" s="1">
         <v>1</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="167">
   <si>
     <t>_ID</t>
   </si>
@@ -551,10 +551,10 @@
     <t>对直线攻击距离内的敌人造成{0}%物攻+{1}点技能伤害</t>
   </si>
   <si>
-    <t>8,7,1,10</t>
-  </si>
-  <si>
-    <t>20,20,30,50</t>
+    <t>8,7,10,11</t>
+  </si>
+  <si>
+    <t>20,20,30,30</t>
   </si>
   <si>
     <t>月华剑网</t>
@@ -575,129 +575,135 @@
     <t>5,6,10,11</t>
   </si>
   <si>
+    <t>1,1,30,30</t>
+  </si>
+  <si>
+    <t>蛮牛冲撞</t>
+  </si>
+  <si>
+    <t>野蛮</t>
+  </si>
+  <si>
+    <t>Chase</t>
+  </si>
+  <si>
+    <t>瞬移到敌人身后造成{0}%物攻+{1}点技能伤害，并且晕眩{2}秒</t>
+  </si>
+  <si>
+    <t>9,1,10,11</t>
+  </si>
+  <si>
+    <t>1,50,30,30</t>
+  </si>
+  <si>
+    <t>龙魂护体</t>
+  </si>
+  <si>
+    <t>武力盾</t>
+  </si>
+  <si>
+    <t>生成一个{0}%生命的护盾</t>
+  </si>
+  <si>
+    <t>1,8,1,1</t>
+  </si>
+  <si>
+    <t>10,20,20,30</t>
+  </si>
+  <si>
+    <t>"12,10,30,3"</t>
+  </si>
+  <si>
+    <t>无求易决</t>
+  </si>
+  <si>
+    <t>战士技能增加{0}%技能系数增幅，无需上阵</t>
+  </si>
+  <si>
+    <t>1,1,1,1</t>
+  </si>
+  <si>
+    <t>火麟剑诀</t>
+  </si>
+  <si>
+    <t>烈火</t>
+  </si>
+  <si>
+    <t>Circle</t>
+  </si>
+  <si>
+    <t>对3个敌人造成{0}%物攻+{1}点伤害</t>
+  </si>
+  <si>
+    <t>1,10,11,8</t>
+  </si>
+  <si>
+    <t>200,50,50,20</t>
+  </si>
+  <si>
+    <t>冥想心法</t>
+  </si>
+  <si>
+    <t>被动增加{0}%的魔攻加成和{1}点魔攻，无需上阵</t>
+  </si>
+  <si>
+    <t>紫电神雷</t>
+  </si>
+  <si>
+    <t>雷电术</t>
+  </si>
+  <si>
+    <t>对{3}个敌人造成{0}%魔法+{1}点技能伤害</t>
+  </si>
+  <si>
+    <t>火狱阵法</t>
+  </si>
+  <si>
+    <t>火墙</t>
+  </si>
+  <si>
+    <t>施展{4}*{5}范围的烈焰，持续{2}s，对其内的敌人造成{0}%魔法+{1}点伤害，按攻速结算</t>
+  </si>
+  <si>
+    <t>烈焰焚天</t>
+  </si>
+  <si>
+    <t>抗拒火环</t>
+  </si>
+  <si>
+    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点技能伤害</t>
+  </si>
+  <si>
+    <t>1,1,40,40</t>
+  </si>
+  <si>
+    <t>炎凰法盾</t>
+  </si>
+  <si>
+    <t>魔法盾</t>
+  </si>
+  <si>
+    <t>"13,10,30,3"</t>
+  </si>
+  <si>
+    <t>万法归宗</t>
+  </si>
+  <si>
+    <t>法师技能增加{0}%技能系数增幅，无需上阵</t>
+  </si>
+  <si>
+    <t>极寒冰暴</t>
+  </si>
+  <si>
+    <t>冰咆哮</t>
+  </si>
+  <si>
+    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点伤害</t>
+  </si>
+  <si>
     <t>1,1,50,50</t>
   </si>
   <si>
-    <t>蛮牛冲撞</t>
-  </si>
-  <si>
-    <t>野蛮</t>
-  </si>
-  <si>
-    <t>Chase</t>
-  </si>
-  <si>
-    <t>瞬移到敌人身后造成{0}%物攻+{1}点技能伤害，并且晕眩{2}秒</t>
-  </si>
-  <si>
-    <t>9,1,10,11</t>
-  </si>
-  <si>
-    <t>1,50,50,50</t>
-  </si>
-  <si>
-    <t>龙魂护体</t>
-  </si>
-  <si>
-    <t>武力盾</t>
-  </si>
-  <si>
-    <t>生成一个{0}%生命的护盾</t>
-  </si>
-  <si>
-    <t>1,8,1,1</t>
-  </si>
-  <si>
-    <t>10,20,20,30</t>
-  </si>
-  <si>
-    <t>"12,10,30,3"</t>
-  </si>
-  <si>
-    <t>无求易决</t>
-  </si>
-  <si>
-    <t>战士技能增加{0}%技能系数增幅，无需上阵</t>
-  </si>
-  <si>
-    <t>1,1,1,1</t>
-  </si>
-  <si>
-    <t>火麟剑诀</t>
-  </si>
-  <si>
-    <t>烈火</t>
-  </si>
-  <si>
-    <t>Circle</t>
-  </si>
-  <si>
-    <t>对3个敌人造成{0}%物攻+{1}点伤害</t>
-  </si>
-  <si>
-    <t>1,10,11,8</t>
-  </si>
-  <si>
-    <t>200,50,50,20</t>
-  </si>
-  <si>
-    <t>冥想心法</t>
-  </si>
-  <si>
-    <t>被动增加{0}%的魔攻加成和{1}点魔攻，无需上阵</t>
-  </si>
-  <si>
-    <t>紫电神雷</t>
-  </si>
-  <si>
-    <t>雷电术</t>
-  </si>
-  <si>
-    <t>对{3}个敌人造成{0}%魔法+{1}点技能伤害</t>
-  </si>
-  <si>
-    <t>火狱阵法</t>
-  </si>
-  <si>
-    <t>火墙</t>
-  </si>
-  <si>
-    <t>施展{4}*{5}范围的烈焰，持续{2}s，对其内的敌人造成{0}%魔法+{1}点伤害，按攻速结算</t>
-  </si>
-  <si>
-    <t>烈焰焚天</t>
-  </si>
-  <si>
-    <t>抗拒火环</t>
-  </si>
-  <si>
-    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点技能伤害</t>
-  </si>
-  <si>
-    <t>炎凰法盾</t>
-  </si>
-  <si>
-    <t>魔法盾</t>
-  </si>
-  <si>
-    <t>"13,10,30,3"</t>
-  </si>
-  <si>
-    <t>万法归宗</t>
-  </si>
-  <si>
-    <t>法师技能增加{0}%技能系数增幅，无需上阵</t>
-  </si>
-  <si>
-    <t>极寒冰暴</t>
-  </si>
-  <si>
-    <t>冰咆哮</t>
-  </si>
-  <si>
-    <t>对{4}*{5}范围内的敌人造成{0}%魔法+{1}点伤害</t>
-  </si>
-  <si>
     <t>清心咒</t>
   </si>
   <si>
@@ -737,7 +743,7 @@
     <t>1,4,8,10</t>
   </si>
   <si>
-    <t>100,1,20,50</t>
+    <t>100,1,20,80</t>
   </si>
   <si>
     <t>太虚麟盾</t>
@@ -3261,7 +3267,7 @@
         <v>86</v>
       </c>
       <c r="AG23" s="7" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="AH23" s="7" t="s">
         <v>74</v>
@@ -3282,10 +3288,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -3366,7 +3372,7 @@
         <v>74</v>
       </c>
       <c r="AI24" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AJ24" s="1">
         <v>10000</v>
@@ -3383,7 +3389,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
@@ -3405,7 +3411,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="P25" s="1">
         <v>0</v>
@@ -3479,10 +3485,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H26" s="1">
         <v>3</v>
@@ -3506,7 +3512,7 @@
         <v>10</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="P26" s="1">
         <v>15</v>
@@ -3560,7 +3566,7 @@
         <v>86</v>
       </c>
       <c r="AG26" s="7" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="AH26" s="7" t="s">
         <v>74</v>
@@ -3606,7 +3612,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
@@ -3628,7 +3634,7 @@
         <v>20</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="P34" s="1">
         <v>0</v>
@@ -3702,10 +3708,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -3729,7 +3735,7 @@
         <v>10</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="P35" s="1">
         <v>1</v>
@@ -3803,10 +3809,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -3830,7 +3836,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="P36" s="1">
         <v>10</v>
@@ -3881,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="AF36" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AG36" s="7" t="s">
         <v>87</v>
@@ -3890,7 +3896,7 @@
         <v>74</v>
       </c>
       <c r="AI36" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AJ36" s="1">
         <v>10000</v>
@@ -3907,10 +3913,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H37" s="1">
         <v>8</v>
@@ -3934,7 +3940,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="P37" s="1">
         <v>15</v>
@@ -3985,10 +3991,10 @@
         <v>0</v>
       </c>
       <c r="AF37" s="7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AG37" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AH37" s="7" t="s">
         <v>74</v>
@@ -4008,10 +4014,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H38" s="1">
         <v>6</v>
@@ -4092,7 +4098,7 @@
         <v>74</v>
       </c>
       <c r="AI38" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AJ38" s="1">
         <v>10000</v>
@@ -4109,7 +4115,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
@@ -4131,7 +4137,7 @@
         <v>10</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="P39" s="1">
         <v>0</v>
@@ -4205,10 +4211,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="H40" s="1">
         <v>4</v>
@@ -4232,7 +4238,7 @@
         <v>100</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P40" s="1">
         <v>30</v>
@@ -4283,10 +4289,10 @@
         <v>0</v>
       </c>
       <c r="AF40" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG40" s="7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="AH40" s="7" t="s">
         <v>74</v>
@@ -4315,10 +4321,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -4339,7 +4345,7 @@
         <v>-100</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P44" s="1">
         <v>30</v>
@@ -4404,10 +4410,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -4428,7 +4434,7 @@
         <v>200</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="P45" s="1">
         <v>60</v>
@@ -4497,10 +4503,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -4521,7 +4527,7 @@
         <v>-1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P46" s="1">
         <v>60</v>
@@ -4589,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H48" s="1">
         <v>9</v>
@@ -4616,7 +4622,7 @@
         <v>10</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P48" s="1">
         <v>0</v>
@@ -4685,10 +4691,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -3243,13 +3248,13 @@
         <v>4</v>
       </c>
       <c r="Y23" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AA23" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB23" s="1">
         <v>0</v>
@@ -3542,13 +3547,13 @@
         <v>5</v>
       </c>
       <c r="Y26" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Z26" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AA26" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AB26" s="1">
         <v>0</v>

--- a/Excel/SkillConfig.xlsx
+++ b/Excel/SkillConfig.xlsx
@@ -317,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="168">
   <si>
     <t>_ID</t>
   </si>
@@ -518,6 +518,9 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>double</t>
   </si>
   <si>
     <t>int[]</t>
@@ -2083,7 +2086,7 @@
         <v>66</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q5" s="4" t="s">
         <v>65</v>
@@ -2131,16 +2134,16 @@
         <v>65</v>
       </c>
       <c r="AF5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AG5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AH5" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AJ5" s="4" t="s">
         <v>65</v>
@@ -2157,7 +2160,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1">
@@ -2167,7 +2170,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -2179,7 +2182,7 @@
         <v>10</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="P6" s="1">
         <v>0</v>
@@ -2230,13 +2233,13 @@
         <v>0</v>
       </c>
       <c r="AF6" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AG6" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH6" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ6" s="1">
         <v>10000</v>
@@ -2253,10 +2256,10 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H7" s="1">
         <v>9</v>
@@ -2265,10 +2268,10 @@
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -2280,10 +2283,10 @@
         <v>10</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="P7" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q7" s="1">
         <v>0</v>
@@ -2331,13 +2334,13 @@
         <v>0</v>
       </c>
       <c r="AF7" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG7" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH7" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ7" s="1">
         <v>10000</v>
@@ -2354,10 +2357,10 @@
         <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" s="1">
         <v>5</v>
@@ -2366,10 +2369,10 @@
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -2381,7 +2384,7 @@
         <v>10</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P8" s="1">
         <v>10</v>
@@ -2432,13 +2435,13 @@
         <v>0</v>
       </c>
       <c r="AF8" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG8" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH8" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI8" s="1"/>
       <c r="AJ8" s="1">
@@ -2456,10 +2459,10 @@
         <v>4</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H9" s="1">
         <v>0</v>
@@ -2468,10 +2471,10 @@
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -2483,7 +2486,7 @@
         <v>10</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P9" s="1">
         <v>8</v>
@@ -2534,13 +2537,13 @@
         <v>0</v>
       </c>
       <c r="AF9" s="7" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG9" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AH9" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI9" s="1"/>
       <c r="AJ9" s="1">
@@ -2558,10 +2561,10 @@
         <v>5</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H10" s="1">
         <v>6</v>
@@ -2570,7 +2573,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L10" s="1">
         <v>5</v>
@@ -2582,7 +2585,7 @@
         <v>50</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P10" s="1">
         <v>60</v>
@@ -2633,16 +2636,16 @@
         <v>0</v>
       </c>
       <c r="AF10" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG10" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AH10" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI10" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AJ10" s="1">
         <v>10000</v>
@@ -2659,7 +2662,7 @@
         <v>6</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1">
@@ -2669,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
@@ -2681,7 +2684,7 @@
         <v>10</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="P11" s="1">
         <v>0</v>
@@ -2732,13 +2735,13 @@
         <v>0</v>
       </c>
       <c r="AF11" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG11" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH11" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ11" s="1">
         <v>10000</v>
@@ -2755,10 +2758,10 @@
         <v>7</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" s="1">
         <v>2</v>
@@ -2767,10 +2770,10 @@
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -2782,7 +2785,7 @@
         <v>10</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="P12" s="1">
         <v>10</v>
@@ -2833,13 +2836,13 @@
         <v>0</v>
       </c>
       <c r="AF12" s="7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG12" s="7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AH12" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI12" s="1"/>
       <c r="AJ12" s="1">
@@ -2893,7 +2896,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1">
@@ -2903,7 +2906,7 @@
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -2915,7 +2918,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P20" s="1">
         <v>0</v>
@@ -2966,13 +2969,13 @@
         <v>0</v>
       </c>
       <c r="AF20" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AG20" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH20" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ20" s="1">
         <v>10000</v>
@@ -2989,10 +2992,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H21" s="1">
         <v>2</v>
@@ -3001,10 +3004,10 @@
         <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -3016,10 +3019,10 @@
         <v>10</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="P21" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q21" s="1">
         <v>0</v>
@@ -3067,13 +3070,13 @@
         <v>0</v>
       </c>
       <c r="AF21" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG21" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH21" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ21" s="1">
         <v>10000</v>
@@ -3090,10 +3093,10 @@
         <v>3</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H22" s="1">
         <v>5</v>
@@ -3102,10 +3105,10 @@
         <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -3117,7 +3120,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="P22" s="1">
         <v>10</v>
@@ -3168,13 +3171,13 @@
         <v>0</v>
       </c>
       <c r="AF22" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG22" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH22" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ22" s="1">
         <v>10000</v>
@@ -3191,10 +3194,10 @@
         <v>4</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H23" s="1">
         <v>3</v>
@@ -3203,10 +3206,10 @@
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L23" s="1">
         <v>0</v>
@@ -3218,7 +3221,7 @@
         <v>10</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="P23" s="1">
         <v>5</v>
@@ -3269,13 +3272,13 @@
         <v>0</v>
       </c>
       <c r="AF23" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG23" s="7" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AH23" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI23" s="1"/>
       <c r="AJ23" s="1">
@@ -3293,10 +3296,10 @@
         <v>5</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H24" s="1">
         <v>6</v>
@@ -3305,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L24" s="1">
         <v>5</v>
@@ -3317,7 +3320,7 @@
         <v>50</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P24" s="1">
         <v>60</v>
@@ -3368,16 +3371,16 @@
         <v>0</v>
       </c>
       <c r="AF24" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG24" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AH24" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI24" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AJ24" s="1">
         <v>10000</v>
@@ -3394,7 +3397,7 @@
         <v>6</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G25" s="1"/>
       <c r="H25" s="1">
@@ -3404,7 +3407,7 @@
         <v>0</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -3416,7 +3419,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="P25" s="1">
         <v>0</v>
@@ -3467,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="AF25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG25" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH25" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ25" s="1">
         <v>10000</v>
@@ -3490,10 +3493,10 @@
         <v>7</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H26" s="1">
         <v>3</v>
@@ -3502,10 +3505,10 @@
         <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -3517,7 +3520,7 @@
         <v>10</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P26" s="1">
         <v>15</v>
@@ -3568,13 +3571,13 @@
         <v>0</v>
       </c>
       <c r="AF26" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG26" s="7" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AH26" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI26" s="1"/>
       <c r="AJ26" s="1">
@@ -3617,7 +3620,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="1">
@@ -3627,7 +3630,7 @@
         <v>1</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -3639,7 +3642,7 @@
         <v>20</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="P34" s="1">
         <v>0</v>
@@ -3690,13 +3693,13 @@
         <v>0</v>
       </c>
       <c r="AF34" s="7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AG34" s="7" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AH34" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ34" s="1">
         <v>10000</v>
@@ -3713,10 +3716,10 @@
         <v>2</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H35" s="1">
         <v>2</v>
@@ -3725,10 +3728,10 @@
         <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -3740,10 +3743,10 @@
         <v>10</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P35" s="1">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Q35" s="1">
         <v>0</v>
@@ -3791,13 +3794,13 @@
         <v>0</v>
       </c>
       <c r="AF35" s="7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="AG35" s="7" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AH35" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ35" s="1">
         <v>10000</v>
@@ -3814,10 +3817,10 @@
         <v>3</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H36" s="1">
         <v>2</v>
@@ -3826,10 +3829,10 @@
         <v>1</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -3841,7 +3844,7 @@
         <v>10</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="P36" s="1">
         <v>10</v>
@@ -3892,16 +3895,16 @@
         <v>0</v>
       </c>
       <c r="AF36" s="7" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG36" s="7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AH36" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI36" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AJ36" s="1">
         <v>10000</v>
@@ -3918,10 +3921,10 @@
         <v>4</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H37" s="1">
         <v>8</v>
@@ -3930,10 +3933,10 @@
         <v>1</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -3945,7 +3948,7 @@
         <v>100</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="P37" s="1">
         <v>15</v>
@@ -3996,13 +3999,13 @@
         <v>0</v>
       </c>
       <c r="AF37" s="7" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG37" s="7" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AH37" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ37" s="1">
         <v>10000</v>
@@ -4019,10 +4022,10 @@
         <v>5</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H38" s="1">
         <v>6</v>
@@ -4031,7 +4034,7 @@
         <v>1</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L38" s="1">
         <v>5</v>
@@ -4043,7 +4046,7 @@
         <v>50</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P38" s="1">
         <v>60</v>
@@ -4094,16 +4097,16 @@
         <v>0</v>
       </c>
       <c r="AF38" s="7" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG38" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AH38" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AI38" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AJ38" s="1">
         <v>10000</v>
@@ -4120,7 +4123,7 @@
         <v>6</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G39" s="1"/>
       <c r="H39" s="1">
@@ -4130,7 +4133,7 @@
         <v>0</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -4142,7 +4145,7 @@
         <v>10</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="P39" s="1">
         <v>0</v>
@@ -4193,13 +4196,13 @@
         <v>0</v>
       </c>
       <c r="AF39" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG39" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AH39" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ39" s="1">
         <v>10000</v>
@@ -4216,10 +4219,10 @@
         <v>7</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H40" s="1">
         <v>4</v>
@@ -4228,10 +4231,10 @@
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L40" s="1">
         <v>6</v>
@@ -4243,7 +4246,7 @@
         <v>100</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="P40" s="1">
         <v>30</v>
@@ -4294,13 +4297,13 @@
         <v>0</v>
       </c>
       <c r="AF40" s="7" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG40" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AH40" s="7" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AJ40" s="1">
         <v>10000</v>
@@ -4326,10 +4329,10 @@
         <v>0</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H44" s="1">
         <v>0</v>
@@ -4338,7 +4341,7 @@
         <v>0</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -4350,7 +4353,7 @@
         <v>-100</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P44" s="1">
         <v>30</v>
@@ -4415,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H45" s="1">
         <v>0</v>
@@ -4427,7 +4430,7 @@
         <v>0</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -4439,7 +4442,7 @@
         <v>200</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="P45" s="1">
         <v>60</v>
@@ -4508,10 +4511,10 @@
         <v>0</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H46" s="1">
         <v>0</v>
@@ -4520,7 +4523,7 @@
         <v>0</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
@@ -4532,7 +4535,7 @@
         <v>-1</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P46" s="1">
         <v>60</v>
@@ -4600,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H48" s="1">
         <v>9</v>
@@ -4612,10 +4615,10 @@
         <v>0</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L48" s="1">
         <v>0</v>
@@ -4627,7 +4630,7 @@
         <v>10</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="P48" s="1">
         <v>0</v>
@@ -4696,10 +4699,10 @@
         <v>0</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H50" s="1">
         <v>0</v>
@@ -4708,10 +4711,10 @@
         <v>0</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L50" s="1">
         <v>0</v>
